--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,87 +417,87 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>run_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>coin_id</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>symbol</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>current_price</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>market_cap_rank</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>total_volume</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>high_24h</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>low_24h</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price_change_24h</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>price_change_percentage_24h</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>circulating_supply</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>total_supply</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>ath</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>ath_date</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>last_updated</t>
         </is>
@@ -518,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260901T003239Z-816a43</t>
+          <t>20260901T005351Z-67d0df</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -537,16 +525,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>78847</v>
+        <v>78728</v>
       </c>
       <c r="F2" t="n">
-        <v>1583131500744</v>
+        <v>1580778315744</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>29472754143</v>
+        <v>29450393310</v>
       </c>
       <c r="I2" t="n">
         <v>79230</v>
@@ -555,13 +543,13 @@
         <v>77388</v>
       </c>
       <c r="K2" t="n">
-        <v>1077.89</v>
+        <v>1002.03</v>
       </c>
       <c r="L2" t="n">
-        <v>1.23946</v>
+        <v>1.0051</v>
       </c>
       <c r="M2" t="n">
-        <v>20077862</v>
+        <v>20077953</v>
       </c>
       <c r="N2" t="n">
         <v>20077953</v>
@@ -576,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-01T00:29:20.000Z</t>
+          <t>2026-09-01T00:51:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260901T003239Z-816a43</t>
+          <t>20260901T005351Z-67d0df</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -602,16 +590,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2474.56</v>
+        <v>2473.12</v>
       </c>
       <c r="F3" t="n">
-        <v>298620559442</v>
+        <v>298475905066</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>11946803967</v>
+        <v>11897534874</v>
       </c>
       <c r="I3" t="n">
         <v>2488.52</v>
@@ -620,10 +608,10 @@
         <v>2401.8</v>
       </c>
       <c r="K3" t="n">
-        <v>54.6</v>
+        <v>56.09</v>
       </c>
       <c r="L3" t="n">
-        <v>1.87852</v>
+        <v>1.83616</v>
       </c>
       <c r="M3" t="n">
         <v>120681146.1824211</v>
@@ -641,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-01T00:29:20.000Z</t>
+          <t>2026-09-01T00:51:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260901T003239Z-816a43</t>
+          <t>20260901T005351Z-67d0df</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -667,16 +655,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999749</v>
+        <v>0.9997470000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>183333059723</v>
+        <v>183329226957</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>51638630557</v>
+        <v>51495051628</v>
       </c>
       <c r="I4" t="n">
         <v>0.999934</v>
@@ -685,10 +673,10 @@
         <v>0.999631</v>
       </c>
       <c r="K4" t="n">
-        <v>-9.7532108561227e-05</v>
+        <v>-8.9317885615059e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.00878</v>
+        <v>-0.00436</v>
       </c>
       <c r="M4" t="n">
         <v>183378837337.8042</v>
@@ -706,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-01T00:29:20.000Z</t>
+          <t>2026-09-01T00:51:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260901T003239Z-816a43</t>
+          <t>20260901T005351Z-67d0df</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -732,16 +720,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>692.6</v>
+        <v>693.64</v>
       </c>
       <c r="F5" t="n">
-        <v>92242055573</v>
+        <v>92357416908</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>693097485</v>
+        <v>673876800</v>
       </c>
       <c r="I5" t="n">
         <v>694.12</v>
@@ -750,16 +738,16 @@
         <v>682.1799999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>7.27</v>
+        <v>9.81</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8912099999999999</v>
+        <v>1.04667</v>
       </c>
       <c r="M5" t="n">
-        <v>133162373.25</v>
+        <v>133162372.09</v>
       </c>
       <c r="N5" t="n">
-        <v>133162372.09</v>
+        <v>133162369.79</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -771,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-01T00:29:20.000Z</t>
+          <t>2026-09-01T00:51:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260901T003239Z-816a43</t>
+          <t>20260901T005351Z-67d0df</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -800,13 +788,13 @@
         <v>1.39</v>
       </c>
       <c r="F6" t="n">
-        <v>86999076655</v>
+        <v>86977179381</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>1937093976</v>
+        <v>1938267699</v>
       </c>
       <c r="I6" t="n">
         <v>1.4</v>
@@ -815,10 +803,10 @@
         <v>1.34</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03563504</v>
+        <v>0.03910702</v>
       </c>
       <c r="L6" t="n">
-        <v>1.79356</v>
+        <v>1.50392</v>
       </c>
       <c r="M6" t="n">
         <v>62744504852</v>
@@ -836,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-01T00:29:20.000Z</t>
+          <t>2026-09-01T00:51:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260901T003239Z-816a43</t>
+          <t>20260901T005351Z-67d0df</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -862,16 +850,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999872</v>
+        <v>0.999871</v>
       </c>
       <c r="F7" t="n">
-        <v>73423967633</v>
+        <v>73422945687</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>16162619273</v>
+        <v>16056035978</v>
       </c>
       <c r="I7" t="n">
         <v>0.999991</v>
@@ -880,16 +868,16 @@
         <v>0.999709</v>
       </c>
       <c r="K7" t="n">
-        <v>2.841e-05</v>
+        <v>1.82e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0025</v>
+        <v>0.00643</v>
       </c>
       <c r="M7" t="n">
         <v>73433561549.91263</v>
       </c>
       <c r="N7" t="n">
-        <v>73471746533.49838</v>
+        <v>73448496102.22746</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -901,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-01T00:29:20.000Z</t>
+          <t>2026-09-01T00:51:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260901T003239Z-816a43</t>
+          <t>20260901T005351Z-67d0df</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -927,16 +915,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103.38</v>
+        <v>103.35</v>
       </c>
       <c r="F8" t="n">
-        <v>60498733909</v>
+        <v>60487860541</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>3171840372</v>
+        <v>3178330803</v>
       </c>
       <c r="I8" t="n">
         <v>104.9</v>
@@ -945,16 +933,16 @@
         <v>100.95</v>
       </c>
       <c r="K8" t="n">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="L8" t="n">
-        <v>1.26255</v>
+        <v>1.12473</v>
       </c>
       <c r="M8" t="n">
-        <v>585206984.2423131</v>
+        <v>585207285.2428405</v>
       </c>
       <c r="N8" t="n">
-        <v>633267738.9238557</v>
+        <v>633267702.8268631</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -966,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-01T00:29:20.000Z</t>
+          <t>2026-09-01T00:51:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260901T003239Z-816a43</t>
+          <t>20260901T005351Z-67d0df</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -992,16 +980,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.332267</v>
+        <v>0.332235</v>
       </c>
       <c r="F9" t="n">
-        <v>31546068709</v>
+        <v>31536968896</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>438427702</v>
+        <v>440032448</v>
       </c>
       <c r="I9" t="n">
         <v>0.337174</v>
@@ -1010,16 +998,16 @@
         <v>0.331749</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.003983881937509759</v>
+        <v>-0.003754662527843622</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.95259</v>
+        <v>-1.04159</v>
       </c>
       <c r="M9" t="n">
         <v>94928981414.23039</v>
       </c>
       <c r="N9" t="n">
-        <v>94929496652.37318</v>
+        <v>94929625284.13228</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1031,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-01T00:29:20.000Z</t>
+          <t>2026-09-01T00:51:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260901T003239Z-816a43</t>
+          <t>20260901T005351Z-67d0df</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1060,13 +1048,13 @@
         <v>1.002</v>
       </c>
       <c r="F10" t="n">
-        <v>21871084856</v>
+        <v>21871413440</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>657231219</v>
+        <v>657228318</v>
       </c>
       <c r="I10" t="n">
         <v>1.056</v>
@@ -1092,14 +1080,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-09-01T00:29:20.000Z</t>
+          <t>2026-09-01T00:51:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260901T003239Z-816a43</t>
+          <t>20260901T005351Z-67d0df</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1118,16 +1106,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>84.2</v>
+        <v>84.25</v>
       </c>
       <c r="F11" t="n">
-        <v>18728062147</v>
+        <v>18742898740</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>1165892279</v>
+        <v>1166971971</v>
       </c>
       <c r="I11" t="n">
         <v>85.29000000000001</v>
@@ -1136,10 +1124,10 @@
         <v>79.84999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>4.01</v>
+        <v>4.16</v>
       </c>
       <c r="L11" t="n">
-        <v>4.73969</v>
+        <v>5.14335</v>
       </c>
       <c r="M11" t="n">
         <v>222445714.0741414</v>
@@ -1157,14 +1145,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-01T00:29:20.000Z</t>
+          <t>2026-09-01T00:51:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260901T003239Z-816a43</t>
+          <t>20260901T005351Z-67d0df</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1183,16 +1171,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>856.98</v>
+        <v>857.38</v>
       </c>
       <c r="F12" t="n">
-        <v>14491022676</v>
+        <v>14494713816</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>647582142</v>
+        <v>636968112</v>
       </c>
       <c r="I12" t="n">
         <v>870.96</v>
@@ -1201,16 +1189,16 @@
         <v>808.4</v>
       </c>
       <c r="K12" t="n">
-        <v>20.74</v>
+        <v>25.04</v>
       </c>
       <c r="L12" t="n">
-        <v>2.4785</v>
+        <v>2.40646</v>
       </c>
       <c r="M12" t="n">
         <v>16906800.1655448</v>
       </c>
       <c r="N12" t="n">
-        <v>16907714.2280448</v>
+        <v>16907807.9780448</v>
       </c>
       <c r="O12" t="n">
         <v>3191.93</v>
@@ -1222,14 +1210,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-01T00:29:20.000Z</t>
+          <t>2026-09-01T00:51:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260901T003239Z-816a43</t>
+          <t>20260901T005351Z-67d0df</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1248,16 +1236,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.083094</v>
+        <v>0.083166</v>
       </c>
       <c r="F13" t="n">
-        <v>12938197506</v>
+        <v>12949407896</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>494143585</v>
+        <v>499155486</v>
       </c>
       <c r="I13" t="n">
         <v>0.083884</v>
@@ -1266,16 +1254,16 @@
         <v>0.08148</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0010273</v>
+        <v>0.00138356</v>
       </c>
       <c r="L13" t="n">
-        <v>0.91935</v>
+        <v>0.84102</v>
       </c>
       <c r="M13" t="n">
-        <v>155725996383.7052</v>
+        <v>155727946383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>155727396383.7052</v>
+        <v>155728106383.7052</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1287,14 +1275,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-01T00:29:20.000Z</t>
+          <t>2026-09-01T00:51:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260901T003239Z-816a43</t>
+          <t>20260901T005351Z-67d0df</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1313,16 +1301,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.01674115</v>
+        <v>0.01673351</v>
       </c>
       <c r="F14" t="n">
-        <v>11873125598</v>
+        <v>11868015273</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>30038661</v>
+        <v>30036741</v>
       </c>
       <c r="I14" t="n">
         <v>0.01712303</v>
@@ -1331,10 +1319,10 @@
         <v>0.01598181</v>
       </c>
       <c r="K14" t="n">
-        <v>7.799e-05</v>
+        <v>8.610000000000001e-05</v>
       </c>
       <c r="L14" t="n">
-        <v>0.24574</v>
+        <v>0.42422</v>
       </c>
       <c r="M14" t="n">
         <v>709195093196.6458</v>
@@ -1352,14 +1340,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-09-01T00:29:20.000Z</t>
+          <t>2026-09-01T00:51:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260901T003239Z-816a43</t>
+          <t>20260901T005351Z-67d0df</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1378,16 +1366,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.9998089999999999</v>
+        <v>0.999814</v>
       </c>
       <c r="F15" t="n">
-        <v>9824750804</v>
+        <v>9818738787</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>165664793</v>
+        <v>165772701</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
@@ -1396,16 +1384,16 @@
         <v>0.9995039999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>9.501999999999999e-05</v>
+        <v>0.0001093</v>
       </c>
       <c r="L15" t="n">
-        <v>-3e-05</v>
+        <v>0.02021</v>
       </c>
       <c r="M15" t="n">
-        <v>9826619305.728388</v>
+        <v>9819763472.084112</v>
       </c>
       <c r="N15" t="n">
-        <v>9819763472.084112</v>
+        <v>9831073356.288452</v>
       </c>
       <c r="O15" t="n">
         <v>1.057</v>
@@ -1417,14 +1405,14 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-09-01T00:29:20.000Z</t>
+          <t>2026-09-01T00:51:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260901T003239Z-816a43</t>
+          <t>20260901T005351Z-67d0df</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1443,16 +1431,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>522.71</v>
+        <v>520.1900000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>9823289770</v>
+        <v>9778919346</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>211453098</v>
+        <v>208710403</v>
       </c>
       <c r="I16" t="n">
         <v>546.99</v>
@@ -1461,16 +1449,16 @@
         <v>487.57</v>
       </c>
       <c r="K16" t="n">
-        <v>33.74</v>
+        <v>24.49</v>
       </c>
       <c r="L16" t="n">
-        <v>8.562519999999999</v>
+        <v>6.37578</v>
       </c>
       <c r="M16" t="n">
         <v>18798685.22595168</v>
       </c>
       <c r="N16" t="n">
-        <v>18798728.42585589</v>
+        <v>18798743.4258201</v>
       </c>
       <c r="O16" t="n">
         <v>797.73</v>
@@ -1482,14 +1470,14 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-09-01T00:29:20.000Z</t>
+          <t>2026-09-01T00:51:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260901T003239Z-816a43</t>
+          <t>20260901T005351Z-67d0df</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1511,13 +1499,13 @@
         <v>9.57</v>
       </c>
       <c r="F17" t="n">
-        <v>8805509735</v>
+        <v>8805381203</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>114337</v>
+        <v>114299</v>
       </c>
       <c r="I17" t="n">
         <v>9.66</v>
@@ -1526,10 +1514,10 @@
         <v>9.56</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.05622753996260954</v>
+        <v>-0.04792232302102484</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.61276</v>
+        <v>-0.61208</v>
       </c>
       <c r="M17" t="n">
         <v>919864410.9</v>
@@ -1547,14 +1535,14 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-09-01T00:29:20.000Z</t>
+          <t>2026-09-01T00:51:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260901T003239Z-816a43</t>
+          <t>20260901T005351Z-67d0df</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1573,16 +1561,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>72.59999999999999</v>
+        <v>72.56</v>
       </c>
       <c r="F18" t="n">
-        <v>8573058713</v>
+        <v>8558954418</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>100935000</v>
+        <v>100485176</v>
       </c>
       <c r="I18" t="n">
         <v>72.98</v>
@@ -1591,10 +1579,10 @@
         <v>71.20999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>1.079</v>
+        <v>1.056</v>
       </c>
       <c r="L18" t="n">
-        <v>1.22184</v>
+        <v>1.16198</v>
       </c>
       <c r="M18" t="n">
         <v>117956019</v>
@@ -1612,14 +1600,14 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-09-01T00:29:20.000Z</t>
+          <t>2026-09-01T00:51:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260901T003239Z-816a43</t>
+          <t>20260901T005351Z-67d0df</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1638,16 +1626,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>11.35</v>
+        <v>11.39</v>
       </c>
       <c r="F19" t="n">
-        <v>8492671594</v>
+        <v>8516937694</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>385849876</v>
+        <v>397581014</v>
       </c>
       <c r="I19" t="n">
         <v>11.49</v>
@@ -1656,10 +1644,10 @@
         <v>11.04</v>
       </c>
       <c r="K19" t="n">
-        <v>0.188671</v>
+        <v>0.261389</v>
       </c>
       <c r="L19" t="n">
-        <v>1.37545</v>
+        <v>1.68385</v>
       </c>
       <c r="M19" t="n">
         <v>748099970.424884</v>
@@ -1677,14 +1665,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-09-01T00:29:20.000Z</t>
+          <t>2026-09-01T00:51:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260901T003239Z-816a43</t>
+          <t>20260901T005351Z-67d0df</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1703,16 +1691,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.199445</v>
+        <v>0.199819</v>
       </c>
       <c r="F20" t="n">
-        <v>7478172897</v>
+        <v>7493466995</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>292560048</v>
+        <v>312299140</v>
       </c>
       <c r="I20" t="n">
         <v>0.200437</v>
@@ -1721,10 +1709,10 @@
         <v>0.191803</v>
       </c>
       <c r="K20" t="n">
-        <v>0.00600324</v>
+        <v>0.00704607</v>
       </c>
       <c r="L20" t="n">
-        <v>3.0039</v>
+        <v>2.79686</v>
       </c>
       <c r="M20" t="n">
         <v>37498597081.30407</v>
@@ -1742,14 +1730,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-09-01T00:29:20.000Z</t>
+          <t>2026-09-01T00:51:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260901T003239Z-816a43</t>
+          <t>20260901T005351Z-67d0df</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1768,16 +1756,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.178335</v>
+        <v>0.178529</v>
       </c>
       <c r="F21" t="n">
-        <v>6187624438</v>
+        <v>6192850424</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>123511182</v>
+        <v>129445545</v>
       </c>
       <c r="I21" t="n">
         <v>0.179955</v>
@@ -1786,13 +1774,13 @@
         <v>0.173945</v>
       </c>
       <c r="K21" t="n">
-        <v>0.00320599</v>
+        <v>0.00410396</v>
       </c>
       <c r="L21" t="n">
-        <v>1.87529</v>
+        <v>1.59309</v>
       </c>
       <c r="M21" t="n">
-        <v>34690471886.53394</v>
+        <v>34694742172.84229</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.91247</v>
@@ -1807,7 +1795,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-09-01T00:29:20.000Z</t>
+          <t>2026-09-01T00:51:20.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260901T005351Z-67d0df</t>
+          <t>20260901T005723Z-4c9726</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,16 +525,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>78728</v>
+        <v>78632</v>
       </c>
       <c r="F2" t="n">
-        <v>1580778315744</v>
+        <v>1578990806124</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>29450393310</v>
+        <v>29472598256</v>
       </c>
       <c r="I2" t="n">
         <v>79230</v>
@@ -543,16 +543,16 @@
         <v>77388</v>
       </c>
       <c r="K2" t="n">
-        <v>1002.03</v>
+        <v>931.54</v>
       </c>
       <c r="L2" t="n">
-        <v>1.0051</v>
+        <v>0.83735</v>
       </c>
       <c r="M2" t="n">
         <v>20077953</v>
       </c>
       <c r="N2" t="n">
-        <v>20077953</v>
+        <v>20077993</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-01T00:51:20.000Z</t>
+          <t>2026-09-01T00:54:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260901T005351Z-67d0df</t>
+          <t>20260901T005723Z-4c9726</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,16 +590,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2473.12</v>
+        <v>2470.51</v>
       </c>
       <c r="F3" t="n">
-        <v>298475905066</v>
+        <v>298180495623</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>11897534874</v>
+        <v>11886349330</v>
       </c>
       <c r="I3" t="n">
         <v>2488.52</v>
@@ -608,10 +608,10 @@
         <v>2401.8</v>
       </c>
       <c r="K3" t="n">
-        <v>56.09</v>
+        <v>54.39</v>
       </c>
       <c r="L3" t="n">
-        <v>1.83616</v>
+        <v>1.60809</v>
       </c>
       <c r="M3" t="n">
         <v>120681146.1824211</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-01T00:51:20.000Z</t>
+          <t>2026-09-01T00:54:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260901T005351Z-67d0df</t>
+          <t>20260901T005723Z-4c9726</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,16 +655,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9997470000000001</v>
+        <v>0.999735</v>
       </c>
       <c r="F4" t="n">
-        <v>183329226957</v>
+        <v>183332712114</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>51495051628</v>
+        <v>51492998157</v>
       </c>
       <c r="I4" t="n">
         <v>0.999934</v>
@@ -673,10 +673,10 @@
         <v>0.999631</v>
       </c>
       <c r="K4" t="n">
-        <v>-8.9317885615059e-05</v>
+        <v>-0.000110786726701839</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.00436</v>
+        <v>-0.00551</v>
       </c>
       <c r="M4" t="n">
         <v>183378837337.8042</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-01T00:51:20.000Z</t>
+          <t>2026-09-01T00:54:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260901T005351Z-67d0df</t>
+          <t>20260901T005723Z-4c9726</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>693.64</v>
+        <v>693.01</v>
       </c>
       <c r="F5" t="n">
-        <v>92357416908</v>
+        <v>92294766491</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>673876800</v>
+        <v>693095793</v>
       </c>
       <c r="I5" t="n">
         <v>694.12</v>
@@ -738,10 +738,10 @@
         <v>682.1799999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>9.81</v>
+        <v>9.58</v>
       </c>
       <c r="L5" t="n">
-        <v>1.04667</v>
+        <v>0.91062</v>
       </c>
       <c r="M5" t="n">
         <v>133162372.09</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-01T00:51:20.000Z</t>
+          <t>2026-09-01T00:54:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260901T005351Z-67d0df</t>
+          <t>20260901T005723Z-4c9726</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,16 +785,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="F6" t="n">
-        <v>86977179381</v>
+        <v>86859900701</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>1938267699</v>
+        <v>1935723863</v>
       </c>
       <c r="I6" t="n">
         <v>1.4</v>
@@ -803,10 +803,10 @@
         <v>1.34</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03910702</v>
+        <v>0.03835514</v>
       </c>
       <c r="L6" t="n">
-        <v>1.50392</v>
+        <v>1.26048</v>
       </c>
       <c r="M6" t="n">
         <v>62744504852</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-01T00:51:20.000Z</t>
+          <t>2026-09-01T00:54:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260901T005351Z-67d0df</t>
+          <t>20260901T005723Z-4c9726</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,16 +850,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999871</v>
+        <v>0.999865</v>
       </c>
       <c r="F7" t="n">
-        <v>73422945687</v>
+        <v>73424722723</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>16056035978</v>
+        <v>16056657787</v>
       </c>
       <c r="I7" t="n">
         <v>0.999991</v>
@@ -868,10 +868,10 @@
         <v>0.999709</v>
       </c>
       <c r="K7" t="n">
-        <v>1.82e-05</v>
+        <v>1.099e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00643</v>
+        <v>0.00507</v>
       </c>
       <c r="M7" t="n">
         <v>73433561549.91263</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-01T00:51:20.000Z</t>
+          <t>2026-09-01T00:54:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260901T005351Z-67d0df</t>
+          <t>20260901T005723Z-4c9726</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,16 +915,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103.35</v>
+        <v>103.16</v>
       </c>
       <c r="F8" t="n">
-        <v>60487860541</v>
+        <v>60385337474</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>3178330803</v>
+        <v>3174078586</v>
       </c>
       <c r="I8" t="n">
         <v>104.9</v>
@@ -933,10 +933,10 @@
         <v>100.95</v>
       </c>
       <c r="K8" t="n">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="L8" t="n">
-        <v>1.12473</v>
+        <v>0.85678</v>
       </c>
       <c r="M8" t="n">
         <v>585207285.2428405</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-01T00:51:20.000Z</t>
+          <t>2026-09-01T00:54:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260901T005351Z-67d0df</t>
+          <t>20260901T005723Z-4c9726</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,16 +980,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.332235</v>
+        <v>0.332137</v>
       </c>
       <c r="F9" t="n">
-        <v>31536968896</v>
+        <v>31529567260</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>440032448</v>
+        <v>424464221</v>
       </c>
       <c r="I9" t="n">
         <v>0.337174</v>
@@ -998,10 +998,10 @@
         <v>0.331749</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.003754662527843622</v>
+        <v>-0.003795037758068498</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.04159</v>
+        <v>-1.12666</v>
       </c>
       <c r="M9" t="n">
         <v>94928981414.23039</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-01T00:51:20.000Z</t>
+          <t>2026-09-01T00:54:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260901T005351Z-67d0df</t>
+          <t>20260901T005723Z-4c9726</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1048,13 +1048,13 @@
         <v>1.002</v>
       </c>
       <c r="F10" t="n">
-        <v>21871413440</v>
+        <v>21870990604</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>657228318</v>
+        <v>657237710</v>
       </c>
       <c r="I10" t="n">
         <v>1.056</v>
@@ -1080,14 +1080,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-09-01T00:51:20.000Z</t>
+          <t>2026-09-01T00:54:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260901T005351Z-67d0df</t>
+          <t>20260901T005723Z-4c9726</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>84.25</v>
+        <v>84.2</v>
       </c>
       <c r="F11" t="n">
-        <v>18742898740</v>
+        <v>18744099925</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>1166971971</v>
+        <v>1183899067</v>
       </c>
       <c r="I11" t="n">
         <v>85.29000000000001</v>
@@ -1127,7 +1127,7 @@
         <v>4.16</v>
       </c>
       <c r="L11" t="n">
-        <v>5.14335</v>
+        <v>4.88109</v>
       </c>
       <c r="M11" t="n">
         <v>222445714.0741414</v>
@@ -1145,14 +1145,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-01T00:51:20.000Z</t>
+          <t>2026-09-01T00:54:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260901T005351Z-67d0df</t>
+          <t>20260901T005723Z-4c9726</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1171,16 +1171,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>857.38</v>
+        <v>855.3099999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>14494713816</v>
+        <v>14470561233</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>636968112</v>
+        <v>635767204</v>
       </c>
       <c r="I12" t="n">
         <v>870.96</v>
@@ -1189,10 +1189,10 @@
         <v>808.4</v>
       </c>
       <c r="K12" t="n">
-        <v>25.04</v>
+        <v>24.19</v>
       </c>
       <c r="L12" t="n">
-        <v>2.40646</v>
+        <v>2.08492</v>
       </c>
       <c r="M12" t="n">
         <v>16906800.1655448</v>
@@ -1210,14 +1210,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-01T00:51:20.000Z</t>
+          <t>2026-09-01T00:54:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260901T005351Z-67d0df</t>
+          <t>20260901T005723Z-4c9726</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1236,16 +1236,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.083166</v>
+        <v>0.083056</v>
       </c>
       <c r="F13" t="n">
-        <v>12949407896</v>
+        <v>12937214584</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>499155486</v>
+        <v>512037856</v>
       </c>
       <c r="I13" t="n">
         <v>0.083884</v>
@@ -1254,10 +1254,10 @@
         <v>0.08148</v>
       </c>
       <c r="K13" t="n">
-        <v>0.00138356</v>
+        <v>0.00133899</v>
       </c>
       <c r="L13" t="n">
-        <v>0.84102</v>
+        <v>0.6785099999999999</v>
       </c>
       <c r="M13" t="n">
         <v>155727946383.7052</v>
@@ -1275,14 +1275,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-01T00:51:20.000Z</t>
+          <t>2026-09-01T00:54:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260901T005351Z-67d0df</t>
+          <t>20260901T005723Z-4c9726</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1301,16 +1301,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.01673351</v>
+        <v>0.01672047</v>
       </c>
       <c r="F14" t="n">
-        <v>11868015273</v>
+        <v>11855218822</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>30036741</v>
+        <v>28542804</v>
       </c>
       <c r="I14" t="n">
         <v>0.01712303</v>
@@ -1319,10 +1319,10 @@
         <v>0.01598181</v>
       </c>
       <c r="K14" t="n">
-        <v>8.610000000000001e-05</v>
+        <v>8.632e-05</v>
       </c>
       <c r="L14" t="n">
-        <v>0.42422</v>
+        <v>0.23325</v>
       </c>
       <c r="M14" t="n">
         <v>709195093196.6458</v>
@@ -1340,14 +1340,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-09-01T00:51:20.000Z</t>
+          <t>2026-09-01T00:54:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260901T005351Z-67d0df</t>
+          <t>20260901T005723Z-4c9726</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1366,16 +1366,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.999814</v>
+        <v>0.999898</v>
       </c>
       <c r="F15" t="n">
-        <v>9818738787</v>
+        <v>9818915822</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>165772701</v>
+        <v>167207715</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
@@ -1384,10 +1384,10 @@
         <v>0.9995039999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0001093</v>
+        <v>8.75e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02021</v>
+        <v>0.01421</v>
       </c>
       <c r="M15" t="n">
         <v>9819763472.084112</v>
@@ -1405,14 +1405,14 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-09-01T00:51:20.000Z</t>
+          <t>2026-09-01T00:54:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260901T005351Z-67d0df</t>
+          <t>20260901T005723Z-4c9726</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1431,16 +1431,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>520.1900000000001</v>
+        <v>519.7</v>
       </c>
       <c r="F16" t="n">
-        <v>9778919346</v>
+        <v>9772337757</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>208710403</v>
+        <v>208271217</v>
       </c>
       <c r="I16" t="n">
         <v>546.99</v>
@@ -1449,10 +1449,10 @@
         <v>487.57</v>
       </c>
       <c r="K16" t="n">
-        <v>24.49</v>
+        <v>24.77</v>
       </c>
       <c r="L16" t="n">
-        <v>6.37578</v>
+        <v>6.1806</v>
       </c>
       <c r="M16" t="n">
         <v>18798685.22595168</v>
@@ -1470,14 +1470,14 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-09-01T00:51:20.000Z</t>
+          <t>2026-09-01T00:54:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260901T005351Z-67d0df</t>
+          <t>20260901T005723Z-4c9726</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1499,13 +1499,13 @@
         <v>9.57</v>
       </c>
       <c r="F17" t="n">
-        <v>8805381203</v>
+        <v>8805551827</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>114299</v>
+        <v>114261</v>
       </c>
       <c r="I17" t="n">
         <v>9.66</v>
@@ -1514,10 +1514,10 @@
         <v>9.56</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.04792232302102484</v>
+        <v>-0.07297158403318171</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.61208</v>
+        <v>-0.61381</v>
       </c>
       <c r="M17" t="n">
         <v>919864410.9</v>
@@ -1535,14 +1535,14 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-09-01T00:51:20.000Z</t>
+          <t>2026-09-01T00:54:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260901T005351Z-67d0df</t>
+          <t>20260901T005723Z-4c9726</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1561,16 +1561,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>72.56</v>
+        <v>72.48</v>
       </c>
       <c r="F18" t="n">
-        <v>8558954418</v>
+        <v>8549951548</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>100485176</v>
+        <v>100249178</v>
       </c>
       <c r="I18" t="n">
         <v>72.98</v>
@@ -1579,10 +1579,10 @@
         <v>71.20999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>1.056</v>
+        <v>1.007</v>
       </c>
       <c r="L18" t="n">
-        <v>1.16198</v>
+        <v>0.9946</v>
       </c>
       <c r="M18" t="n">
         <v>117956019</v>
@@ -1600,14 +1600,14 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-09-01T00:51:20.000Z</t>
+          <t>2026-09-01T00:54:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260901T005351Z-67d0df</t>
+          <t>20260901T005723Z-4c9726</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1626,16 +1626,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>11.39</v>
+        <v>11.38</v>
       </c>
       <c r="F19" t="n">
-        <v>8516937694</v>
+        <v>8512595851</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>397581014</v>
+        <v>395635840</v>
       </c>
       <c r="I19" t="n">
         <v>11.49</v>
@@ -1644,10 +1644,10 @@
         <v>11.04</v>
       </c>
       <c r="K19" t="n">
-        <v>0.261389</v>
+        <v>0.269309</v>
       </c>
       <c r="L19" t="n">
-        <v>1.68385</v>
+        <v>1.49231</v>
       </c>
       <c r="M19" t="n">
         <v>748099970.424884</v>
@@ -1665,14 +1665,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-09-01T00:51:20.000Z</t>
+          <t>2026-09-01T00:54:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260901T005351Z-67d0df</t>
+          <t>20260901T005723Z-4c9726</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1691,16 +1691,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.199819</v>
+        <v>0.19945</v>
       </c>
       <c r="F20" t="n">
-        <v>7493466995</v>
+        <v>7481940852</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>312299140</v>
+        <v>306147548</v>
       </c>
       <c r="I20" t="n">
         <v>0.200437</v>
@@ -1709,10 +1709,10 @@
         <v>0.191803</v>
       </c>
       <c r="K20" t="n">
-        <v>0.00704607</v>
+        <v>0.00678256</v>
       </c>
       <c r="L20" t="n">
-        <v>2.79686</v>
+        <v>2.5832</v>
       </c>
       <c r="M20" t="n">
         <v>37498597081.30407</v>
@@ -1730,14 +1730,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-09-01T00:51:20.000Z</t>
+          <t>2026-09-01T00:54:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260901T005351Z-67d0df</t>
+          <t>20260901T005723Z-4c9726</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1756,16 +1756,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.178529</v>
+        <v>0.178548</v>
       </c>
       <c r="F21" t="n">
-        <v>6192850424</v>
+        <v>6195019797</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>129445545</v>
+        <v>123379483</v>
       </c>
       <c r="I21" t="n">
         <v>0.179955</v>
@@ -1774,10 +1774,10 @@
         <v>0.173945</v>
       </c>
       <c r="K21" t="n">
-        <v>0.00410396</v>
+        <v>0.00431518</v>
       </c>
       <c r="L21" t="n">
-        <v>1.59309</v>
+        <v>1.58559</v>
       </c>
       <c r="M21" t="n">
         <v>34694742172.84229</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-09-01T00:51:20.000Z</t>
+          <t>2026-09-01T00:54:30.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260901T005723Z-4c9726</t>
+          <t>20260901T140450Z-3c5d68</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>78632</v>
+        <v>78151</v>
       </c>
       <c r="F2" t="n">
-        <v>1578990806124</v>
+        <v>1569885691673</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>29472598256</v>
+        <v>29590585374</v>
       </c>
       <c r="I2" t="n">
         <v>79230</v>
       </c>
       <c r="J2" t="n">
-        <v>77388</v>
+        <v>77523</v>
       </c>
       <c r="K2" t="n">
-        <v>931.54</v>
+        <v>-349.4784373934672</v>
       </c>
       <c r="L2" t="n">
-        <v>0.83735</v>
+        <v>0.35275</v>
       </c>
       <c r="M2" t="n">
-        <v>20077953</v>
+        <v>20078215</v>
       </c>
       <c r="N2" t="n">
-        <v>20077993</v>
+        <v>20078228</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-01T00:54:30.000Z</t>
+          <t>2026-09-01T14:02:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260901T005723Z-4c9726</t>
+          <t>20260901T140450Z-3c5d68</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2470.51</v>
+        <v>2446.09</v>
       </c>
       <c r="F3" t="n">
-        <v>298180495623</v>
+        <v>295448598447</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>11886349330</v>
+        <v>11585451732</v>
       </c>
       <c r="I3" t="n">
         <v>2488.52</v>
       </c>
       <c r="J3" t="n">
-        <v>2401.8</v>
+        <v>2432.33</v>
       </c>
       <c r="K3" t="n">
-        <v>54.39</v>
+        <v>-21.12186156989719</v>
       </c>
       <c r="L3" t="n">
-        <v>1.60809</v>
+        <v>0.21914</v>
       </c>
       <c r="M3" t="n">
-        <v>120681146.1824211</v>
+        <v>120681092.8627613</v>
       </c>
       <c r="N3" t="n">
-        <v>120681146.1824211</v>
+        <v>120681092.8627613</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-01T00:54:30.000Z</t>
+          <t>2026-09-01T14:02:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260901T005723Z-4c9726</t>
+          <t>20260901T140450Z-3c5d68</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,28 +655,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999735</v>
+        <v>0.999742</v>
       </c>
       <c r="F4" t="n">
-        <v>183332712114</v>
+        <v>183331711830</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>51492998157</v>
+        <v>51085779871</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999934</v>
+        <v>0.999904</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999631</v>
+        <v>0.999649</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.000110786726701839</v>
+        <v>-1.5755558932629e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.00551</v>
+        <v>0.00165</v>
       </c>
       <c r="M4" t="n">
         <v>183378837337.8042</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-01T00:54:30.000Z</t>
+          <t>2026-09-01T14:02:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260901T005723Z-4c9726</t>
+          <t>20260901T140450Z-3c5d68</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>693.01</v>
+        <v>687.26</v>
       </c>
       <c r="F5" t="n">
-        <v>92294766491</v>
+        <v>91544389868</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>693095793</v>
+        <v>640331713</v>
       </c>
       <c r="I5" t="n">
-        <v>694.12</v>
+        <v>694.22</v>
       </c>
       <c r="J5" t="n">
-        <v>682.1799999999999</v>
+        <v>683.9</v>
       </c>
       <c r="K5" t="n">
-        <v>9.58</v>
+        <v>-3.095038509529559</v>
       </c>
       <c r="L5" t="n">
-        <v>0.91062</v>
+        <v>0.23543</v>
       </c>
       <c r="M5" t="n">
-        <v>133162372.09</v>
+        <v>133162327.83</v>
       </c>
       <c r="N5" t="n">
-        <v>133162369.79</v>
+        <v>133162323.52</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-01T00:54:30.000Z</t>
+          <t>2026-09-01T14:02:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260901T005723Z-4c9726</t>
+          <t>20260901T140450Z-3c5d68</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -788,25 +788,25 @@
         <v>1.38</v>
       </c>
       <c r="F6" t="n">
-        <v>86859900701</v>
+        <v>86420625668</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>1935723863</v>
+        <v>1794248906</v>
       </c>
       <c r="I6" t="n">
         <v>1.4</v>
       </c>
       <c r="J6" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03835514</v>
+        <v>-0.000543388090346264</v>
       </c>
       <c r="L6" t="n">
-        <v>1.26048</v>
+        <v>0.95508</v>
       </c>
       <c r="M6" t="n">
         <v>62744504852</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-01T00:54:30.000Z</t>
+          <t>2026-09-01T14:02:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260901T005723Z-4c9726</t>
+          <t>20260901T140450Z-3c5d68</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999865</v>
+        <v>0.999858</v>
       </c>
       <c r="F7" t="n">
-        <v>73424722723</v>
+        <v>73409785688</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>16056657787</v>
+        <v>16352182564</v>
       </c>
       <c r="I7" t="n">
-        <v>0.999991</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999709</v>
+        <v>0.999739</v>
       </c>
       <c r="K7" t="n">
-        <v>1.099e-05</v>
+        <v>-6.06512515655e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00507</v>
+        <v>0.00243</v>
       </c>
       <c r="M7" t="n">
-        <v>73433561549.91263</v>
+        <v>73420075133.24463</v>
       </c>
       <c r="N7" t="n">
-        <v>73448496102.22746</v>
+        <v>73434446751.15912</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-01T00:54:30.000Z</t>
+          <t>2026-09-01T14:02:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260901T005723Z-4c9726</t>
+          <t>20260901T140450Z-3c5d68</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103.16</v>
+        <v>102.06</v>
       </c>
       <c r="F8" t="n">
-        <v>60385337474</v>
+        <v>59763125709</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>3174078586</v>
+        <v>3016918536</v>
       </c>
       <c r="I8" t="n">
         <v>104.9</v>
       </c>
       <c r="J8" t="n">
-        <v>100.95</v>
+        <v>101.41</v>
       </c>
       <c r="K8" t="n">
-        <v>1.59</v>
+        <v>-1.457119237005728</v>
       </c>
       <c r="L8" t="n">
-        <v>0.85678</v>
+        <v>-0.39595</v>
       </c>
       <c r="M8" t="n">
-        <v>585207285.2428405</v>
+        <v>585206839.8655083</v>
       </c>
       <c r="N8" t="n">
-        <v>633267702.8268631</v>
+        <v>633267250.9427586</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-01T00:54:30.000Z</t>
+          <t>2026-09-01T14:02:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260901T005723Z-4c9726</t>
+          <t>20260901T140450Z-3c5d68</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.332137</v>
+        <v>0.325939</v>
       </c>
       <c r="F9" t="n">
-        <v>31529567260</v>
+        <v>30938872609</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>424464221</v>
+        <v>510459563</v>
       </c>
       <c r="I9" t="n">
-        <v>0.337174</v>
+        <v>0.334031</v>
       </c>
       <c r="J9" t="n">
-        <v>0.331749</v>
+        <v>0.325524</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.003795037758068498</v>
+        <v>-0.006813270380735537</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.12666</v>
+        <v>-1.8279</v>
       </c>
       <c r="M9" t="n">
-        <v>94928981414.23039</v>
+        <v>94930103918.07219</v>
       </c>
       <c r="N9" t="n">
-        <v>94929625284.13228</v>
+        <v>94930055362.23859</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-01T00:54:30.000Z</t>
+          <t>2026-09-01T14:02:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260901T005723Z-4c9726</t>
+          <t>20260901T140450Z-3c5d68</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,16 +1045,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.002</v>
+        <v>1.013</v>
       </c>
       <c r="F10" t="n">
-        <v>21870990604</v>
+        <v>22110471426</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>657237710</v>
+        <v>861934919</v>
       </c>
       <c r="I10" t="n">
         <v>1.056</v>
@@ -1062,13 +1062,17 @@
       <c r="J10" t="n">
         <v>1.002</v>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="K10" t="n">
+        <v>-0.02229735024079815</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-2.38341</v>
+      </c>
       <c r="M10" t="n">
         <v>21833298808.828</v>
       </c>
       <c r="N10" t="n">
-        <v>21833298808.828</v>
+        <v>22027381341.788</v>
       </c>
       <c r="O10" t="n">
         <v>1.061</v>
@@ -1080,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-09-01T00:54:30.000Z</t>
+          <t>2026-09-01T14:02:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260901T005723Z-4c9726</t>
+          <t>20260901T140450Z-3c5d68</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1106,28 +1110,28 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>84.2</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>18744099925</v>
+        <v>18656551597</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>1183899067</v>
+        <v>1406474481</v>
       </c>
       <c r="I11" t="n">
         <v>85.29000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>79.84999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="K11" t="n">
-        <v>4.16</v>
+        <v>2.34</v>
       </c>
       <c r="L11" t="n">
-        <v>4.88109</v>
+        <v>3.80259</v>
       </c>
       <c r="M11" t="n">
         <v>222445714.0741414</v>
@@ -1145,14 +1149,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-01T00:54:30.000Z</t>
+          <t>2026-09-01T14:02:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260901T005723Z-4c9726</t>
+          <t>20260901T140450Z-3c5d68</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1171,34 +1175,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>855.3099999999999</v>
+        <v>855.98</v>
       </c>
       <c r="F12" t="n">
-        <v>14470561233</v>
+        <v>14475675298</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>635767204</v>
+        <v>573169713</v>
       </c>
       <c r="I12" t="n">
         <v>870.96</v>
       </c>
       <c r="J12" t="n">
-        <v>808.4</v>
+        <v>830.96</v>
       </c>
       <c r="K12" t="n">
-        <v>24.19</v>
+        <v>23.25</v>
       </c>
       <c r="L12" t="n">
-        <v>2.08492</v>
+        <v>4.06158</v>
       </c>
       <c r="M12" t="n">
         <v>16906800.1655448</v>
       </c>
       <c r="N12" t="n">
-        <v>16907807.9780448</v>
+        <v>16908772.0405448</v>
       </c>
       <c r="O12" t="n">
         <v>3191.93</v>
@@ -1210,14 +1214,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-01T00:54:30.000Z</t>
+          <t>2026-09-01T14:02:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260901T005723Z-4c9726</t>
+          <t>20260901T140450Z-3c5d68</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1236,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.083056</v>
+        <v>0.08286399999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>12937214584</v>
+        <v>12909260818</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>512037856</v>
+        <v>488842761</v>
       </c>
       <c r="I13" t="n">
-        <v>0.083884</v>
+        <v>0.083901</v>
       </c>
       <c r="J13" t="n">
-        <v>0.08148</v>
+        <v>0.08204</v>
       </c>
       <c r="K13" t="n">
-        <v>0.00133899</v>
+        <v>-0.0001486738771551</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6785099999999999</v>
+        <v>0.79401</v>
       </c>
       <c r="M13" t="n">
-        <v>155727946383.7052</v>
+        <v>155735116383.7053</v>
       </c>
       <c r="N13" t="n">
-        <v>155728106383.7052</v>
+        <v>171447393126.579</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1275,14 +1279,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-01T00:54:30.000Z</t>
+          <t>2026-09-01T14:02:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260901T005723Z-4c9726</t>
+          <t>20260901T140450Z-3c5d68</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1301,34 +1305,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.01672047</v>
+        <v>0.01660063</v>
       </c>
       <c r="F14" t="n">
-        <v>11855218822</v>
+        <v>11769702829</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>28542804</v>
+        <v>45627776</v>
       </c>
       <c r="I14" t="n">
         <v>0.01712303</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01598181</v>
+        <v>0.01655455</v>
       </c>
       <c r="K14" t="n">
-        <v>8.632e-05</v>
+        <v>-0.000497096489804342</v>
       </c>
       <c r="L14" t="n">
-        <v>0.23325</v>
+        <v>-2.45935</v>
       </c>
       <c r="M14" t="n">
-        <v>709195093196.6458</v>
+        <v>709195842281.2939</v>
       </c>
       <c r="N14" t="n">
-        <v>1142408564124.27</v>
+        <v>1142408552901.351</v>
       </c>
       <c r="O14" t="n">
         <v>0.01946402</v>
@@ -1340,14 +1344,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-09-01T00:54:30.000Z</t>
+          <t>2026-09-01T14:02:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260901T005723Z-4c9726</t>
+          <t>20260901T140450Z-3c5d68</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1366,34 +1370,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.999898</v>
+        <v>0.999902</v>
       </c>
       <c r="F15" t="n">
-        <v>9818915822</v>
+        <v>9839715036</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>167207715</v>
+        <v>180433082</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9995039999999999</v>
+        <v>0.999628</v>
       </c>
       <c r="K15" t="n">
-        <v>8.75e-05</v>
+        <v>0.0001778</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01421</v>
+        <v>0.02113</v>
       </c>
       <c r="M15" t="n">
-        <v>9819763472.084112</v>
+        <v>9840678940.050068</v>
       </c>
       <c r="N15" t="n">
-        <v>9831073356.288452</v>
+        <v>9845234620.789038</v>
       </c>
       <c r="O15" t="n">
         <v>1.057</v>
@@ -1405,14 +1409,14 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-09-01T00:54:30.000Z</t>
+          <t>2026-09-01T14:02:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260901T005723Z-4c9726</t>
+          <t>20260901T140450Z-3c5d68</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1431,34 +1435,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>519.7</v>
+        <v>509.56</v>
       </c>
       <c r="F16" t="n">
-        <v>9772337757</v>
+        <v>9568313100</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>208271217</v>
+        <v>157669034</v>
       </c>
       <c r="I16" t="n">
-        <v>546.99</v>
+        <v>536.53</v>
       </c>
       <c r="J16" t="n">
-        <v>487.57</v>
+        <v>505.67</v>
       </c>
       <c r="K16" t="n">
-        <v>24.77</v>
+        <v>-3.443537903775677</v>
       </c>
       <c r="L16" t="n">
-        <v>6.1806</v>
+        <v>0.29606</v>
       </c>
       <c r="M16" t="n">
-        <v>18798685.22595168</v>
+        <v>18798936.61165905</v>
       </c>
       <c r="N16" t="n">
-        <v>18798743.4258201</v>
+        <v>18798971.40256951</v>
       </c>
       <c r="O16" t="n">
         <v>797.73</v>
@@ -1470,14 +1474,14 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-09-01T00:54:30.000Z</t>
+          <t>2026-09-01T14:02:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260901T005723Z-4c9726</t>
+          <t>20260901T140450Z-3c5d68</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1496,31 +1500,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>9.57</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>8805551827</v>
+        <v>8612750636</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>114261</v>
+        <v>416632</v>
       </c>
       <c r="I17" t="n">
         <v>9.66</v>
       </c>
       <c r="J17" t="n">
-        <v>9.56</v>
+        <v>9.25</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.07297158403318171</v>
+        <v>-0.2771727449167827</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.61381</v>
+        <v>-2.87425</v>
       </c>
       <c r="M17" t="n">
-        <v>919864410.9</v>
+        <v>919857851.9</v>
       </c>
       <c r="N17" t="n">
         <v>985239504</v>
@@ -1535,144 +1539,144 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-09-01T00:54:30.000Z</t>
+          <t>2026-09-01T14:02:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260901T005723Z-4c9726</t>
+          <t>20260901T140450Z-3c5d68</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>whitebit</t>
+          <t>chainlink</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>wbt</t>
+          <t>link</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>WhiteBIT Coin</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>72.48</v>
+        <v>11.41</v>
       </c>
       <c r="F18" t="n">
-        <v>8549951548</v>
+        <v>8544217729</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>100249178</v>
+        <v>402987765</v>
       </c>
       <c r="I18" t="n">
-        <v>72.98</v>
+        <v>11.51</v>
       </c>
       <c r="J18" t="n">
-        <v>71.20999999999999</v>
+        <v>11.27</v>
       </c>
       <c r="K18" t="n">
-        <v>1.007</v>
+        <v>0.065885</v>
       </c>
       <c r="L18" t="n">
-        <v>0.9946</v>
+        <v>1.91985</v>
       </c>
       <c r="M18" t="n">
-        <v>117956019</v>
+        <v>748099970.424884</v>
       </c>
       <c r="N18" t="n">
-        <v>293606018</v>
+        <v>1000000000</v>
       </c>
       <c r="O18" t="n">
-        <v>74.97</v>
+        <v>52.7</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-08-25T02:42:30.000Z</t>
+          <t>2021-05-09T16:13:57.000Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-09-01T00:54:30.000Z</t>
+          <t>2026-09-01T14:02:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260901T005723Z-4c9726</t>
+          <t>20260901T140450Z-3c5d68</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>whitebit</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>wbt</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>WhiteBIT Coin</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>11.38</v>
+        <v>71.94</v>
       </c>
       <c r="F19" t="n">
-        <v>8512595851</v>
+        <v>8493027190</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>395635840</v>
+        <v>87122368</v>
       </c>
       <c r="I19" t="n">
-        <v>11.49</v>
+        <v>72.98</v>
       </c>
       <c r="J19" t="n">
-        <v>11.04</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>0.269309</v>
+        <v>-0.4012711885855538</v>
       </c>
       <c r="L19" t="n">
-        <v>1.49231</v>
+        <v>0.21384</v>
       </c>
       <c r="M19" t="n">
-        <v>748099970.424884</v>
+        <v>117956019</v>
       </c>
       <c r="N19" t="n">
-        <v>1000000000</v>
+        <v>293606018</v>
       </c>
       <c r="O19" t="n">
-        <v>52.7</v>
+        <v>74.97</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2021-05-09T16:13:57.000Z</t>
+          <t>2026-08-25T02:42:30.000Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-09-01T00:54:30.000Z</t>
+          <t>2026-09-01T14:02:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260901T005723Z-4c9726</t>
+          <t>20260901T140450Z-3c5d68</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1691,28 +1695,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.19945</v>
+        <v>0.199351</v>
       </c>
       <c r="F20" t="n">
-        <v>7481940852</v>
+        <v>7481984559</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>306147548</v>
+        <v>331914403</v>
       </c>
       <c r="I20" t="n">
-        <v>0.200437</v>
+        <v>0.202834</v>
       </c>
       <c r="J20" t="n">
-        <v>0.191803</v>
+        <v>0.195018</v>
       </c>
       <c r="K20" t="n">
-        <v>0.00678256</v>
+        <v>0.00258811</v>
       </c>
       <c r="L20" t="n">
-        <v>2.5832</v>
+        <v>2.64758</v>
       </c>
       <c r="M20" t="n">
         <v>37498597081.30407</v>
@@ -1730,14 +1734,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-09-01T00:54:30.000Z</t>
+          <t>2026-09-01T14:02:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260901T005723Z-4c9726</t>
+          <t>20260901T140450Z-3c5d68</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1756,31 +1760,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.178548</v>
+        <v>0.178056</v>
       </c>
       <c r="F21" t="n">
-        <v>6195019797</v>
+        <v>6183046555</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>123379483</v>
+        <v>122590256</v>
       </c>
       <c r="I21" t="n">
         <v>0.179955</v>
       </c>
       <c r="J21" t="n">
-        <v>0.173945</v>
+        <v>0.175005</v>
       </c>
       <c r="K21" t="n">
-        <v>0.00431518</v>
+        <v>0.0013073</v>
       </c>
       <c r="L21" t="n">
-        <v>1.58559</v>
+        <v>1.81229</v>
       </c>
       <c r="M21" t="n">
-        <v>34694742172.84229</v>
+        <v>34694738330.92985</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.91247</v>
@@ -1795,7 +1799,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-09-01T00:54:30.000Z</t>
+          <t>2026-09-01T14:02:20.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260901T140450Z-3c5d68</t>
+          <t>20260902T133046Z-54c889</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>78151</v>
+        <v>76825</v>
       </c>
       <c r="F2" t="n">
-        <v>1569885691673</v>
+        <v>1542423196515</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>29590585374</v>
+        <v>29910171593</v>
       </c>
       <c r="I2" t="n">
-        <v>79230</v>
+        <v>78382</v>
       </c>
       <c r="J2" t="n">
-        <v>77523</v>
+        <v>76298</v>
       </c>
       <c r="K2" t="n">
-        <v>-349.4784373934672</v>
+        <v>-1002.651589646965</v>
       </c>
       <c r="L2" t="n">
-        <v>0.35275</v>
+        <v>-1.25854</v>
       </c>
       <c r="M2" t="n">
-        <v>20078215</v>
+        <v>20078565</v>
       </c>
       <c r="N2" t="n">
-        <v>20078228</v>
+        <v>20078643</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-01T14:02:20.000Z</t>
+          <t>2026-09-02T13:27:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260901T140450Z-3c5d68</t>
+          <t>20260902T133046Z-54c889</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2446.09</v>
+        <v>2387.38</v>
       </c>
       <c r="F3" t="n">
-        <v>295448598447</v>
+        <v>291332644561</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>11585451732</v>
+        <v>13770939897</v>
       </c>
       <c r="I3" t="n">
-        <v>2488.52</v>
+        <v>2455.71</v>
       </c>
       <c r="J3" t="n">
-        <v>2432.33</v>
+        <v>2357.48</v>
       </c>
       <c r="K3" t="n">
-        <v>-21.12186156989719</v>
+        <v>-54.72458130220775</v>
       </c>
       <c r="L3" t="n">
-        <v>0.21914</v>
+        <v>-2.18948</v>
       </c>
       <c r="M3" t="n">
-        <v>120681092.8627613</v>
+        <v>122012212.9066439</v>
       </c>
       <c r="N3" t="n">
-        <v>120681092.8627613</v>
+        <v>122012212.9066439</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-01T14:02:20.000Z</t>
+          <t>2026-09-02T13:27:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260901T140450Z-3c5d68</t>
+          <t>20260902T133046Z-54c889</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,34 +655,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999742</v>
+        <v>0.99954</v>
       </c>
       <c r="F4" t="n">
-        <v>183331711830</v>
+        <v>183295436666</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>51085779871</v>
+        <v>52709975483</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999904</v>
+        <v>0.999814</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999649</v>
+        <v>0.999515</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.5755558932629e-05</v>
+        <v>-0.00020246591598283</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00165</v>
+        <v>-0.02004</v>
       </c>
       <c r="M4" t="n">
-        <v>183378837337.8042</v>
+        <v>183379537337.4499</v>
       </c>
       <c r="N4" t="n">
-        <v>188845783126.6962</v>
+        <v>188846483126.6962</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-01T14:02:20.000Z</t>
+          <t>2026-09-02T13:27:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260901T140450Z-3c5d68</t>
+          <t>20260902T133046Z-54c889</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>687.26</v>
+        <v>684.4400000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>91544389868</v>
+        <v>91139011046</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>640331713</v>
+        <v>845395094</v>
       </c>
       <c r="I5" t="n">
-        <v>694.22</v>
+        <v>689.16</v>
       </c>
       <c r="J5" t="n">
-        <v>683.9</v>
+        <v>674.95</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.095038509529559</v>
+        <v>-1.253657959365682</v>
       </c>
       <c r="L5" t="n">
-        <v>0.23543</v>
+        <v>-0.15838</v>
       </c>
       <c r="M5" t="n">
-        <v>133162327.83</v>
+        <v>133162268.3</v>
       </c>
       <c r="N5" t="n">
-        <v>133162323.52</v>
+        <v>133162263.84</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-01T14:02:20.000Z</t>
+          <t>2026-09-02T13:27:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260901T140450Z-3c5d68</t>
+          <t>20260902T133046Z-54c889</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="F6" t="n">
-        <v>86420625668</v>
+        <v>83222481160</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>1794248906</v>
+        <v>2416965587</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="J6" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.000543388090346264</v>
+        <v>-0.04130235788648329</v>
       </c>
       <c r="L6" t="n">
-        <v>0.95508</v>
+        <v>-2.96193</v>
       </c>
       <c r="M6" t="n">
         <v>62744504852</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-01T14:02:20.000Z</t>
+          <t>2026-09-02T13:27:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260901T140450Z-3c5d68</t>
+          <t>20260902T133046Z-54c889</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999858</v>
+        <v>0.999689</v>
       </c>
       <c r="F7" t="n">
-        <v>73409785688</v>
+        <v>73705657549</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>16352182564</v>
+        <v>14939027310</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0.999908</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999739</v>
+        <v>0.9996699999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>-6.06512515655e-07</v>
+        <v>-0.000171298470141301</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00243</v>
+        <v>-0.01822</v>
       </c>
       <c r="M7" t="n">
-        <v>73420075133.24463</v>
+        <v>73728533578.19063</v>
       </c>
       <c r="N7" t="n">
-        <v>73434446751.15912</v>
+        <v>73728533578.19063</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-01T14:02:20.000Z</t>
+          <t>2026-09-02T13:27:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260901T140450Z-3c5d68</t>
+          <t>20260902T133046Z-54c889</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102.06</v>
+        <v>98.3</v>
       </c>
       <c r="F8" t="n">
-        <v>59763125709</v>
+        <v>57534662152</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>3016918536</v>
+        <v>3305727041</v>
       </c>
       <c r="I8" t="n">
-        <v>104.9</v>
+        <v>102.49</v>
       </c>
       <c r="J8" t="n">
-        <v>101.41</v>
+        <v>97.38</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.457119237005728</v>
+        <v>-3.510154654535157</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.39595</v>
+        <v>-3.41387</v>
       </c>
       <c r="M8" t="n">
-        <v>585206839.8655083</v>
+        <v>585292366.3940911</v>
       </c>
       <c r="N8" t="n">
-        <v>633267250.9427586</v>
+        <v>633361734.0984335</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-01T14:02:20.000Z</t>
+          <t>2026-09-02T13:27:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260901T140450Z-3c5d68</t>
+          <t>20260902T133046Z-54c889</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.325939</v>
+        <v>0.323814</v>
       </c>
       <c r="F9" t="n">
-        <v>30938872609</v>
+        <v>30741447311</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>510459563</v>
+        <v>494988053</v>
       </c>
       <c r="I9" t="n">
-        <v>0.334031</v>
+        <v>0.326132</v>
       </c>
       <c r="J9" t="n">
-        <v>0.325524</v>
+        <v>0.321537</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.006813270380735537</v>
+        <v>-0.002477228054187097</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.8279</v>
+        <v>-0.76412</v>
       </c>
       <c r="M9" t="n">
-        <v>94930103918.07219</v>
+        <v>94931132310.40048</v>
       </c>
       <c r="N9" t="n">
-        <v>94930055362.23859</v>
+        <v>94931142533.51439</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-01T14:02:20.000Z</t>
+          <t>2026-09-02T13:27:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260901T140450Z-3c5d68</t>
+          <t>20260902T133046Z-54c889</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,31 +1045,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.013</v>
+        <v>1.034</v>
       </c>
       <c r="F10" t="n">
-        <v>22110471426</v>
+        <v>22767436715</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>861934919</v>
+        <v>42969692</v>
       </c>
       <c r="I10" t="n">
-        <v>1.056</v>
+        <v>1.047</v>
       </c>
       <c r="J10" t="n">
-        <v>1.002</v>
+        <v>1.008</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.02229735024079815</v>
+        <v>0.02095998</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.38341</v>
+        <v>2.06984</v>
       </c>
       <c r="M10" t="n">
-        <v>21833298808.828</v>
+        <v>22027381341.788</v>
       </c>
       <c r="N10" t="n">
         <v>22027381341.788</v>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-09-01T14:02:20.000Z</t>
+          <t>2026-09-02T13:27:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260901T140450Z-3c5d68</t>
+          <t>20260902T133046Z-54c889</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,28 +1110,28 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>83.84999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>18656551597</v>
+        <v>18106117386</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>1406474481</v>
+        <v>1268281707</v>
       </c>
       <c r="I11" t="n">
-        <v>85.29000000000001</v>
+        <v>84.37</v>
       </c>
       <c r="J11" t="n">
-        <v>81.3</v>
+        <v>80.3</v>
       </c>
       <c r="K11" t="n">
-        <v>2.34</v>
+        <v>-2.155817514329826</v>
       </c>
       <c r="L11" t="n">
-        <v>3.80259</v>
+        <v>-2.5226</v>
       </c>
       <c r="M11" t="n">
         <v>222445714.0741414</v>
@@ -1149,14 +1149,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-01T14:02:20.000Z</t>
+          <t>2026-09-02T13:27:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260901T140450Z-3c5d68</t>
+          <t>20260902T133046Z-54c889</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,34 +1175,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>855.98</v>
+        <v>802.27</v>
       </c>
       <c r="F12" t="n">
-        <v>14475675298</v>
+        <v>13553563424</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>573169713</v>
+        <v>524836360</v>
       </c>
       <c r="I12" t="n">
-        <v>870.96</v>
+        <v>862.03</v>
       </c>
       <c r="J12" t="n">
-        <v>830.96</v>
+        <v>788.6799999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>23.25</v>
+        <v>-44.89854163467476</v>
       </c>
       <c r="L12" t="n">
-        <v>4.06158</v>
+        <v>-5.3623</v>
       </c>
       <c r="M12" t="n">
         <v>16906800.1655448</v>
       </c>
       <c r="N12" t="n">
-        <v>16908772.0405448</v>
+        <v>16910500.1655448</v>
       </c>
       <c r="O12" t="n">
         <v>3191.93</v>
@@ -1214,14 +1214,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-01T14:02:20.000Z</t>
+          <t>2026-09-02T13:27:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260901T140450Z-3c5d68</t>
+          <t>20260902T133046Z-54c889</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.08286399999999999</v>
+        <v>0.08107200000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>12909260818</v>
+        <v>12623522800</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>488842761</v>
+        <v>562735508</v>
       </c>
       <c r="I13" t="n">
-        <v>0.083901</v>
+        <v>0.083062</v>
       </c>
       <c r="J13" t="n">
-        <v>0.08204</v>
+        <v>0.08021499999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.0001486738771551</v>
+        <v>-0.001407561754612638</v>
       </c>
       <c r="L13" t="n">
-        <v>0.79401</v>
+        <v>-1.72411</v>
       </c>
       <c r="M13" t="n">
-        <v>155735116383.7053</v>
+        <v>155747916383.7053</v>
       </c>
       <c r="N13" t="n">
-        <v>171447393126.579</v>
+        <v>155748796383.7052</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-01T14:02:20.000Z</t>
+          <t>2026-09-02T13:27:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260901T140450Z-3c5d68</t>
+          <t>20260902T133046Z-54c889</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,34 +1305,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.01660063</v>
+        <v>0.0168374</v>
       </c>
       <c r="F14" t="n">
-        <v>11769702829</v>
+        <v>11937506024</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>45627776</v>
+        <v>33283024</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01712303</v>
+        <v>0.01728967</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01655455</v>
+        <v>0.01631161</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.000497096489804342</v>
+        <v>0.00022473</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.45935</v>
+        <v>1.41486</v>
       </c>
       <c r="M14" t="n">
-        <v>709195842281.2939</v>
+        <v>709196850938.1379</v>
       </c>
       <c r="N14" t="n">
-        <v>1142408552901.351</v>
+        <v>1142408547588.968</v>
       </c>
       <c r="O14" t="n">
         <v>0.01946402</v>
@@ -1344,14 +1344,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-09-01T14:02:20.000Z</t>
+          <t>2026-09-02T13:27:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260901T140450Z-3c5d68</t>
+          <t>20260902T133046Z-54c889</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1370,34 +1370,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.999902</v>
+        <v>0.999704</v>
       </c>
       <c r="F15" t="n">
-        <v>9839715036</v>
+        <v>9820686416</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>180433082</v>
+        <v>148865188</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.999628</v>
+        <v>0.999567</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0001778</v>
+        <v>-0.000104980875193839</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02113</v>
+        <v>-0.01042</v>
       </c>
       <c r="M15" t="n">
-        <v>9840678940.050068</v>
+        <v>9823601338.161301</v>
       </c>
       <c r="N15" t="n">
-        <v>9845234620.789038</v>
+        <v>9826678345.257963</v>
       </c>
       <c r="O15" t="n">
         <v>1.057</v>
@@ -1409,14 +1409,14 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-09-01T14:02:20.000Z</t>
+          <t>2026-09-02T13:27:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260901T140450Z-3c5d68</t>
+          <t>20260902T133046Z-54c889</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1435,34 +1435,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>509.56</v>
+        <v>509.17</v>
       </c>
       <c r="F16" t="n">
-        <v>9568313100</v>
+        <v>9572002809</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>157669034</v>
+        <v>142139831</v>
       </c>
       <c r="I16" t="n">
-        <v>536.53</v>
+        <v>526.01</v>
       </c>
       <c r="J16" t="n">
-        <v>505.67</v>
+        <v>484.3</v>
       </c>
       <c r="K16" t="n">
-        <v>-3.443537903775677</v>
+        <v>-0.8381929943632258</v>
       </c>
       <c r="L16" t="n">
-        <v>0.29606</v>
+        <v>-0.05818</v>
       </c>
       <c r="M16" t="n">
-        <v>18798936.61165905</v>
+        <v>18799329.43167939</v>
       </c>
       <c r="N16" t="n">
-        <v>18798971.40256951</v>
+        <v>18799382.23144822</v>
       </c>
       <c r="O16" t="n">
         <v>797.73</v>
@@ -1474,14 +1474,14 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-09-01T14:02:20.000Z</t>
+          <t>2026-09-02T13:27:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260901T140450Z-3c5d68</t>
+          <t>20260902T133046Z-54c889</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1500,28 +1500,28 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>9.359999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="F17" t="n">
-        <v>8612750636</v>
+        <v>8507850686</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>416632</v>
+        <v>185868</v>
       </c>
       <c r="I17" t="n">
-        <v>9.66</v>
+        <v>9.43</v>
       </c>
       <c r="J17" t="n">
         <v>9.25</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.2771727449167827</v>
+        <v>-0.1220381871116487</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.87425</v>
+        <v>-1.2928</v>
       </c>
       <c r="M17" t="n">
         <v>919857851.9</v>
@@ -1539,144 +1539,144 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-09-01T14:02:20.000Z</t>
+          <t>2026-09-02T13:27:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260901T140450Z-3c5d68</t>
+          <t>20260902T133046Z-54c889</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>whitebit</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>wbt</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>WhiteBIT Coin</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>11.41</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>8544217729</v>
+        <v>8312643184</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>402987765</v>
+        <v>91363365</v>
       </c>
       <c r="I18" t="n">
-        <v>11.51</v>
+        <v>72.20999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>11.27</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>0.065885</v>
+        <v>-1.252096395542267</v>
       </c>
       <c r="L18" t="n">
-        <v>1.91985</v>
+        <v>-1.7306</v>
       </c>
       <c r="M18" t="n">
-        <v>748099970.424884</v>
+        <v>117956019</v>
       </c>
       <c r="N18" t="n">
-        <v>1000000000</v>
+        <v>293606018</v>
       </c>
       <c r="O18" t="n">
-        <v>52.7</v>
+        <v>74.97</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2021-05-09T16:13:57.000Z</t>
+          <t>2026-08-25T02:42:30.000Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-09-01T14:02:20.000Z</t>
+          <t>2026-09-02T13:27:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260901T140450Z-3c5d68</t>
+          <t>20260902T133046Z-54c889</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>whitebit</t>
+          <t>chainlink</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>wbt</t>
+          <t>link</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>WhiteBIT Coin</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>71.94</v>
+        <v>11.06</v>
       </c>
       <c r="F19" t="n">
-        <v>8493027190</v>
+        <v>8274697354</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>87122368</v>
+        <v>382377647</v>
       </c>
       <c r="I19" t="n">
-        <v>72.98</v>
+        <v>11.48</v>
       </c>
       <c r="J19" t="n">
-        <v>71.51000000000001</v>
+        <v>10.92</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.4012711885855538</v>
+        <v>-0.3246382705200261</v>
       </c>
       <c r="L19" t="n">
-        <v>0.21384</v>
+        <v>-2.79996</v>
       </c>
       <c r="M19" t="n">
-        <v>117956019</v>
+        <v>748099970.424884</v>
       </c>
       <c r="N19" t="n">
-        <v>293606018</v>
+        <v>1000000000</v>
       </c>
       <c r="O19" t="n">
-        <v>74.97</v>
+        <v>52.7</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-08-25T02:42:30.000Z</t>
+          <t>2021-05-09T16:13:57.000Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-09-01T14:02:20.000Z</t>
+          <t>2026-09-02T13:27:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260901T140450Z-3c5d68</t>
+          <t>20260902T133046Z-54c889</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1695,31 +1695,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.199351</v>
+        <v>0.194361</v>
       </c>
       <c r="F20" t="n">
-        <v>7481984559</v>
+        <v>7288205494</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>331914403</v>
+        <v>333445755</v>
       </c>
       <c r="I20" t="n">
-        <v>0.202834</v>
+        <v>0.200337</v>
       </c>
       <c r="J20" t="n">
-        <v>0.195018</v>
+        <v>0.192055</v>
       </c>
       <c r="K20" t="n">
-        <v>0.00258811</v>
+        <v>-0.003409470119800861</v>
       </c>
       <c r="L20" t="n">
-        <v>2.64758</v>
+        <v>-1.70406</v>
       </c>
       <c r="M20" t="n">
-        <v>37498597081.30407</v>
+        <v>37504333228.36598</v>
       </c>
       <c r="N20" t="n">
         <v>45000000000</v>
@@ -1734,14 +1734,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-09-01T14:02:20.000Z</t>
+          <t>2026-09-02T13:27:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260901T140450Z-3c5d68</t>
+          <t>20260902T133046Z-54c889</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1760,31 +1760,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.178056</v>
+        <v>0.172497</v>
       </c>
       <c r="F21" t="n">
-        <v>6183046555</v>
+        <v>5989392319</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>122590256</v>
+        <v>106318920</v>
       </c>
       <c r="I21" t="n">
-        <v>0.179955</v>
+        <v>0.17922</v>
       </c>
       <c r="J21" t="n">
-        <v>0.175005</v>
+        <v>0.171513</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0013073</v>
+        <v>-0.004773480670451191</v>
       </c>
       <c r="L21" t="n">
-        <v>1.81229</v>
+        <v>-2.65848</v>
       </c>
       <c r="M21" t="n">
-        <v>34694738330.92985</v>
+        <v>34699916993.46402</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.91247</v>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-09-01T14:02:20.000Z</t>
+          <t>2026-09-02T13:27:30.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260902T133046Z-54c889</t>
+          <t>20260903T132935Z-451690</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>76825</v>
+        <v>78482</v>
       </c>
       <c r="F2" t="n">
-        <v>1542423196515</v>
+        <v>1576127417399</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>29910171593</v>
+        <v>26111425070</v>
       </c>
       <c r="I2" t="n">
-        <v>78382</v>
+        <v>78725</v>
       </c>
       <c r="J2" t="n">
-        <v>76298</v>
+        <v>76733</v>
       </c>
       <c r="K2" t="n">
-        <v>-1002.651589646965</v>
+        <v>1644.46</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.25854</v>
+        <v>2.14017</v>
       </c>
       <c r="M2" t="n">
-        <v>20078565</v>
+        <v>20079031</v>
       </c>
       <c r="N2" t="n">
-        <v>20078643</v>
+        <v>20079084</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-02T13:27:30.000Z</t>
+          <t>2026-09-03T13:26:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260902T133046Z-54c889</t>
+          <t>20260903T132935Z-451690</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2387.38</v>
+        <v>2418.19</v>
       </c>
       <c r="F3" t="n">
-        <v>291332644561</v>
+        <v>295091157760</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>13770939897</v>
+        <v>11817258284</v>
       </c>
       <c r="I3" t="n">
-        <v>2455.71</v>
+        <v>2424.53</v>
       </c>
       <c r="J3" t="n">
-        <v>2357.48</v>
+        <v>2372.43</v>
       </c>
       <c r="K3" t="n">
-        <v>-54.72458130220775</v>
+        <v>30.89</v>
       </c>
       <c r="L3" t="n">
-        <v>-2.18948</v>
+        <v>1.29413</v>
       </c>
       <c r="M3" t="n">
-        <v>122012212.9066439</v>
+        <v>122015122.2602313</v>
       </c>
       <c r="N3" t="n">
-        <v>122012212.9066439</v>
+        <v>122015122.2602312</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-02T13:27:30.000Z</t>
+          <t>2026-09-03T13:26:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260902T133046Z-54c889</t>
+          <t>20260903T132935Z-451690</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,34 +655,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.99954</v>
+        <v>0.999798</v>
       </c>
       <c r="F4" t="n">
-        <v>183295436666</v>
+        <v>183341736575</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>52709975483</v>
+        <v>48438002016</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999814</v>
+        <v>0.999806</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999515</v>
+        <v>0.999401</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.00020246591598283</v>
+        <v>0.00025704</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.02004</v>
+        <v>0.02572</v>
       </c>
       <c r="M4" t="n">
-        <v>183379537337.4499</v>
+        <v>183384335764.3195</v>
       </c>
       <c r="N4" t="n">
-        <v>188846483126.6962</v>
+        <v>188851281632.5462</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-02T13:27:30.000Z</t>
+          <t>2026-09-03T13:26:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260902T133046Z-54c889</t>
+          <t>20260903T132935Z-451690</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>684.4400000000001</v>
+        <v>711.67</v>
       </c>
       <c r="F5" t="n">
-        <v>91139011046</v>
+        <v>94775703072</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>845395094</v>
+        <v>914551407</v>
       </c>
       <c r="I5" t="n">
-        <v>689.16</v>
+        <v>714.55</v>
       </c>
       <c r="J5" t="n">
-        <v>674.95</v>
+        <v>683.61</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.253657959365682</v>
+        <v>27.17</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.15838</v>
+        <v>3.96984</v>
       </c>
       <c r="M5" t="n">
-        <v>133162268.3</v>
+        <v>133162182.21</v>
       </c>
       <c r="N5" t="n">
-        <v>133162263.84</v>
+        <v>133162177.71</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-02T13:27:30.000Z</t>
+          <t>2026-09-03T13:26:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260902T133046Z-54c889</t>
+          <t>20260903T132935Z-451690</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="F6" t="n">
-        <v>83222481160</v>
+        <v>86979321495</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>2416965587</v>
+        <v>2565177895</v>
       </c>
       <c r="I6" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="J6" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.04130235788648329</v>
+        <v>0.05955</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.96193</v>
+        <v>4.49003</v>
       </c>
       <c r="M6" t="n">
         <v>62744504852</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-02T13:27:30.000Z</t>
+          <t>2026-09-03T13:26:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260902T133046Z-54c889</t>
+          <t>20260903T132935Z-451690</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999689</v>
+        <v>0.999985</v>
       </c>
       <c r="F7" t="n">
-        <v>73705657549</v>
+        <v>73628527440</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>14939027310</v>
+        <v>13510819449</v>
       </c>
       <c r="I7" t="n">
-        <v>0.999908</v>
+        <v>0.9998860000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9996699999999999</v>
+        <v>0.999625</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.000171298470141301</v>
+        <v>0.00030033</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.01822</v>
+        <v>0.03004</v>
       </c>
       <c r="M7" t="n">
-        <v>73728533578.19063</v>
+        <v>73631627030.26306</v>
       </c>
       <c r="N7" t="n">
-        <v>73728533578.19063</v>
+        <v>73652845901.84007</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-02T13:27:30.000Z</t>
+          <t>2026-09-03T13:26:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260902T133046Z-54c889</t>
+          <t>20260903T132935Z-451690</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>98.3</v>
+        <v>101.43</v>
       </c>
       <c r="F8" t="n">
-        <v>57534662152</v>
+        <v>59371186900</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>3305727041</v>
+        <v>3176671492</v>
       </c>
       <c r="I8" t="n">
-        <v>102.49</v>
+        <v>101.74</v>
       </c>
       <c r="J8" t="n">
-        <v>97.38</v>
+        <v>98.2</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.510154654535157</v>
+        <v>3.11</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.41387</v>
+        <v>3.16764</v>
       </c>
       <c r="M8" t="n">
-        <v>585292366.3940911</v>
+        <v>585274842.0808067</v>
       </c>
       <c r="N8" t="n">
-        <v>633361734.0984335</v>
+        <v>633360879.4456359</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-02T13:27:30.000Z</t>
+          <t>2026-09-03T13:26:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260902T133046Z-54c889</t>
+          <t>20260903T132935Z-451690</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.323814</v>
+        <v>0.328306</v>
       </c>
       <c r="F9" t="n">
-        <v>30741447311</v>
+        <v>31168114599</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>494988053</v>
+        <v>327951098</v>
       </c>
       <c r="I9" t="n">
-        <v>0.326132</v>
+        <v>0.328395</v>
       </c>
       <c r="J9" t="n">
-        <v>0.321537</v>
+        <v>0.323468</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.002477228054187097</v>
+        <v>0.00454957</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.76412</v>
+        <v>1.40524</v>
       </c>
       <c r="M9" t="n">
-        <v>94931132310.40048</v>
+        <v>94932446749.01399</v>
       </c>
       <c r="N9" t="n">
-        <v>94931142533.51439</v>
+        <v>94932447701.51509</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-02T13:27:30.000Z</t>
+          <t>2026-09-03T13:26:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260902T133046Z-54c889</t>
+          <t>20260903T132935Z-451690</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,34 +1045,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.034</v>
+        <v>1.013</v>
       </c>
       <c r="F10" t="n">
-        <v>22767436715</v>
+        <v>22408021554</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>42969692</v>
+        <v>66131014</v>
       </c>
       <c r="I10" t="n">
-        <v>1.047</v>
+        <v>1.045</v>
       </c>
       <c r="J10" t="n">
-        <v>1.008</v>
+        <v>1.011</v>
       </c>
       <c r="K10" t="n">
-        <v>0.02095998</v>
+        <v>-0.02087418389063145</v>
       </c>
       <c r="L10" t="n">
-        <v>2.06984</v>
+        <v>-2.01957</v>
       </c>
       <c r="M10" t="n">
-        <v>22027381341.788</v>
+        <v>22125837239.598</v>
       </c>
       <c r="N10" t="n">
-        <v>22027381341.788</v>
+        <v>22125837239.598</v>
       </c>
       <c r="O10" t="n">
         <v>1.061</v>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-09-02T13:27:30.000Z</t>
+          <t>2026-09-03T13:26:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260902T133046Z-54c889</t>
+          <t>20260903T132935Z-451690</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,28 +1110,28 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>81.40000000000001</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>18106117386</v>
+        <v>18361742402</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>1268281707</v>
+        <v>1153468984</v>
       </c>
       <c r="I11" t="n">
-        <v>84.37</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>80.3</v>
+        <v>80.56999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.155817514329826</v>
+        <v>1.12</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.5226</v>
+        <v>1.37936</v>
       </c>
       <c r="M11" t="n">
         <v>222445714.0741414</v>
@@ -1149,14 +1149,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-02T13:27:30.000Z</t>
+          <t>2026-09-03T13:26:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260902T133046Z-54c889</t>
+          <t>20260903T132935Z-451690</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,34 +1175,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>802.27</v>
+        <v>847.09</v>
       </c>
       <c r="F12" t="n">
-        <v>13553563424</v>
+        <v>14330696484</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>524836360</v>
+        <v>441257364</v>
       </c>
       <c r="I12" t="n">
-        <v>862.03</v>
+        <v>848.54</v>
       </c>
       <c r="J12" t="n">
-        <v>788.6799999999999</v>
+        <v>805.49</v>
       </c>
       <c r="K12" t="n">
-        <v>-44.89854163467476</v>
+        <v>45.04</v>
       </c>
       <c r="L12" t="n">
-        <v>-5.3623</v>
+        <v>5.61603</v>
       </c>
       <c r="M12" t="n">
-        <v>16906800.1655448</v>
+        <v>16912153.2905448</v>
       </c>
       <c r="N12" t="n">
-        <v>16910500.1655448</v>
+        <v>16912309.5405448</v>
       </c>
       <c r="O12" t="n">
         <v>3191.93</v>
@@ -1214,14 +1214,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-02T13:27:30.000Z</t>
+          <t>2026-09-03T13:26:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260902T133046Z-54c889</t>
+          <t>20260903T132935Z-451690</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.08107200000000001</v>
+        <v>0.083375</v>
       </c>
       <c r="F13" t="n">
-        <v>12623522800</v>
+        <v>12987540814</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>562735508</v>
+        <v>619880361</v>
       </c>
       <c r="I13" t="n">
-        <v>0.083062</v>
+        <v>0.08366800000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>0.08021499999999999</v>
+        <v>0.08078399999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.001407561754612638</v>
+        <v>0.00230837</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.72411</v>
+        <v>2.84751</v>
       </c>
       <c r="M13" t="n">
-        <v>155747916383.7053</v>
+        <v>155762576383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>155748796383.7052</v>
+        <v>155762596383.7051</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-02T13:27:30.000Z</t>
+          <t>2026-09-03T13:26:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260902T133046Z-54c889</t>
+          <t>20260903T132935Z-451690</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,34 +1305,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.0168374</v>
+        <v>0.01659025</v>
       </c>
       <c r="F14" t="n">
-        <v>11937506024</v>
+        <v>11766844169</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>33283024</v>
+        <v>36832212</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01728967</v>
+        <v>0.01686102</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01631161</v>
+        <v>0.01653375</v>
       </c>
       <c r="K14" t="n">
-        <v>0.00022473</v>
+        <v>-0.000244411633823719</v>
       </c>
       <c r="L14" t="n">
-        <v>1.41486</v>
+        <v>-1.45184</v>
       </c>
       <c r="M14" t="n">
-        <v>709196850938.1379</v>
+        <v>709197221825.1671</v>
       </c>
       <c r="N14" t="n">
-        <v>1142408547588.968</v>
+        <v>1142408547582.957</v>
       </c>
       <c r="O14" t="n">
         <v>0.01946402</v>
@@ -1344,14 +1344,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-09-02T13:27:30.000Z</t>
+          <t>2026-09-03T13:26:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260902T133046Z-54c889</t>
+          <t>20260903T132935Z-451690</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1370,34 +1370,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.999704</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>9820686416</v>
+        <v>9813297747</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>148865188</v>
+        <v>182199044</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.999567</v>
+        <v>0.999584</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.000104980875193839</v>
+        <v>0.00030711</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.01042</v>
+        <v>0.03072</v>
       </c>
       <c r="M15" t="n">
-        <v>9823601338.161301</v>
+        <v>9813476056.000912</v>
       </c>
       <c r="N15" t="n">
-        <v>9826678345.257963</v>
+        <v>9812556423.774925</v>
       </c>
       <c r="O15" t="n">
         <v>1.057</v>
@@ -1409,14 +1409,14 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-09-02T13:27:30.000Z</t>
+          <t>2026-09-03T13:26:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260902T133046Z-54c889</t>
+          <t>20260903T132935Z-451690</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1435,34 +1435,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>509.17</v>
+        <v>513.17</v>
       </c>
       <c r="F16" t="n">
-        <v>9572002809</v>
+        <v>9649702955</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>142139831</v>
+        <v>152552117</v>
       </c>
       <c r="I16" t="n">
-        <v>526.01</v>
+        <v>540.73</v>
       </c>
       <c r="J16" t="n">
-        <v>484.3</v>
+        <v>484.58</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.8381929943632258</v>
+        <v>3.91</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.05818</v>
+        <v>0.76874</v>
       </c>
       <c r="M16" t="n">
-        <v>18799329.43167939</v>
+        <v>18799765.02797851</v>
       </c>
       <c r="N16" t="n">
-        <v>18799382.23144822</v>
+        <v>18799804.62647666</v>
       </c>
       <c r="O16" t="n">
         <v>797.73</v>
@@ -1474,14 +1474,14 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-09-02T13:27:30.000Z</t>
+          <t>2026-09-03T13:26:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260902T133046Z-54c889</t>
+          <t>20260903T132935Z-451690</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1500,28 +1500,28 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>9.25</v>
+        <v>9.32</v>
       </c>
       <c r="F17" t="n">
-        <v>8507850686</v>
+        <v>8574375003</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>185868</v>
+        <v>313309</v>
       </c>
       <c r="I17" t="n">
-        <v>9.43</v>
+        <v>9.49</v>
       </c>
       <c r="J17" t="n">
-        <v>9.25</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.1220381871116487</v>
+        <v>0.072253</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.2928</v>
+        <v>0.7811900000000001</v>
       </c>
       <c r="M17" t="n">
         <v>919857851.9</v>
@@ -1539,144 +1539,144 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-09-02T13:27:30.000Z</t>
+          <t>2026-09-03T13:26:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260902T133046Z-54c889</t>
+          <t>20260903T132935Z-451690</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>whitebit</t>
+          <t>chainlink</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>wbt</t>
+          <t>link</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>WhiteBIT Coin</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>70.48999999999999</v>
+        <v>11.37</v>
       </c>
       <c r="F18" t="n">
-        <v>8312643184</v>
+        <v>8507227277</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>91363365</v>
+        <v>338595773</v>
       </c>
       <c r="I18" t="n">
-        <v>72.20999999999999</v>
+        <v>11.42</v>
       </c>
       <c r="J18" t="n">
-        <v>69.98999999999999</v>
+        <v>11.01</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.252096395542267</v>
+        <v>0.31122</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.7306</v>
+        <v>2.81426</v>
       </c>
       <c r="M18" t="n">
-        <v>117956019</v>
+        <v>748099970.424884</v>
       </c>
       <c r="N18" t="n">
-        <v>293606018</v>
+        <v>1000000000</v>
       </c>
       <c r="O18" t="n">
-        <v>74.97</v>
+        <v>52.7</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-08-25T02:42:30.000Z</t>
+          <t>2021-05-09T16:13:57.000Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-09-02T13:27:30.000Z</t>
+          <t>2026-09-03T13:26:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260902T133046Z-54c889</t>
+          <t>20260903T132935Z-451690</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>whitebit</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>wbt</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>WhiteBIT Coin</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>11.06</v>
+        <v>71.8</v>
       </c>
       <c r="F19" t="n">
-        <v>8274697354</v>
+        <v>8469768924</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>382377647</v>
+        <v>91974546</v>
       </c>
       <c r="I19" t="n">
-        <v>11.48</v>
+        <v>72.2</v>
       </c>
       <c r="J19" t="n">
-        <v>10.92</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.3246382705200261</v>
+        <v>1.3</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.79996</v>
+        <v>1.8422</v>
       </c>
       <c r="M19" t="n">
-        <v>748099970.424884</v>
+        <v>117956019</v>
       </c>
       <c r="N19" t="n">
-        <v>1000000000</v>
+        <v>293606018</v>
       </c>
       <c r="O19" t="n">
-        <v>52.7</v>
+        <v>74.97</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2021-05-09T16:13:57.000Z</t>
+          <t>2026-08-25T02:42:30.000Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-09-02T13:27:30.000Z</t>
+          <t>2026-09-03T13:26:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260902T133046Z-54c889</t>
+          <t>20260903T132935Z-451690</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1695,28 +1695,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.194361</v>
+        <v>0.209123</v>
       </c>
       <c r="F20" t="n">
-        <v>7288205494</v>
+        <v>7842758079</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>333445755</v>
+        <v>443747840</v>
       </c>
       <c r="I20" t="n">
-        <v>0.200337</v>
+        <v>0.209371</v>
       </c>
       <c r="J20" t="n">
-        <v>0.192055</v>
+        <v>0.194409</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.003409470119800861</v>
+        <v>0.01478594</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.70406</v>
+        <v>7.6084</v>
       </c>
       <c r="M20" t="n">
         <v>37504333228.36598</v>
@@ -1734,14 +1734,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-09-02T13:27:30.000Z</t>
+          <t>2026-09-03T13:26:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260902T133046Z-54c889</t>
+          <t>20260903T132935Z-451690</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1760,31 +1760,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.172497</v>
+        <v>0.178899</v>
       </c>
       <c r="F21" t="n">
-        <v>5989392319</v>
+        <v>6209997351</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>106318920</v>
+        <v>112055752</v>
       </c>
       <c r="I21" t="n">
-        <v>0.17922</v>
+        <v>0.179211</v>
       </c>
       <c r="J21" t="n">
-        <v>0.171513</v>
+        <v>0.172163</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.004773480670451191</v>
+        <v>0.0063597</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.65848</v>
+        <v>3.68593</v>
       </c>
       <c r="M21" t="n">
-        <v>34699916993.46402</v>
+        <v>34704715988.73615</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.91247</v>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-09-02T13:27:30.000Z</t>
+          <t>2026-09-03T13:26:30.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260903T132935Z-451690</t>
+          <t>20260904T132342Z-108cc5</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>78482</v>
+        <v>79359</v>
       </c>
       <c r="F2" t="n">
-        <v>1576127417399</v>
+        <v>1593163682686</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>26111425070</v>
+        <v>45522244662</v>
       </c>
       <c r="I2" t="n">
-        <v>78725</v>
+        <v>82108</v>
       </c>
       <c r="J2" t="n">
-        <v>76733</v>
+        <v>78730</v>
       </c>
       <c r="K2" t="n">
-        <v>1644.46</v>
+        <v>861.05</v>
       </c>
       <c r="L2" t="n">
-        <v>2.14017</v>
+        <v>1.09549</v>
       </c>
       <c r="M2" t="n">
-        <v>20079031</v>
+        <v>20079456</v>
       </c>
       <c r="N2" t="n">
-        <v>20079084</v>
+        <v>20079587</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-03T13:26:30.000Z</t>
+          <t>2026-09-04T13:20:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260903T132935Z-451690</t>
+          <t>20260904T132342Z-108cc5</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2418.19</v>
+        <v>2451.68</v>
       </c>
       <c r="F3" t="n">
-        <v>295091157760</v>
+        <v>299114785042</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>11817258284</v>
+        <v>20712588179</v>
       </c>
       <c r="I3" t="n">
-        <v>2424.53</v>
+        <v>2543.95</v>
       </c>
       <c r="J3" t="n">
-        <v>2372.43</v>
+        <v>2426.1</v>
       </c>
       <c r="K3" t="n">
-        <v>30.89</v>
+        <v>33.3</v>
       </c>
       <c r="L3" t="n">
-        <v>1.29413</v>
+        <v>1.3592</v>
       </c>
       <c r="M3" t="n">
-        <v>122015122.2602313</v>
+        <v>122018029.5481636</v>
       </c>
       <c r="N3" t="n">
-        <v>122015122.2602312</v>
+        <v>122018029.5481636</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-03T13:26:30.000Z</t>
+          <t>2026-09-04T13:20:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260903T132935Z-451690</t>
+          <t>20260904T132342Z-108cc5</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,34 +655,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999798</v>
+        <v>0.999968</v>
       </c>
       <c r="F4" t="n">
-        <v>183341736575</v>
+        <v>183374342961</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>48438002016</v>
+        <v>81047342194</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999806</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999401</v>
+        <v>0.999741</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00025704</v>
+        <v>0.00022336</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02572</v>
+        <v>0.02096</v>
       </c>
       <c r="M4" t="n">
-        <v>183384335764.3195</v>
+        <v>183380584914.2666</v>
       </c>
       <c r="N4" t="n">
-        <v>188851281632.5462</v>
+        <v>188847530724.5562</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-03T13:26:30.000Z</t>
+          <t>2026-09-04T13:20:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260903T132935Z-451690</t>
+          <t>20260904T132342Z-108cc5</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>711.67</v>
+        <v>715.78</v>
       </c>
       <c r="F5" t="n">
-        <v>94775703072</v>
+        <v>95301515751</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>914551407</v>
+        <v>1230869124</v>
       </c>
       <c r="I5" t="n">
-        <v>714.55</v>
+        <v>729.04</v>
       </c>
       <c r="J5" t="n">
-        <v>683.61</v>
+        <v>711.2</v>
       </c>
       <c r="K5" t="n">
-        <v>27.17</v>
+        <v>3.75</v>
       </c>
       <c r="L5" t="n">
-        <v>3.96984</v>
+        <v>0.5324</v>
       </c>
       <c r="M5" t="n">
-        <v>133162182.21</v>
+        <v>133162092.19</v>
       </c>
       <c r="N5" t="n">
-        <v>133162177.71</v>
+        <v>133162083.78</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-03T13:26:30.000Z</t>
+          <t>2026-09-04T13:20:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260903T132935Z-451690</t>
+          <t>20260904T132342Z-108cc5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="F6" t="n">
-        <v>86979321495</v>
+        <v>88478547018</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>2565177895</v>
+        <v>4425155361</v>
       </c>
       <c r="I6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="J6" t="n">
         <v>1.39</v>
       </c>
-      <c r="J6" t="n">
-        <v>1.33</v>
-      </c>
       <c r="K6" t="n">
-        <v>0.05955</v>
+        <v>0.01888811</v>
       </c>
       <c r="L6" t="n">
-        <v>4.49003</v>
+        <v>1.41438</v>
       </c>
       <c r="M6" t="n">
         <v>62744504852</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-03T13:26:30.000Z</t>
+          <t>2026-09-04T13:20:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260903T132935Z-451690</t>
+          <t>20260904T132342Z-108cc5</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999985</v>
+        <v>0.999919</v>
       </c>
       <c r="F7" t="n">
-        <v>73628527440</v>
+        <v>74211857091</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>13510819449</v>
+        <v>22705930478</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9998860000000001</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999625</v>
+        <v>0.999813</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00030033</v>
+        <v>-2.8590609912227e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03004</v>
+        <v>-0.00457</v>
       </c>
       <c r="M7" t="n">
-        <v>73631627030.26306</v>
+        <v>74218059764.11169</v>
       </c>
       <c r="N7" t="n">
-        <v>73652845901.84007</v>
+        <v>74217369421.13387</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-03T13:26:30.000Z</t>
+          <t>2026-09-04T13:20:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260903T132935Z-451690</t>
+          <t>20260904T132342Z-108cc5</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101.43</v>
+        <v>101.47</v>
       </c>
       <c r="F8" t="n">
-        <v>59371186900</v>
+        <v>59379954644</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>3176671492</v>
+        <v>4533394665</v>
       </c>
       <c r="I8" t="n">
-        <v>101.74</v>
+        <v>105.61</v>
       </c>
       <c r="J8" t="n">
-        <v>98.2</v>
+        <v>100.76</v>
       </c>
       <c r="K8" t="n">
-        <v>3.11</v>
+        <v>-0.02710679754788714</v>
       </c>
       <c r="L8" t="n">
-        <v>3.16764</v>
+        <v>-0.01819</v>
       </c>
       <c r="M8" t="n">
-        <v>585274842.0808067</v>
+        <v>585360321.7759155</v>
       </c>
       <c r="N8" t="n">
-        <v>633360879.4456359</v>
+        <v>633455345.7040083</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-03T13:26:30.000Z</t>
+          <t>2026-09-04T13:20:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260903T132935Z-451690</t>
+          <t>20260904T132342Z-108cc5</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.328306</v>
+        <v>0.329213</v>
       </c>
       <c r="F9" t="n">
-        <v>31168114599</v>
+        <v>31247823690</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>327951098</v>
+        <v>468576739</v>
       </c>
       <c r="I9" t="n">
-        <v>0.328395</v>
+        <v>0.332098</v>
       </c>
       <c r="J9" t="n">
-        <v>0.323468</v>
+        <v>0.327679</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00454957</v>
+        <v>0.00100057</v>
       </c>
       <c r="L9" t="n">
-        <v>1.40524</v>
+        <v>0.31056</v>
       </c>
       <c r="M9" t="n">
-        <v>94932446749.01399</v>
+        <v>94933766962.63728</v>
       </c>
       <c r="N9" t="n">
-        <v>94932447701.51509</v>
+        <v>94933768457.70969</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-03T13:26:30.000Z</t>
+          <t>2026-09-04T13:20:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260903T132935Z-451690</t>
+          <t>20260904T132342Z-108cc5</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,34 +1045,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.013</v>
+        <v>1.032</v>
       </c>
       <c r="F10" t="n">
-        <v>22408021554</v>
+        <v>22912232176</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>66131014</v>
+        <v>353723962</v>
       </c>
       <c r="I10" t="n">
-        <v>1.045</v>
+        <v>1.036</v>
       </c>
       <c r="J10" t="n">
-        <v>1.011</v>
+        <v>1.008</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.02087418389063145</v>
+        <v>0.01955</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.01957</v>
+        <v>1.93174</v>
       </c>
       <c r="M10" t="n">
-        <v>22125837239.598</v>
+        <v>22194607152.968</v>
       </c>
       <c r="N10" t="n">
-        <v>22125837239.598</v>
+        <v>22194607152.968</v>
       </c>
       <c r="O10" t="n">
         <v>1.061</v>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-09-03T13:26:30.000Z</t>
+          <t>2026-09-04T13:20:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260903T132935Z-451690</t>
+          <t>20260904T132342Z-108cc5</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,28 +1110,28 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>82.54000000000001</v>
+        <v>85.31999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>18361742402</v>
+        <v>18971512459</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>1153468984</v>
+        <v>1617303734</v>
       </c>
       <c r="I11" t="n">
-        <v>82.76000000000001</v>
+        <v>88.06</v>
       </c>
       <c r="J11" t="n">
-        <v>80.56999999999999</v>
+        <v>82.73999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>1.12</v>
+        <v>2.76</v>
       </c>
       <c r="L11" t="n">
-        <v>1.37936</v>
+        <v>3.36738</v>
       </c>
       <c r="M11" t="n">
         <v>222445714.0741414</v>
@@ -1140,23 +1140,23 @@
         <v>955307079.4341414</v>
       </c>
       <c r="O11" t="n">
-        <v>86.70999999999999</v>
+        <v>88.06</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-08-27T19:18:00.000Z</t>
+          <t>2026-09-03T23:46:20.000Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-03T13:26:30.000Z</t>
+          <t>2026-09-04T13:20:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260903T132935Z-451690</t>
+          <t>20260904T132342Z-108cc5</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,34 +1175,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>847.09</v>
+        <v>976.79</v>
       </c>
       <c r="F12" t="n">
-        <v>14330696484</v>
+        <v>16512298003</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>441257364</v>
+        <v>1326160924</v>
       </c>
       <c r="I12" t="n">
-        <v>848.54</v>
+        <v>1023.4</v>
       </c>
       <c r="J12" t="n">
-        <v>805.49</v>
+        <v>855.09</v>
       </c>
       <c r="K12" t="n">
-        <v>45.04</v>
+        <v>129.51</v>
       </c>
       <c r="L12" t="n">
-        <v>5.61603</v>
+        <v>15.38889</v>
       </c>
       <c r="M12" t="n">
         <v>16912153.2905448</v>
       </c>
       <c r="N12" t="n">
-        <v>16912309.5405448</v>
+        <v>16914089.2280448</v>
       </c>
       <c r="O12" t="n">
         <v>3191.93</v>
@@ -1214,14 +1214,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-03T13:26:30.000Z</t>
+          <t>2026-09-04T13:20:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260903T132935Z-451690</t>
+          <t>20260904T132342Z-108cc5</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.083375</v>
+        <v>0.085092</v>
       </c>
       <c r="F13" t="n">
-        <v>12987540814</v>
+        <v>13251461834</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>619880361</v>
+        <v>1225658758</v>
       </c>
       <c r="I13" t="n">
-        <v>0.08366800000000001</v>
+        <v>0.08987000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>0.08078399999999999</v>
+        <v>0.08334800000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>0.00230837</v>
+        <v>0.00162881</v>
       </c>
       <c r="L13" t="n">
-        <v>2.84751</v>
+        <v>1.97942</v>
       </c>
       <c r="M13" t="n">
-        <v>155762576383.7052</v>
+        <v>155774816383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>155762596383.7051</v>
+        <v>155776086383.7052</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-03T13:26:30.000Z</t>
+          <t>2026-09-04T13:20:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260903T132935Z-451690</t>
+          <t>20260904T132342Z-108cc5</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,34 +1305,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.01659025</v>
+        <v>0.01663205</v>
       </c>
       <c r="F14" t="n">
-        <v>11766844169</v>
+        <v>11797364850</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>36832212</v>
+        <v>42602475</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01686102</v>
+        <v>0.01718139</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01653375</v>
+        <v>0.0165917</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.000244411633823719</v>
+        <v>5.362e-05</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.45184</v>
+        <v>0.27174</v>
       </c>
       <c r="M14" t="n">
-        <v>709197221825.1671</v>
+        <v>709200329550.1813</v>
       </c>
       <c r="N14" t="n">
-        <v>1142408547582.957</v>
+        <v>1142408546819.001</v>
       </c>
       <c r="O14" t="n">
         <v>0.01946402</v>
@@ -1344,339 +1344,339 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-09-03T13:26:30.000Z</t>
+          <t>2026-09-04T13:20:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260903T132935Z-451690</t>
+          <t>20260904T132342Z-108cc5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>monero</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>xmr</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>USDS</t>
+          <t>Monero</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>527.37</v>
       </c>
       <c r="F15" t="n">
-        <v>9813297747</v>
+        <v>9912069668</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>182199044</v>
+        <v>209126501</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>565.05</v>
       </c>
       <c r="J15" t="n">
-        <v>0.999584</v>
+        <v>499.99</v>
       </c>
       <c r="K15" t="n">
-        <v>0.00030711</v>
+        <v>14.72</v>
       </c>
       <c r="L15" t="n">
-        <v>0.03072</v>
+        <v>3.04267</v>
       </c>
       <c r="M15" t="n">
-        <v>9813476056.000912</v>
+        <v>18800177.20512704</v>
       </c>
       <c r="N15" t="n">
-        <v>9812556423.774925</v>
+        <v>18800212.60457258</v>
       </c>
       <c r="O15" t="n">
-        <v>1.057</v>
+        <v>797.73</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2024-10-28T21:40:51.000Z</t>
+          <t>2026-01-14T11:34:07.000Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-09-03T13:26:30.000Z</t>
+          <t>2026-09-04T13:20:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260903T132935Z-451690</t>
+          <t>20260904T132342Z-108cc5</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>monero</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>xmr</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Monero</t>
+          <t>USDS</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>513.17</v>
+        <v>0.99992</v>
       </c>
       <c r="F16" t="n">
-        <v>9649702955</v>
+        <v>9788041911</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>152552117</v>
+        <v>178743055</v>
       </c>
       <c r="I16" t="n">
-        <v>540.73</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>484.58</v>
+        <v>0.999699</v>
       </c>
       <c r="K16" t="n">
-        <v>3.91</v>
+        <v>-3.4802293604974e-05</v>
       </c>
       <c r="L16" t="n">
-        <v>0.76874</v>
+        <v>-0.00502</v>
       </c>
       <c r="M16" t="n">
-        <v>18799765.02797851</v>
+        <v>9788862059.147768</v>
       </c>
       <c r="N16" t="n">
-        <v>18799804.62647666</v>
+        <v>9788244960.351456</v>
       </c>
       <c r="O16" t="n">
-        <v>797.73</v>
+        <v>1.057</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-01-14T11:34:07.000Z</t>
+          <t>2024-10-28T21:40:51.000Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-09-03T13:26:30.000Z</t>
+          <t>2026-09-04T13:20:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260903T132935Z-451690</t>
+          <t>20260904T132342Z-108cc5</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>leo-token</t>
+          <t>chainlink</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>leo</t>
+          <t>link</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LEO Token</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>9.32</v>
+        <v>11.62</v>
       </c>
       <c r="F17" t="n">
-        <v>8574375003</v>
+        <v>8688399026</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>313309</v>
+        <v>543808477</v>
       </c>
       <c r="I17" t="n">
-        <v>9.49</v>
+        <v>12.15</v>
       </c>
       <c r="J17" t="n">
-        <v>9.210000000000001</v>
+        <v>11.4</v>
       </c>
       <c r="K17" t="n">
-        <v>0.072253</v>
+        <v>0.232654</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7811900000000001</v>
+        <v>2.11083</v>
       </c>
       <c r="M17" t="n">
-        <v>919857851.9</v>
+        <v>748099970.424884</v>
       </c>
       <c r="N17" t="n">
-        <v>985239504</v>
+        <v>1000000000</v>
       </c>
       <c r="O17" t="n">
-        <v>10.61</v>
+        <v>52.7</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-05-04T09:35:00.000Z</t>
+          <t>2021-05-09T16:13:57.000Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-09-03T13:26:30.000Z</t>
+          <t>2026-09-04T13:20:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260903T132935Z-451690</t>
+          <t>20260904T132342Z-108cc5</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>whitebit</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>wbt</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>WhiteBIT Coin</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>11.37</v>
+        <v>72.98</v>
       </c>
       <c r="F18" t="n">
-        <v>8507227277</v>
+        <v>8606781427</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>338595773</v>
+        <v>139278540</v>
       </c>
       <c r="I18" t="n">
-        <v>11.42</v>
+        <v>74.91</v>
       </c>
       <c r="J18" t="n">
-        <v>11.01</v>
+        <v>71.98</v>
       </c>
       <c r="K18" t="n">
-        <v>0.31122</v>
+        <v>1.17</v>
       </c>
       <c r="L18" t="n">
-        <v>2.81426</v>
+        <v>1.59778</v>
       </c>
       <c r="M18" t="n">
-        <v>748099970.424884</v>
+        <v>117956019</v>
       </c>
       <c r="N18" t="n">
-        <v>1000000000</v>
+        <v>293606018</v>
       </c>
       <c r="O18" t="n">
-        <v>52.7</v>
+        <v>74.97</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2021-05-09T16:13:57.000Z</t>
+          <t>2026-08-25T02:42:30.000Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-09-03T13:26:30.000Z</t>
+          <t>2026-09-04T13:20:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260903T132935Z-451690</t>
+          <t>20260904T132342Z-108cc5</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>whitebit</t>
+          <t>leo-token</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>wbt</t>
+          <t>leo</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>WhiteBIT Coin</t>
+          <t>LEO Token</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>71.8</v>
+        <v>9.23</v>
       </c>
       <c r="F19" t="n">
-        <v>8469768924</v>
+        <v>8492336269</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>91974546</v>
+        <v>158502</v>
       </c>
       <c r="I19" t="n">
-        <v>72.2</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>70.43000000000001</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>1.3</v>
+        <v>-0.06892478826383019</v>
       </c>
       <c r="L19" t="n">
-        <v>1.8422</v>
+        <v>-0.7431</v>
       </c>
       <c r="M19" t="n">
-        <v>117956019</v>
+        <v>919857851.9</v>
       </c>
       <c r="N19" t="n">
-        <v>293606018</v>
+        <v>985239504</v>
       </c>
       <c r="O19" t="n">
-        <v>74.97</v>
+        <v>10.61</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-08-25T02:42:30.000Z</t>
+          <t>2026-05-04T09:35:00.000Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-09-03T13:26:30.000Z</t>
+          <t>2026-09-04T13:20:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260903T132935Z-451690</t>
+          <t>20260904T132342Z-108cc5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1695,28 +1695,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.209123</v>
+        <v>0.214565</v>
       </c>
       <c r="F20" t="n">
-        <v>7842758079</v>
+        <v>8043119372</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>443747840</v>
+        <v>761119607</v>
       </c>
       <c r="I20" t="n">
-        <v>0.209371</v>
+        <v>0.226776</v>
       </c>
       <c r="J20" t="n">
-        <v>0.194409</v>
+        <v>0.209667</v>
       </c>
       <c r="K20" t="n">
-        <v>0.01478594</v>
+        <v>0.00541804</v>
       </c>
       <c r="L20" t="n">
-        <v>7.6084</v>
+        <v>2.63109</v>
       </c>
       <c r="M20" t="n">
         <v>37504333228.36598</v>
@@ -1734,14 +1734,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-09-03T13:26:30.000Z</t>
+          <t>2026-09-04T13:20:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260903T132935Z-451690</t>
+          <t>20260904T132342Z-108cc5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1760,31 +1760,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.178899</v>
+        <v>0.180543</v>
       </c>
       <c r="F21" t="n">
-        <v>6209997351</v>
+        <v>6263102886</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>112055752</v>
+        <v>175302475</v>
       </c>
       <c r="I21" t="n">
-        <v>0.179211</v>
+        <v>0.188001</v>
       </c>
       <c r="J21" t="n">
-        <v>0.172163</v>
+        <v>0.179006</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0063597</v>
+        <v>0.00140816</v>
       </c>
       <c r="L21" t="n">
-        <v>3.68593</v>
+        <v>0.79822</v>
       </c>
       <c r="M21" t="n">
-        <v>34704715988.73615</v>
+        <v>34718653715.55763</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.91247</v>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-09-03T13:26:30.000Z</t>
+          <t>2026-09-04T13:20:30.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260904T132342Z-108cc5</t>
+          <t>20260905T123308Z-b8d665</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>79359</v>
+        <v>79627</v>
       </c>
       <c r="F2" t="n">
-        <v>1593163682686</v>
+        <v>1599559585726</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>45522244662</v>
+        <v>26745226109</v>
       </c>
       <c r="I2" t="n">
-        <v>82108</v>
+        <v>79848</v>
       </c>
       <c r="J2" t="n">
-        <v>78730</v>
+        <v>78706</v>
       </c>
       <c r="K2" t="n">
-        <v>861.05</v>
+        <v>-494.7438492716319</v>
       </c>
       <c r="L2" t="n">
-        <v>1.09549</v>
+        <v>-0.34503</v>
       </c>
       <c r="M2" t="n">
-        <v>20079456</v>
+        <v>20079921</v>
       </c>
       <c r="N2" t="n">
-        <v>20079587</v>
+        <v>20079981</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-04T13:20:30.000Z</t>
+          <t>2026-09-05T12:30:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260904T132342Z-108cc5</t>
+          <t>20260905T123308Z-b8d665</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2451.68</v>
+        <v>2454.03</v>
       </c>
       <c r="F3" t="n">
-        <v>299114785042</v>
+        <v>299538882721</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>20712588179</v>
+        <v>10563398954</v>
       </c>
       <c r="I3" t="n">
-        <v>2543.95</v>
+        <v>2463.12</v>
       </c>
       <c r="J3" t="n">
-        <v>2426.1</v>
+        <v>2435.15</v>
       </c>
       <c r="K3" t="n">
-        <v>33.3</v>
+        <v>-15.95687009235553</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3592</v>
+        <v>-0.03568</v>
       </c>
       <c r="M3" t="n">
-        <v>122018029.5481636</v>
+        <v>122020932.8534729</v>
       </c>
       <c r="N3" t="n">
-        <v>122018029.5481636</v>
+        <v>122020932.8534728</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-04T13:20:30.000Z</t>
+          <t>2026-09-05T12:30:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260904T132342Z-108cc5</t>
+          <t>20260905T123308Z-b8d665</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,34 +655,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999968</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>183374342961</v>
+        <v>183411232653</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>81047342194</v>
+        <v>51368333618</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999741</v>
+        <v>0.999868</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00022336</v>
+        <v>9.855e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02096</v>
+        <v>0.00524</v>
       </c>
       <c r="M4" t="n">
-        <v>183380584914.2666</v>
+        <v>183392383062.0927</v>
       </c>
       <c r="N4" t="n">
-        <v>188847530724.5562</v>
+        <v>188859328873.3562</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-04T13:20:30.000Z</t>
+          <t>2026-09-05T12:30:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260904T132342Z-108cc5</t>
+          <t>20260905T123308Z-b8d665</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>715.78</v>
+        <v>754.75</v>
       </c>
       <c r="F5" t="n">
-        <v>95301515751</v>
+        <v>100669627319</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1230869124</v>
+        <v>1539825166</v>
       </c>
       <c r="I5" t="n">
-        <v>729.04</v>
+        <v>755.23</v>
       </c>
       <c r="J5" t="n">
-        <v>711.2</v>
+        <v>709.29</v>
       </c>
       <c r="K5" t="n">
-        <v>3.75</v>
+        <v>37.26</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5324</v>
+        <v>5.44966</v>
       </c>
       <c r="M5" t="n">
-        <v>133162092.19</v>
+        <v>133161986.43</v>
       </c>
       <c r="N5" t="n">
-        <v>133162083.78</v>
+        <v>133161979.25</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-04T13:20:30.000Z</t>
+          <t>2026-09-05T12:30:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260904T132342Z-108cc5</t>
+          <t>20260905T123308Z-b8d665</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="F6" t="n">
-        <v>88478547018</v>
+        <v>88145207092</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>4425155361</v>
+        <v>2053892311</v>
       </c>
       <c r="I6" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="J6" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01888811</v>
+        <v>-0.01074625837040433</v>
       </c>
       <c r="L6" t="n">
-        <v>1.41438</v>
+        <v>-0.2599</v>
       </c>
       <c r="M6" t="n">
         <v>62744504852</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-04T13:20:30.000Z</t>
+          <t>2026-09-05T12:30:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260904T132342Z-108cc5</t>
+          <t>20260905T123308Z-b8d665</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999919</v>
+        <v>0.999995</v>
       </c>
       <c r="F7" t="n">
-        <v>74211857091</v>
+        <v>74603986980</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>22705930478</v>
+        <v>13560913142</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999813</v>
+        <v>0.9997740000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.8590609912227e-05</v>
+        <v>-4.42967446945e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.00457</v>
+        <v>-0.00246</v>
       </c>
       <c r="M7" t="n">
-        <v>74218059764.11169</v>
+        <v>74602236473.1615</v>
       </c>
       <c r="N7" t="n">
-        <v>74217369421.13387</v>
+        <v>74604014988.58582</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-04T13:20:30.000Z</t>
+          <t>2026-09-05T12:30:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260904T132342Z-108cc5</t>
+          <t>20260905T123308Z-b8d665</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101.47</v>
+        <v>102.33</v>
       </c>
       <c r="F8" t="n">
-        <v>59379954644</v>
+        <v>59935721064</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>4533394665</v>
+        <v>2605188432</v>
       </c>
       <c r="I8" t="n">
-        <v>105.61</v>
+        <v>102.79</v>
       </c>
       <c r="J8" t="n">
-        <v>100.76</v>
+        <v>100.4</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.02710679754788714</v>
+        <v>0.760165</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.01819</v>
+        <v>1.11121</v>
       </c>
       <c r="M8" t="n">
-        <v>585360321.7759155</v>
+        <v>585359561.7917758</v>
       </c>
       <c r="N8" t="n">
-        <v>633455345.7040083</v>
+        <v>633454599.1689531</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-04T13:20:30.000Z</t>
+          <t>2026-09-05T12:30:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260904T132342Z-108cc5</t>
+          <t>20260905T123308Z-b8d665</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.329213</v>
+        <v>0.332812</v>
       </c>
       <c r="F9" t="n">
-        <v>31247823690</v>
+        <v>31594137028</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>468576739</v>
+        <v>311107005</v>
       </c>
       <c r="I9" t="n">
-        <v>0.332098</v>
+        <v>0.333228</v>
       </c>
       <c r="J9" t="n">
-        <v>0.327679</v>
+        <v>0.328453</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00100057</v>
+        <v>0.00402935</v>
       </c>
       <c r="L9" t="n">
-        <v>0.31056</v>
+        <v>1.27509</v>
       </c>
       <c r="M9" t="n">
-        <v>94933766962.63728</v>
+        <v>94933696444.65239</v>
       </c>
       <c r="N9" t="n">
-        <v>94933768457.70969</v>
+        <v>94935403392.50798</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-04T13:20:30.000Z</t>
+          <t>2026-09-05T12:30:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260904T132342Z-108cc5</t>
+          <t>20260905T123308Z-b8d665</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,34 +1045,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.032</v>
+        <v>1.039</v>
       </c>
       <c r="F10" t="n">
-        <v>22912232176</v>
+        <v>23111985829</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>353723962</v>
+        <v>23229332</v>
       </c>
       <c r="I10" t="n">
-        <v>1.036</v>
+        <v>1.041</v>
       </c>
       <c r="J10" t="n">
-        <v>1.008</v>
+        <v>1.03</v>
       </c>
       <c r="K10" t="n">
-        <v>0.01955</v>
+        <v>0.00627504</v>
       </c>
       <c r="L10" t="n">
-        <v>1.93174</v>
+        <v>0.61245</v>
       </c>
       <c r="M10" t="n">
-        <v>22194607152.968</v>
+        <v>22254918397.228</v>
       </c>
       <c r="N10" t="n">
-        <v>22194607152.968</v>
+        <v>22254918397.228</v>
       </c>
       <c r="O10" t="n">
         <v>1.061</v>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-09-04T13:20:30.000Z</t>
+          <t>2026-09-05T12:30:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260904T132342Z-108cc5</t>
+          <t>20260905T123308Z-b8d665</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,28 +1110,28 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>85.31999999999999</v>
+        <v>84.98999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>18971512459</v>
+        <v>18927342709</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>1617303734</v>
+        <v>1038012646</v>
       </c>
       <c r="I11" t="n">
-        <v>88.06</v>
+        <v>85.75</v>
       </c>
       <c r="J11" t="n">
-        <v>82.73999999999999</v>
+        <v>83.64</v>
       </c>
       <c r="K11" t="n">
-        <v>2.76</v>
+        <v>-0.9863609708923349</v>
       </c>
       <c r="L11" t="n">
-        <v>3.36738</v>
+        <v>-0.54309</v>
       </c>
       <c r="M11" t="n">
         <v>222445714.0741414</v>
@@ -1149,14 +1149,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-04T13:20:30.000Z</t>
+          <t>2026-09-05T12:30:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260904T132342Z-108cc5</t>
+          <t>20260905T123308Z-b8d665</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,34 +1175,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>976.79</v>
+        <v>1008.51</v>
       </c>
       <c r="F12" t="n">
-        <v>16512298003</v>
+        <v>17074273476</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>1326160924</v>
+        <v>1074051251</v>
       </c>
       <c r="I12" t="n">
-        <v>1023.4</v>
+        <v>1046.3</v>
       </c>
       <c r="J12" t="n">
-        <v>855.09</v>
+        <v>966.84</v>
       </c>
       <c r="K12" t="n">
-        <v>129.51</v>
+        <v>24.98</v>
       </c>
       <c r="L12" t="n">
-        <v>15.38889</v>
+        <v>2.85001</v>
       </c>
       <c r="M12" t="n">
         <v>16912153.2905448</v>
       </c>
       <c r="N12" t="n">
-        <v>16914089.2280448</v>
+        <v>16915817.3530448</v>
       </c>
       <c r="O12" t="n">
         <v>3191.93</v>
@@ -1214,14 +1214,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-04T13:20:30.000Z</t>
+          <t>2026-09-05T12:30:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260904T132342Z-108cc5</t>
+          <t>20260905T123308Z-b8d665</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.085092</v>
+        <v>0.086243</v>
       </c>
       <c r="F13" t="n">
-        <v>13251461834</v>
+        <v>13452940677</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>1225658758</v>
+        <v>726461375</v>
       </c>
       <c r="I13" t="n">
-        <v>0.08987000000000001</v>
+        <v>0.086267</v>
       </c>
       <c r="J13" t="n">
-        <v>0.08334800000000001</v>
+        <v>0.083882</v>
       </c>
       <c r="K13" t="n">
-        <v>0.00162881</v>
+        <v>0.00059221</v>
       </c>
       <c r="L13" t="n">
-        <v>1.97942</v>
+        <v>1.36679</v>
       </c>
       <c r="M13" t="n">
-        <v>155774816383.7052</v>
+        <v>155789276383.7053</v>
       </c>
       <c r="N13" t="n">
-        <v>155776086383.7052</v>
+        <v>171501463126.579</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-04T13:20:30.000Z</t>
+          <t>2026-09-05T12:30:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260904T132342Z-108cc5</t>
+          <t>20260905T123308Z-b8d665</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,34 +1305,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.01663205</v>
+        <v>0.01640475</v>
       </c>
       <c r="F14" t="n">
-        <v>11797364850</v>
+        <v>11637183792</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>42602475</v>
+        <v>43201814</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01718139</v>
+        <v>0.01664376</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0165917</v>
+        <v>0.01638085</v>
       </c>
       <c r="K14" t="n">
-        <v>5.362e-05</v>
+        <v>-0.000372463176358119</v>
       </c>
       <c r="L14" t="n">
-        <v>0.27174</v>
+        <v>-1.7997</v>
       </c>
       <c r="M14" t="n">
-        <v>709200329550.1813</v>
+        <v>709200789569.0093</v>
       </c>
       <c r="N14" t="n">
-        <v>1142408546819.001</v>
+        <v>1142408543706.983</v>
       </c>
       <c r="O14" t="n">
         <v>0.01946402</v>
@@ -1344,14 +1344,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-09-04T13:20:30.000Z</t>
+          <t>2026-09-05T12:30:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260904T132342Z-108cc5</t>
+          <t>20260905T123308Z-b8d665</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1370,34 +1370,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>527.37</v>
+        <v>541.04</v>
       </c>
       <c r="F15" t="n">
-        <v>9912069668</v>
+        <v>10178542171</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>209126501</v>
+        <v>138656489</v>
       </c>
       <c r="I15" t="n">
-        <v>565.05</v>
+        <v>542.21</v>
       </c>
       <c r="J15" t="n">
-        <v>499.99</v>
+        <v>513.76</v>
       </c>
       <c r="K15" t="n">
-        <v>14.72</v>
+        <v>6.78</v>
       </c>
       <c r="L15" t="n">
-        <v>3.04267</v>
+        <v>1.91457</v>
       </c>
       <c r="M15" t="n">
-        <v>18800177.20512704</v>
+        <v>18800635.00240712</v>
       </c>
       <c r="N15" t="n">
-        <v>18800212.60457258</v>
+        <v>18800676.40196387</v>
       </c>
       <c r="O15" t="n">
         <v>797.73</v>
@@ -1409,14 +1409,14 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-09-04T13:20:30.000Z</t>
+          <t>2026-09-05T12:30:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260904T132342Z-108cc5</t>
+          <t>20260905T123308Z-b8d665</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1435,34 +1435,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.99992</v>
+        <v>0.999731</v>
       </c>
       <c r="F16" t="n">
-        <v>9788041911</v>
+        <v>9807111492</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>178743055</v>
+        <v>179554912</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.999699</v>
+        <v>0.999538</v>
       </c>
       <c r="K16" t="n">
-        <v>-3.4802293604974e-05</v>
+        <v>-0.000132116749177458</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.00502</v>
+        <v>-0.0177</v>
       </c>
       <c r="M16" t="n">
-        <v>9788862059.147768</v>
+        <v>9809540195.529448</v>
       </c>
       <c r="N16" t="n">
-        <v>9788244960.351456</v>
+        <v>9812791674.646385</v>
       </c>
       <c r="O16" t="n">
         <v>1.057</v>
@@ -1474,14 +1474,14 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-09-04T13:20:30.000Z</t>
+          <t>2026-09-05T12:30:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260904T132342Z-108cc5</t>
+          <t>20260905T123308Z-b8d665</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1500,28 +1500,28 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>11.62</v>
+        <v>11.74</v>
       </c>
       <c r="F17" t="n">
-        <v>8688399026</v>
+        <v>8792255966</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>543808477</v>
+        <v>355406637</v>
       </c>
       <c r="I17" t="n">
-        <v>12.15</v>
+        <v>11.86</v>
       </c>
       <c r="J17" t="n">
-        <v>11.4</v>
+        <v>11.48</v>
       </c>
       <c r="K17" t="n">
-        <v>0.232654</v>
+        <v>0.00755558</v>
       </c>
       <c r="L17" t="n">
-        <v>2.11083</v>
+        <v>0.98095</v>
       </c>
       <c r="M17" t="n">
         <v>748099970.424884</v>
@@ -1539,14 +1539,14 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-09-04T13:20:30.000Z</t>
+          <t>2026-09-05T12:30:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260904T132342Z-108cc5</t>
+          <t>20260905T123308Z-b8d665</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1565,28 +1565,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>72.98</v>
+        <v>73.13</v>
       </c>
       <c r="F18" t="n">
-        <v>8606781427</v>
+        <v>8628496457</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>139278540</v>
+        <v>72217792</v>
       </c>
       <c r="I18" t="n">
-        <v>74.91</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>71.98</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>1.17</v>
+        <v>-0.171271908333992</v>
       </c>
       <c r="L18" t="n">
-        <v>1.59778</v>
+        <v>-0.25905</v>
       </c>
       <c r="M18" t="n">
         <v>117956019</v>
@@ -1604,14 +1604,14 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-09-04T13:20:30.000Z</t>
+          <t>2026-09-05T12:30:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260904T132342Z-108cc5</t>
+          <t>20260905T123308Z-b8d665</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1630,28 +1630,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>9.23</v>
+        <v>9.26</v>
       </c>
       <c r="F19" t="n">
-        <v>8492336269</v>
+        <v>8518246603</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>158502</v>
+        <v>272469</v>
       </c>
       <c r="I19" t="n">
-        <v>9.449999999999999</v>
+        <v>9.35</v>
       </c>
       <c r="J19" t="n">
-        <v>9.220000000000001</v>
+        <v>9.18</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.06892478826383019</v>
+        <v>-0.03216060213670424</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7431</v>
+        <v>-0.34608</v>
       </c>
       <c r="M19" t="n">
         <v>919857851.9</v>
@@ -1669,14 +1669,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-09-04T13:20:30.000Z</t>
+          <t>2026-09-05T12:30:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260904T132342Z-108cc5</t>
+          <t>20260905T123308Z-b8d665</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1695,28 +1695,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.214565</v>
+        <v>0.213712</v>
       </c>
       <c r="F20" t="n">
-        <v>8043119372</v>
+        <v>8027219370</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>761119607</v>
+        <v>459082454</v>
       </c>
       <c r="I20" t="n">
-        <v>0.226776</v>
+        <v>0.216575</v>
       </c>
       <c r="J20" t="n">
-        <v>0.209667</v>
+        <v>0.209454</v>
       </c>
       <c r="K20" t="n">
-        <v>0.00541804</v>
+        <v>-0.002336477761568062</v>
       </c>
       <c r="L20" t="n">
-        <v>2.63109</v>
+        <v>-0.60293</v>
       </c>
       <c r="M20" t="n">
         <v>37504333228.36598</v>
@@ -1734,14 +1734,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-09-04T13:20:30.000Z</t>
+          <t>2026-09-05T12:30:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260904T132342Z-108cc5</t>
+          <t>20260905T123308Z-b8d665</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1760,31 +1760,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.180543</v>
+        <v>0.182699</v>
       </c>
       <c r="F21" t="n">
-        <v>6263102886</v>
+        <v>6360291592</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>175302475</v>
+        <v>132582460</v>
       </c>
       <c r="I21" t="n">
-        <v>0.188001</v>
+        <v>0.183928</v>
       </c>
       <c r="J21" t="n">
-        <v>0.179006</v>
+        <v>0.177583</v>
       </c>
       <c r="K21" t="n">
-        <v>0.00140816</v>
+        <v>0.00131473</v>
       </c>
       <c r="L21" t="n">
-        <v>0.79822</v>
+        <v>1.43083</v>
       </c>
       <c r="M21" t="n">
-        <v>34718653715.55763</v>
+        <v>34802067673.74753</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.91247</v>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-09-04T13:20:30.000Z</t>
+          <t>2026-09-05T12:30:20.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260905T123308Z-b8d665</t>
+          <t>20260906T124754Z-98baf9</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>79627</v>
+        <v>79939</v>
       </c>
       <c r="F2" t="n">
-        <v>1599559585726</v>
+        <v>1605188574631</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>26745226109</v>
+        <v>20251566573</v>
       </c>
       <c r="I2" t="n">
-        <v>79848</v>
+        <v>80147</v>
       </c>
       <c r="J2" t="n">
-        <v>78706</v>
+        <v>79586</v>
       </c>
       <c r="K2" t="n">
-        <v>-494.7438492716319</v>
+        <v>182.18</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.34503</v>
+        <v>0.22842</v>
       </c>
       <c r="M2" t="n">
-        <v>20079921</v>
+        <v>20080328</v>
       </c>
       <c r="N2" t="n">
-        <v>20079981</v>
+        <v>20080475</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-05T12:30:20.000Z</t>
+          <t>2026-09-06T12:45:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260905T123308Z-b8d665</t>
+          <t>20260906T124754Z-98baf9</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2454.03</v>
+        <v>2500.08</v>
       </c>
       <c r="F3" t="n">
-        <v>299538882721</v>
+        <v>305070663503</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>10563398954</v>
+        <v>8846529688</v>
       </c>
       <c r="I3" t="n">
-        <v>2463.12</v>
+        <v>2521.39</v>
       </c>
       <c r="J3" t="n">
-        <v>2435.15</v>
+        <v>2451.62</v>
       </c>
       <c r="K3" t="n">
-        <v>-15.95687009235553</v>
+        <v>39.04</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.03568</v>
+        <v>1.58646</v>
       </c>
       <c r="M3" t="n">
-        <v>122020932.8534729</v>
+        <v>122023857.5661058</v>
       </c>
       <c r="N3" t="n">
-        <v>122020932.8534728</v>
+        <v>122023857.5661057</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-05T12:30:20.000Z</t>
+          <t>2026-09-06T12:45:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260905T123308Z-b8d665</t>
+          <t>20260906T124754Z-98baf9</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,28 +655,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0.999969</v>
       </c>
       <c r="F4" t="n">
-        <v>183411232653</v>
+        <v>183388819396</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>51368333618</v>
+        <v>44064394164</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999868</v>
+        <v>0.999881</v>
       </c>
       <c r="K4" t="n">
-        <v>9.855e-05</v>
+        <v>-0.000104016805162255</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00524</v>
+        <v>-0.0104</v>
       </c>
       <c r="M4" t="n">
         <v>183392383062.0927</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-05T12:30:20.000Z</t>
+          <t>2026-09-06T12:45:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260905T123308Z-b8d665</t>
+          <t>20260906T124754Z-98baf9</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>754.75</v>
+        <v>755.42</v>
       </c>
       <c r="F5" t="n">
-        <v>100669627319</v>
+        <v>100599740056</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1539825166</v>
+        <v>1751071588</v>
       </c>
       <c r="I5" t="n">
-        <v>755.23</v>
+        <v>779.7</v>
       </c>
       <c r="J5" t="n">
-        <v>709.29</v>
+        <v>754.74</v>
       </c>
       <c r="K5" t="n">
-        <v>37.26</v>
+        <v>-2.519272375029004</v>
       </c>
       <c r="L5" t="n">
-        <v>5.44966</v>
+        <v>-0.33239</v>
       </c>
       <c r="M5" t="n">
-        <v>133161986.43</v>
+        <v>133161861.44</v>
       </c>
       <c r="N5" t="n">
-        <v>133161979.25</v>
+        <v>133161857.19</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-05T12:30:20.000Z</t>
+          <t>2026-09-06T12:45:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260905T123308Z-b8d665</t>
+          <t>20260906T124754Z-98baf9</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="F6" t="n">
-        <v>88145207092</v>
+        <v>89160333986</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>2053892311</v>
+        <v>1581409616</v>
       </c>
       <c r="I6" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="J6" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.01074625837040433</v>
+        <v>0.00580668</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.2599</v>
+        <v>0.4103</v>
       </c>
       <c r="M6" t="n">
         <v>62744504852</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-05T12:30:20.000Z</t>
+          <t>2026-09-06T12:45:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260905T123308Z-b8d665</t>
+          <t>20260906T124754Z-98baf9</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999995</v>
+        <v>0.999915</v>
       </c>
       <c r="F7" t="n">
-        <v>74603986980</v>
+        <v>74538257617</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>13560913142</v>
+        <v>9927107053</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9997740000000001</v>
+        <v>0.999897</v>
       </c>
       <c r="K7" t="n">
-        <v>-4.42967446945e-07</v>
+        <v>-7.2408344941155e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.00246</v>
+        <v>-0.00724</v>
       </c>
       <c r="M7" t="n">
-        <v>74602236473.1615</v>
+        <v>74543550970.483</v>
       </c>
       <c r="N7" t="n">
-        <v>74604014988.58582</v>
+        <v>74560251624.61424</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-05T12:30:20.000Z</t>
+          <t>2026-09-06T12:45:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260905T123308Z-b8d665</t>
+          <t>20260906T124754Z-98baf9</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102.33</v>
+        <v>107.01</v>
       </c>
       <c r="F8" t="n">
-        <v>59935721064</v>
+        <v>62646101572</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>2605188432</v>
+        <v>3770027474</v>
       </c>
       <c r="I8" t="n">
-        <v>102.79</v>
+        <v>107.14</v>
       </c>
       <c r="J8" t="n">
-        <v>100.4</v>
+        <v>102.65</v>
       </c>
       <c r="K8" t="n">
-        <v>0.760165</v>
+        <v>4.06</v>
       </c>
       <c r="L8" t="n">
-        <v>1.11121</v>
+        <v>3.94863</v>
       </c>
       <c r="M8" t="n">
-        <v>585359561.7917758</v>
+        <v>585445163.7810631</v>
       </c>
       <c r="N8" t="n">
-        <v>633454599.1689531</v>
+        <v>633549033.2962806</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-05T12:30:20.000Z</t>
+          <t>2026-09-06T12:45:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260905T123308Z-b8d665</t>
+          <t>20260906T124754Z-98baf9</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.332812</v>
+        <v>0.335192</v>
       </c>
       <c r="F9" t="n">
-        <v>31594137028</v>
+        <v>31821584143</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>311107005</v>
+        <v>245347772</v>
       </c>
       <c r="I9" t="n">
-        <v>0.333228</v>
+        <v>0.335145</v>
       </c>
       <c r="J9" t="n">
-        <v>0.328453</v>
+        <v>0.332901</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00402935</v>
+        <v>0.00210288</v>
       </c>
       <c r="L9" t="n">
-        <v>1.27509</v>
+        <v>0.6313299999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>94933696444.65239</v>
+        <v>94935900212.59479</v>
       </c>
       <c r="N9" t="n">
-        <v>94935403392.50798</v>
+        <v>94937622231.33868</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-05T12:30:20.000Z</t>
+          <t>2026-09-06T12:45:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260905T123308Z-b8d665</t>
+          <t>20260906T124754Z-98baf9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,34 +1045,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.039</v>
+        <v>1.055</v>
       </c>
       <c r="F10" t="n">
-        <v>23111985829</v>
+        <v>23516084575</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>23229332</v>
+        <v>343538</v>
       </c>
       <c r="I10" t="n">
-        <v>1.041</v>
+        <v>1.055</v>
       </c>
       <c r="J10" t="n">
-        <v>1.03</v>
+        <v>1.004</v>
       </c>
       <c r="K10" t="n">
-        <v>0.00627504</v>
+        <v>0.01582381</v>
       </c>
       <c r="L10" t="n">
-        <v>0.61245</v>
+        <v>1.52276</v>
       </c>
       <c r="M10" t="n">
-        <v>22254918397.228</v>
+        <v>22290650137.398</v>
       </c>
       <c r="N10" t="n">
-        <v>22254918397.228</v>
+        <v>22290650137.398</v>
       </c>
       <c r="O10" t="n">
         <v>1.061</v>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-09-05T12:30:20.000Z</t>
+          <t>2026-09-05T22:40:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260905T123308Z-b8d665</t>
+          <t>20260906T124754Z-98baf9</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,28 +1110,28 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>84.98999999999999</v>
+        <v>89.02</v>
       </c>
       <c r="F11" t="n">
-        <v>18927342709</v>
+        <v>19795941723</v>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>1038012646</v>
+        <v>1144346545</v>
       </c>
       <c r="I11" t="n">
-        <v>85.75</v>
+        <v>88.64</v>
       </c>
       <c r="J11" t="n">
-        <v>83.64</v>
+        <v>84.94</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.9863609708923349</v>
+        <v>4.05</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.54309</v>
+        <v>4.76586</v>
       </c>
       <c r="M11" t="n">
         <v>222445714.0741414</v>
@@ -1140,23 +1140,23 @@
         <v>955307079.4341414</v>
       </c>
       <c r="O11" t="n">
-        <v>88.06</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-09-03T23:46:20.000Z</t>
+          <t>2026-09-06T12:28:40.000Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-05T12:30:20.000Z</t>
+          <t>2026-09-06T12:45:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260905T123308Z-b8d665</t>
+          <t>20260906T124754Z-98baf9</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,34 +1175,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1008.51</v>
+        <v>1169.04</v>
       </c>
       <c r="F12" t="n">
-        <v>17074273476</v>
+        <v>19770302555</v>
       </c>
       <c r="G12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>1074051251</v>
+        <v>1257047900</v>
       </c>
       <c r="I12" t="n">
-        <v>1046.3</v>
+        <v>1206.41</v>
       </c>
       <c r="J12" t="n">
-        <v>966.84</v>
+        <v>1004.71</v>
       </c>
       <c r="K12" t="n">
-        <v>24.98</v>
+        <v>158.45</v>
       </c>
       <c r="L12" t="n">
-        <v>2.85001</v>
+        <v>15.67862</v>
       </c>
       <c r="M12" t="n">
-        <v>16912153.2905448</v>
+        <v>16916382.9780448</v>
       </c>
       <c r="N12" t="n">
-        <v>16915817.3530448</v>
+        <v>16917600.1655448</v>
       </c>
       <c r="O12" t="n">
         <v>3191.93</v>
@@ -1214,14 +1214,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-05T12:30:20.000Z</t>
+          <t>2026-09-06T12:45:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260905T123308Z-b8d665</t>
+          <t>20260906T124754Z-98baf9</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.086243</v>
+        <v>0.089807</v>
       </c>
       <c r="F13" t="n">
-        <v>13452940677</v>
+        <v>13992269638</v>
       </c>
       <c r="G13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H13" t="n">
-        <v>726461375</v>
+        <v>1376984983</v>
       </c>
       <c r="I13" t="n">
-        <v>0.086267</v>
+        <v>0.094557</v>
       </c>
       <c r="J13" t="n">
-        <v>0.083882</v>
+        <v>0.087114</v>
       </c>
       <c r="K13" t="n">
-        <v>0.00059221</v>
+        <v>0.00248877</v>
       </c>
       <c r="L13" t="n">
-        <v>1.36679</v>
+        <v>2.85022</v>
       </c>
       <c r="M13" t="n">
-        <v>155789276383.7053</v>
+        <v>155802096383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>171501463126.579</v>
+        <v>171515383126.579</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-05T12:30:20.000Z</t>
+          <t>2026-09-06T12:45:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260905T123308Z-b8d665</t>
+          <t>20260906T124754Z-98baf9</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,34 +1305,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.01640475</v>
+        <v>0.01700862</v>
       </c>
       <c r="F14" t="n">
-        <v>11637183792</v>
+        <v>12064176009</v>
       </c>
       <c r="G14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H14" t="n">
-        <v>43201814</v>
+        <v>40485344</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01664376</v>
+        <v>0.01727553</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01638085</v>
+        <v>0.01639659</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.000372463176358119</v>
+        <v>0.0005725</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.7997</v>
+        <v>3.48317</v>
       </c>
       <c r="M14" t="n">
-        <v>709200789569.0093</v>
+        <v>709207157937.1138</v>
       </c>
       <c r="N14" t="n">
-        <v>1142408543706.983</v>
+        <v>1142408539441.109</v>
       </c>
       <c r="O14" t="n">
         <v>0.01946402</v>
@@ -1344,14 +1344,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-09-05T12:30:20.000Z</t>
+          <t>2026-09-06T12:45:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260905T123308Z-b8d665</t>
+          <t>20260906T124754Z-98baf9</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1370,34 +1370,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>541.04</v>
+        <v>538.6900000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>10178542171</v>
+        <v>10128038877</v>
       </c>
       <c r="G15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H15" t="n">
-        <v>138656489</v>
+        <v>110036085</v>
       </c>
       <c r="I15" t="n">
-        <v>542.21</v>
+        <v>558.79</v>
       </c>
       <c r="J15" t="n">
-        <v>513.76</v>
+        <v>535.45</v>
       </c>
       <c r="K15" t="n">
-        <v>6.78</v>
+        <v>-4.958884659106616</v>
       </c>
       <c r="L15" t="n">
-        <v>1.91457</v>
+        <v>-0.91215</v>
       </c>
       <c r="M15" t="n">
-        <v>18800635.00240712</v>
+        <v>18801037.59904108</v>
       </c>
       <c r="N15" t="n">
-        <v>18800676.40196387</v>
+        <v>18801069.99830875</v>
       </c>
       <c r="O15" t="n">
         <v>797.73</v>
@@ -1409,14 +1409,14 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-09-05T12:30:20.000Z</t>
+          <t>2026-09-06T12:45:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260905T123308Z-b8d665</t>
+          <t>20260906T124754Z-98baf9</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1435,34 +1435,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.999731</v>
+        <v>0.999645</v>
       </c>
       <c r="F16" t="n">
-        <v>9807111492</v>
+        <v>9819481809</v>
       </c>
       <c r="G16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H16" t="n">
-        <v>179554912</v>
+        <v>84132005</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0.999953</v>
       </c>
       <c r="J16" t="n">
-        <v>0.999538</v>
+        <v>0.999501</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.000132116749177458</v>
+        <v>-8.3381295249429e-05</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.0177</v>
+        <v>-0.00834</v>
       </c>
       <c r="M16" t="n">
-        <v>9809540195.529448</v>
+        <v>9822846877.735327</v>
       </c>
       <c r="N16" t="n">
-        <v>9812791674.646385</v>
+        <v>9823362298.231236</v>
       </c>
       <c r="O16" t="n">
         <v>1.057</v>
@@ -1474,14 +1474,14 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-09-05T12:30:20.000Z</t>
+          <t>2026-09-06T12:45:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260905T123308Z-b8d665</t>
+          <t>20260906T124754Z-98baf9</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1500,28 +1500,28 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>11.74</v>
+        <v>12.31</v>
       </c>
       <c r="F17" t="n">
-        <v>8792255966</v>
+        <v>9207158395</v>
       </c>
       <c r="G17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H17" t="n">
-        <v>355406637</v>
+        <v>457889255</v>
       </c>
       <c r="I17" t="n">
-        <v>11.86</v>
+        <v>12.44</v>
       </c>
       <c r="J17" t="n">
-        <v>11.48</v>
+        <v>11.83</v>
       </c>
       <c r="K17" t="n">
-        <v>0.00755558</v>
+        <v>0.481165</v>
       </c>
       <c r="L17" t="n">
-        <v>0.98095</v>
+        <v>4.06912</v>
       </c>
       <c r="M17" t="n">
         <v>748099970.424884</v>
@@ -1539,14 +1539,14 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-09-05T12:30:20.000Z</t>
+          <t>2026-09-06T12:45:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260905T123308Z-b8d665</t>
+          <t>20260906T124754Z-98baf9</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1565,28 +1565,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>73.13</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>8628496457</v>
+        <v>8690494127</v>
       </c>
       <c r="G18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H18" t="n">
-        <v>72217792</v>
+        <v>48458085</v>
       </c>
       <c r="I18" t="n">
-        <v>73.40000000000001</v>
+        <v>73.97</v>
       </c>
       <c r="J18" t="n">
-        <v>72.40000000000001</v>
+        <v>73.09</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.171271908333992</v>
+        <v>0.401616</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.25905</v>
+        <v>0.54832</v>
       </c>
       <c r="M18" t="n">
         <v>117956019</v>
@@ -1604,14 +1604,14 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-09-05T12:30:20.000Z</t>
+          <t>2026-09-06T12:45:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260905T123308Z-b8d665</t>
+          <t>20260906T124754Z-98baf9</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1630,28 +1630,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>9.26</v>
+        <v>9.34</v>
       </c>
       <c r="F19" t="n">
-        <v>8518246603</v>
+        <v>8590679634</v>
       </c>
       <c r="G19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H19" t="n">
-        <v>272469</v>
+        <v>112941</v>
       </c>
       <c r="I19" t="n">
         <v>9.35</v>
       </c>
       <c r="J19" t="n">
-        <v>9.18</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.03216060213670424</v>
+        <v>0.07811999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.34608</v>
+        <v>0.84353</v>
       </c>
       <c r="M19" t="n">
         <v>919857851.9</v>
@@ -1669,14 +1669,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-09-05T12:30:20.000Z</t>
+          <t>2026-09-06T12:45:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260905T123308Z-b8d665</t>
+          <t>20260906T124754Z-98baf9</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1695,28 +1695,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.213712</v>
+        <v>0.220705</v>
       </c>
       <c r="F20" t="n">
-        <v>8027219370</v>
+        <v>8277231415</v>
       </c>
       <c r="G20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H20" t="n">
-        <v>459082454</v>
+        <v>456551881</v>
       </c>
       <c r="I20" t="n">
-        <v>0.216575</v>
+        <v>0.223606</v>
       </c>
       <c r="J20" t="n">
-        <v>0.209454</v>
+        <v>0.215218</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.002336477761568062</v>
+        <v>0.00417536</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.60293</v>
+        <v>1.92831</v>
       </c>
       <c r="M20" t="n">
         <v>37504333228.36598</v>
@@ -1734,14 +1734,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-09-05T12:30:20.000Z</t>
+          <t>2026-09-06T12:45:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260905T123308Z-b8d665</t>
+          <t>20260906T124754Z-98baf9</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1760,31 +1760,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.182699</v>
+        <v>0.1866</v>
       </c>
       <c r="F21" t="n">
-        <v>6360291592</v>
+        <v>6493581518</v>
       </c>
       <c r="G21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H21" t="n">
-        <v>132582460</v>
+        <v>123669612</v>
       </c>
       <c r="I21" t="n">
-        <v>0.183928</v>
+        <v>0.187637</v>
       </c>
       <c r="J21" t="n">
-        <v>0.177583</v>
+        <v>0.183105</v>
       </c>
       <c r="K21" t="n">
-        <v>0.00131473</v>
+        <v>0.00216844</v>
       </c>
       <c r="L21" t="n">
-        <v>1.43083</v>
+        <v>1.17575</v>
       </c>
       <c r="M21" t="n">
-        <v>34802067673.74753</v>
+        <v>34802059386.72196</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.91247</v>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-09-05T12:30:20.000Z</t>
+          <t>2026-09-06T12:45:20.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260906T124754Z-98baf9</t>
+          <t>20260907T145846Z-c22ca5</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>79939</v>
+        <v>79205</v>
       </c>
       <c r="F2" t="n">
-        <v>1605188574631</v>
+        <v>1590659585794</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>20251566573</v>
+        <v>23116890590</v>
       </c>
       <c r="I2" t="n">
-        <v>80147</v>
+        <v>80494</v>
       </c>
       <c r="J2" t="n">
-        <v>79586</v>
+        <v>79081</v>
       </c>
       <c r="K2" t="n">
-        <v>182.18</v>
+        <v>-422.9073076706554</v>
       </c>
       <c r="L2" t="n">
-        <v>0.22842</v>
+        <v>-0.51552</v>
       </c>
       <c r="M2" t="n">
-        <v>20080328</v>
+        <v>20081015</v>
       </c>
       <c r="N2" t="n">
-        <v>20080475</v>
+        <v>20081043</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-06T12:45:20.000Z</t>
+          <t>2026-09-07T14:55:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260906T124754Z-98baf9</t>
+          <t>20260907T145846Z-c22ca5</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2500.08</v>
+        <v>2488.47</v>
       </c>
       <c r="F3" t="n">
-        <v>305070663503</v>
+        <v>303678062021</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>8846529688</v>
+        <v>11310169661</v>
       </c>
       <c r="I3" t="n">
-        <v>2521.39</v>
+        <v>2532.72</v>
       </c>
       <c r="J3" t="n">
-        <v>2451.62</v>
+        <v>2473.53</v>
       </c>
       <c r="K3" t="n">
-        <v>39.04</v>
+        <v>7.37</v>
       </c>
       <c r="L3" t="n">
-        <v>1.58646</v>
+        <v>0.32631</v>
       </c>
       <c r="M3" t="n">
-        <v>122023857.5661058</v>
+        <v>122026782.2520997</v>
       </c>
       <c r="N3" t="n">
-        <v>122023857.5661057</v>
+        <v>122026782.2520997</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-06T12:45:20.000Z</t>
+          <t>2026-09-07T14:55:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260906T124754Z-98baf9</t>
+          <t>20260907T145846Z-c22ca5</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,34 +655,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999969</v>
+        <v>0.999845</v>
       </c>
       <c r="F4" t="n">
-        <v>183388819396</v>
+        <v>183385485330</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>44064394164</v>
+        <v>47843327085</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999881</v>
+        <v>0.999789</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.000104016805162255</v>
+        <v>-0.000112741507668934</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0104</v>
+        <v>-0.00805</v>
       </c>
       <c r="M4" t="n">
-        <v>183392383062.0927</v>
+        <v>183410739312.7418</v>
       </c>
       <c r="N4" t="n">
-        <v>188859328873.3562</v>
+        <v>188877685134.3562</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-06T12:45:20.000Z</t>
+          <t>2026-09-07T14:55:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260906T124754Z-98baf9</t>
+          <t>20260907T145846Z-c22ca5</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>755.42</v>
+        <v>743.61</v>
       </c>
       <c r="F5" t="n">
-        <v>100599740056</v>
+        <v>99031901283</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1751071588</v>
+        <v>932988612</v>
       </c>
       <c r="I5" t="n">
-        <v>779.7</v>
+        <v>755.9</v>
       </c>
       <c r="J5" t="n">
-        <v>754.74</v>
+        <v>740.53</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.519272375029004</v>
+        <v>1.12</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.33239</v>
+        <v>0.16072</v>
       </c>
       <c r="M5" t="n">
-        <v>133161861.44</v>
+        <v>133161695.81</v>
       </c>
       <c r="N5" t="n">
-        <v>133161857.19</v>
+        <v>133161685.82</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-06T12:45:20.000Z</t>
+          <t>2026-09-07T14:55:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260906T124754Z-98baf9</t>
+          <t>20260907T145846Z-c22ca5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="F6" t="n">
-        <v>89160333986</v>
+        <v>87790603215</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>1581409616</v>
+        <v>1905204251</v>
       </c>
       <c r="I6" t="n">
         <v>1.43</v>
       </c>
       <c r="J6" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00580668</v>
+        <v>-0.01164624825002725</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4103</v>
+        <v>-0.79796</v>
       </c>
       <c r="M6" t="n">
         <v>62744504852</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-06T12:45:20.000Z</t>
+          <t>2026-09-07T14:55:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260906T124754Z-98baf9</t>
+          <t>20260907T145846Z-c22ca5</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999915</v>
+        <v>0.999862</v>
       </c>
       <c r="F7" t="n">
-        <v>74538257617</v>
+        <v>74429895164</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>9927107053</v>
+        <v>11849654999</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999897</v>
+        <v>0.999792</v>
       </c>
       <c r="K7" t="n">
-        <v>-7.2408344941155e-05</v>
+        <v>-9.6660980189456e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.00724</v>
+        <v>-0.00581</v>
       </c>
       <c r="M7" t="n">
-        <v>74543550970.483</v>
+        <v>74438462885.66106</v>
       </c>
       <c r="N7" t="n">
-        <v>74560251624.61424</v>
+        <v>74446493791.62599</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-06T12:45:20.000Z</t>
+          <t>2026-09-07T14:55:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260906T124754Z-98baf9</t>
+          <t>20260907T145846Z-c22ca5</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>107.01</v>
+        <v>104.63</v>
       </c>
       <c r="F8" t="n">
-        <v>62646101572</v>
+        <v>61334747310</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>3770027474</v>
+        <v>3268333090</v>
       </c>
       <c r="I8" t="n">
-        <v>107.14</v>
+        <v>106.96</v>
       </c>
       <c r="J8" t="n">
-        <v>102.65</v>
+        <v>103.95</v>
       </c>
       <c r="K8" t="n">
-        <v>4.06</v>
+        <v>-1.190910922008328</v>
       </c>
       <c r="L8" t="n">
-        <v>3.94863</v>
+        <v>-1.10505</v>
       </c>
       <c r="M8" t="n">
-        <v>585445163.7810631</v>
+        <v>586166024.1307415</v>
       </c>
       <c r="N8" t="n">
-        <v>633549033.2962806</v>
+        <v>633643310.3873425</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-06T12:45:20.000Z</t>
+          <t>2026-09-07T14:55:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260906T124754Z-98baf9</t>
+          <t>20260907T145846Z-c22ca5</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.335192</v>
+        <v>0.334807</v>
       </c>
       <c r="F9" t="n">
-        <v>31821584143</v>
+        <v>31789190703</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>245347772</v>
+        <v>312110607</v>
       </c>
       <c r="I9" t="n">
-        <v>0.335145</v>
+        <v>0.337279</v>
       </c>
       <c r="J9" t="n">
-        <v>0.332901</v>
+        <v>0.334766</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00210288</v>
+        <v>-0.000286055151930975</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6313299999999999</v>
+        <v>-0.07874</v>
       </c>
       <c r="M9" t="n">
-        <v>94935900212.59479</v>
+        <v>94939385018.58868</v>
       </c>
       <c r="N9" t="n">
-        <v>94937622231.33868</v>
+        <v>94939383860.86168</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-06T12:45:20.000Z</t>
+          <t>2026-09-07T14:55:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260906T124754Z-98baf9</t>
+          <t>20260907T145846Z-c22ca5</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1057,22 +1057,18 @@
         <v>343538</v>
       </c>
       <c r="I10" t="n">
-        <v>1.055</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.004</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.01582381</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.52276</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>22290650137.398</v>
       </c>
       <c r="N10" t="n">
-        <v>22290650137.398</v>
+        <v>22292012681.268</v>
       </c>
       <c r="O10" t="n">
         <v>1.061</v>
@@ -1091,137 +1087,137 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260906T124754Z-98baf9</t>
+          <t>20260907T145846Z-c22ca5</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>hyperliquid</t>
+          <t>zcash</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>hype</t>
+          <t>zec</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Hyperliquid</t>
+          <t>Zcash</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>89.02</v>
+        <v>1173.2</v>
       </c>
       <c r="F11" t="n">
-        <v>19795941723</v>
+        <v>19849025512</v>
       </c>
       <c r="G11" t="n">
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>1144346545</v>
+        <v>1283780184</v>
       </c>
       <c r="I11" t="n">
-        <v>88.64</v>
+        <v>1249.28</v>
       </c>
       <c r="J11" t="n">
-        <v>84.94</v>
+        <v>1153.85</v>
       </c>
       <c r="K11" t="n">
-        <v>4.05</v>
+        <v>11.19</v>
       </c>
       <c r="L11" t="n">
-        <v>4.76586</v>
+        <v>0.79725</v>
       </c>
       <c r="M11" t="n">
-        <v>222445714.0741414</v>
+        <v>16919136.1030448</v>
       </c>
       <c r="N11" t="n">
-        <v>955307079.4341414</v>
+        <v>16919603.2905448</v>
       </c>
       <c r="O11" t="n">
-        <v>89.59999999999999</v>
+        <v>3191.93</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-09-06T12:28:40.000Z</t>
+          <t>2016-10-28T16:00:00.000Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-06T12:45:20.000Z</t>
+          <t>2026-09-07T14:55:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260906T124754Z-98baf9</t>
+          <t>20260907T145846Z-c22ca5</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>zcash</t>
+          <t>hyperliquid</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>zec</t>
+          <t>hype</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Zcash</t>
+          <t>Hyperliquid</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1169.04</v>
+        <v>86.79000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>19770302555</v>
+        <v>19312568388</v>
       </c>
       <c r="G12" t="n">
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>1257047900</v>
+        <v>1293943906</v>
       </c>
       <c r="I12" t="n">
-        <v>1206.41</v>
+        <v>89.47</v>
       </c>
       <c r="J12" t="n">
-        <v>1004.71</v>
+        <v>86.09</v>
       </c>
       <c r="K12" t="n">
-        <v>158.45</v>
+        <v>-2.307690637938222</v>
       </c>
       <c r="L12" t="n">
-        <v>15.67862</v>
+        <v>-2.57363</v>
       </c>
       <c r="M12" t="n">
-        <v>16916382.9780448</v>
+        <v>222445714.0741414</v>
       </c>
       <c r="N12" t="n">
-        <v>16917600.1655448</v>
+        <v>955307079.4341414</v>
       </c>
       <c r="O12" t="n">
-        <v>3191.93</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2016-10-28T16:00:00.000Z</t>
+          <t>2026-09-06T12:28:40.000Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-06T12:45:20.000Z</t>
+          <t>2026-09-07T14:55:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260906T124754Z-98baf9</t>
+          <t>20260907T145846Z-c22ca5</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1236,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.089807</v>
+        <v>0.09057800000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>13992269638</v>
+        <v>14110684519</v>
       </c>
       <c r="G13" t="n">
         <v>11</v>
       </c>
       <c r="H13" t="n">
-        <v>1376984983</v>
+        <v>783869671</v>
       </c>
       <c r="I13" t="n">
-        <v>0.094557</v>
+        <v>0.091742</v>
       </c>
       <c r="J13" t="n">
-        <v>0.087114</v>
+        <v>0.08817899999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>0.00248877</v>
+        <v>0.00192907</v>
       </c>
       <c r="L13" t="n">
-        <v>2.85022</v>
+        <v>2.23945</v>
       </c>
       <c r="M13" t="n">
-        <v>155802096383.7052</v>
+        <v>155817046383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>171515383126.579</v>
+        <v>171530173126.579</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,14 +1275,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-06T12:45:20.000Z</t>
+          <t>2026-09-07T14:55:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260906T124754Z-98baf9</t>
+          <t>20260907T145846Z-c22ca5</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,34 +1301,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.01700862</v>
+        <v>0.01642947</v>
       </c>
       <c r="F14" t="n">
-        <v>12064176009</v>
+        <v>11652058418</v>
       </c>
       <c r="G14" t="n">
         <v>12</v>
       </c>
       <c r="H14" t="n">
-        <v>40485344</v>
+        <v>28003652</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01727553</v>
+        <v>0.0168531</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01639659</v>
+        <v>0.01644404</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0005725</v>
+        <v>-0.000401803670891002</v>
       </c>
       <c r="L14" t="n">
-        <v>3.48317</v>
+        <v>-2.41006</v>
       </c>
       <c r="M14" t="n">
-        <v>709207157937.1138</v>
+        <v>709208086630.5371</v>
       </c>
       <c r="N14" t="n">
-        <v>1142408539441.109</v>
+        <v>1142408537396.226</v>
       </c>
       <c r="O14" t="n">
         <v>0.01946402</v>
@@ -1344,14 +1340,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-09-06T12:45:20.000Z</t>
+          <t>2026-09-07T14:55:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260906T124754Z-98baf9</t>
+          <t>20260907T145846Z-c22ca5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1370,34 +1366,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>538.6900000000001</v>
+        <v>536.79</v>
       </c>
       <c r="F15" t="n">
-        <v>10128038877</v>
+        <v>10090294482</v>
       </c>
       <c r="G15" t="n">
         <v>13</v>
       </c>
       <c r="H15" t="n">
-        <v>110036085</v>
+        <v>128059809</v>
       </c>
       <c r="I15" t="n">
-        <v>558.79</v>
+        <v>546.23</v>
       </c>
       <c r="J15" t="n">
-        <v>535.45</v>
+        <v>522.6900000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>-4.958884659106616</v>
+        <v>7.5</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.91215</v>
+        <v>1.38272</v>
       </c>
       <c r="M15" t="n">
-        <v>18801037.59904108</v>
+        <v>18801531.99160966</v>
       </c>
       <c r="N15" t="n">
-        <v>18801069.99830875</v>
+        <v>18801559.59019433</v>
       </c>
       <c r="O15" t="n">
         <v>797.73</v>
@@ -1409,14 +1405,14 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-09-06T12:45:20.000Z</t>
+          <t>2026-09-07T14:55:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260906T124754Z-98baf9</t>
+          <t>20260907T145846Z-c22ca5</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1435,34 +1431,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.999645</v>
+        <v>0.999797</v>
       </c>
       <c r="F16" t="n">
-        <v>9819481809</v>
+        <v>9848004350</v>
       </c>
       <c r="G16" t="n">
         <v>14</v>
       </c>
       <c r="H16" t="n">
-        <v>84132005</v>
+        <v>101081919</v>
       </c>
       <c r="I16" t="n">
-        <v>0.999953</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.999501</v>
+        <v>0.999631</v>
       </c>
       <c r="K16" t="n">
-        <v>-8.3381295249429e-05</v>
+        <v>-0.000124456003702367</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.00834</v>
+        <v>-0.009379999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>9822846877.735327</v>
+        <v>9849826110.139755</v>
       </c>
       <c r="N16" t="n">
-        <v>9823362298.231236</v>
+        <v>9846533593.644836</v>
       </c>
       <c r="O16" t="n">
         <v>1.057</v>
@@ -1474,14 +1470,14 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-09-06T12:45:20.000Z</t>
+          <t>2026-09-07T14:55:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260906T124754Z-98baf9</t>
+          <t>20260907T145846Z-c22ca5</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1500,28 +1496,28 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>12.31</v>
+        <v>13.04</v>
       </c>
       <c r="F17" t="n">
-        <v>9207158395</v>
+        <v>9760443017</v>
       </c>
       <c r="G17" t="n">
         <v>15</v>
       </c>
       <c r="H17" t="n">
-        <v>457889255</v>
+        <v>881960287</v>
       </c>
       <c r="I17" t="n">
-        <v>12.44</v>
+        <v>13.67</v>
       </c>
       <c r="J17" t="n">
-        <v>11.83</v>
+        <v>12.12</v>
       </c>
       <c r="K17" t="n">
-        <v>0.481165</v>
+        <v>0.863357</v>
       </c>
       <c r="L17" t="n">
-        <v>4.06912</v>
+        <v>7.13279</v>
       </c>
       <c r="M17" t="n">
         <v>748099970.424884</v>
@@ -1539,14 +1535,14 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-09-06T12:45:20.000Z</t>
+          <t>2026-09-07T14:55:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260906T124754Z-98baf9</t>
+          <t>20260907T145846Z-c22ca5</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1565,28 +1561,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>73.65000000000001</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>8690494127</v>
+        <v>8613578245</v>
       </c>
       <c r="G18" t="n">
         <v>16</v>
       </c>
       <c r="H18" t="n">
-        <v>48458085</v>
+        <v>68514591</v>
       </c>
       <c r="I18" t="n">
-        <v>73.97</v>
+        <v>74.25</v>
       </c>
       <c r="J18" t="n">
-        <v>73.09</v>
+        <v>72.98999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>0.401616</v>
+        <v>-0.3217745450649119</v>
       </c>
       <c r="L18" t="n">
-        <v>0.54832</v>
+        <v>-0.40532</v>
       </c>
       <c r="M18" t="n">
         <v>117956019</v>
@@ -1604,14 +1600,14 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-09-06T12:45:20.000Z</t>
+          <t>2026-09-07T14:55:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260906T124754Z-98baf9</t>
+          <t>20260907T145846Z-c22ca5</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1630,28 +1626,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>9.34</v>
+        <v>9.15</v>
       </c>
       <c r="F19" t="n">
-        <v>8590679634</v>
+        <v>8418541168</v>
       </c>
       <c r="G19" t="n">
         <v>17</v>
       </c>
       <c r="H19" t="n">
-        <v>112941</v>
+        <v>601096</v>
       </c>
       <c r="I19" t="n">
-        <v>9.35</v>
+        <v>9.41</v>
       </c>
       <c r="J19" t="n">
-        <v>9.220000000000001</v>
+        <v>8.81</v>
       </c>
       <c r="K19" t="n">
-        <v>0.07811999999999999</v>
+        <v>-0.1772484978069055</v>
       </c>
       <c r="L19" t="n">
-        <v>0.84353</v>
+        <v>-1.9007</v>
       </c>
       <c r="M19" t="n">
         <v>919857851.9</v>
@@ -1669,14 +1665,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-09-06T12:45:20.000Z</t>
+          <t>2026-09-07T14:55:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260906T124754Z-98baf9</t>
+          <t>20260907T145846Z-c22ca5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1695,31 +1691,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.220705</v>
+        <v>0.221773</v>
       </c>
       <c r="F20" t="n">
-        <v>8277231415</v>
+        <v>8319640276</v>
       </c>
       <c r="G20" t="n">
         <v>18</v>
       </c>
       <c r="H20" t="n">
-        <v>456551881</v>
+        <v>440209788</v>
       </c>
       <c r="I20" t="n">
-        <v>0.223606</v>
+        <v>0.226224</v>
       </c>
       <c r="J20" t="n">
-        <v>0.215218</v>
+        <v>0.215287</v>
       </c>
       <c r="K20" t="n">
-        <v>0.00417536</v>
+        <v>0.00410905</v>
       </c>
       <c r="L20" t="n">
-        <v>1.92831</v>
+        <v>1.89788</v>
       </c>
       <c r="M20" t="n">
-        <v>37504333228.36598</v>
+        <v>37510482444.2993</v>
       </c>
       <c r="N20" t="n">
         <v>45000000000</v>
@@ -1734,14 +1730,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-09-06T12:45:20.000Z</t>
+          <t>2026-09-07T14:55:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260906T124754Z-98baf9</t>
+          <t>20260907T145846Z-c22ca5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1760,34 +1756,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.1866</v>
+        <v>0.192242</v>
       </c>
       <c r="F21" t="n">
-        <v>6493581518</v>
+        <v>6695445369</v>
       </c>
       <c r="G21" t="n">
         <v>19</v>
       </c>
       <c r="H21" t="n">
-        <v>123669612</v>
+        <v>227800014</v>
       </c>
       <c r="I21" t="n">
-        <v>0.187637</v>
+        <v>0.196218</v>
       </c>
       <c r="J21" t="n">
-        <v>0.183105</v>
+        <v>0.182861</v>
       </c>
       <c r="K21" t="n">
-        <v>0.00216844</v>
+        <v>0.008405579999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>1.17575</v>
+        <v>4.52481</v>
       </c>
       <c r="M21" t="n">
-        <v>34802059386.72196</v>
+        <v>34802050139.15266</v>
       </c>
       <c r="N21" t="n">
-        <v>50001786839.91247</v>
+        <v>50001786839.70248</v>
       </c>
       <c r="O21" t="n">
         <v>0.875563</v>
@@ -1799,7 +1795,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-09-06T12:45:20.000Z</t>
+          <t>2026-09-07T14:55:20.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260907T145846Z-c22ca5</t>
+          <t>20260908T132838Z-1cee9e</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>79205</v>
+        <v>78348</v>
       </c>
       <c r="F2" t="n">
-        <v>1590659585794</v>
+        <v>1573587576688</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>23116890590</v>
+        <v>30082292059</v>
       </c>
       <c r="I2" t="n">
-        <v>80494</v>
+        <v>79432</v>
       </c>
       <c r="J2" t="n">
-        <v>79081</v>
+        <v>78193</v>
       </c>
       <c r="K2" t="n">
-        <v>-422.9073076706554</v>
+        <v>-1271.482630612853</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.51552</v>
+        <v>-1.59094</v>
       </c>
       <c r="M2" t="n">
-        <v>20081015</v>
+        <v>20081356</v>
       </c>
       <c r="N2" t="n">
-        <v>20081043</v>
+        <v>20081431</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-07T14:55:20.000Z</t>
+          <t>2026-09-08T13:25:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260907T145846Z-c22ca5</t>
+          <t>20260908T132838Z-1cee9e</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2488.47</v>
+        <v>2470.09</v>
       </c>
       <c r="F3" t="n">
-        <v>303678062021</v>
+        <v>301482428305</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>11310169661</v>
+        <v>10738190789</v>
       </c>
       <c r="I3" t="n">
-        <v>2532.72</v>
+        <v>2505.13</v>
       </c>
       <c r="J3" t="n">
-        <v>2473.53</v>
+        <v>2463.89</v>
       </c>
       <c r="K3" t="n">
-        <v>7.37</v>
+        <v>-38.36756983722034</v>
       </c>
       <c r="L3" t="n">
-        <v>0.32631</v>
+        <v>-1.49884</v>
       </c>
       <c r="M3" t="n">
-        <v>122026782.2520997</v>
+        <v>122029704.5242925</v>
       </c>
       <c r="N3" t="n">
-        <v>122026782.2520997</v>
+        <v>122029704.5242924</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-07T14:55:20.000Z</t>
+          <t>2026-09-08T13:25:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260907T145846Z-c22ca5</t>
+          <t>20260908T132838Z-1cee9e</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,34 +655,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999845</v>
+        <v>0.999564</v>
       </c>
       <c r="F4" t="n">
-        <v>183385485330</v>
+        <v>183357643237</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>47843327085</v>
+        <v>53434039190</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0.999943</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999789</v>
+        <v>0.999545</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.000112741507668934</v>
+        <v>-0.000342179458228675</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.00805</v>
+        <v>-0.034</v>
       </c>
       <c r="M4" t="n">
-        <v>183410739312.7418</v>
+        <v>183438580383.2119</v>
       </c>
       <c r="N4" t="n">
-        <v>188877685134.3562</v>
+        <v>188905526211.2662</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-07T14:55:20.000Z</t>
+          <t>2026-09-08T13:25:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260907T145846Z-c22ca5</t>
+          <t>20260908T132838Z-1cee9e</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>743.61</v>
+        <v>750.66</v>
       </c>
       <c r="F5" t="n">
-        <v>99031901283</v>
+        <v>99976744355</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>932988612</v>
+        <v>1150532846</v>
       </c>
       <c r="I5" t="n">
-        <v>755.9</v>
+        <v>760.33</v>
       </c>
       <c r="J5" t="n">
-        <v>740.53</v>
+        <v>734.6799999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>1.12</v>
+        <v>3.48</v>
       </c>
       <c r="L5" t="n">
-        <v>0.16072</v>
+        <v>0.45732</v>
       </c>
       <c r="M5" t="n">
-        <v>133161695.81</v>
+        <v>133161510.7</v>
       </c>
       <c r="N5" t="n">
-        <v>133161685.82</v>
+        <v>133161494.2</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-07T14:55:20.000Z</t>
+          <t>2026-09-08T13:25:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260907T145846Z-c22ca5</t>
+          <t>20260908T132838Z-1cee9e</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -788,25 +788,25 @@
         <v>1.4</v>
       </c>
       <c r="F6" t="n">
-        <v>87790603215</v>
+        <v>87873524544</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>1905204251</v>
+        <v>1856362704</v>
       </c>
       <c r="I6" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="J6" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.01164624825002725</v>
+        <v>-0.01193590122546562</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.79796</v>
+        <v>-0.80897</v>
       </c>
       <c r="M6" t="n">
         <v>62744504852</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-07T14:55:20.000Z</t>
+          <t>2026-09-08T13:25:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260907T145846Z-c22ca5</t>
+          <t>20260908T132838Z-1cee9e</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999862</v>
+        <v>0.999827</v>
       </c>
       <c r="F7" t="n">
-        <v>74429895164</v>
+        <v>74219309720</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>11849654999</v>
+        <v>13276104278</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0.999974</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999792</v>
+        <v>0.999715</v>
       </c>
       <c r="K7" t="n">
-        <v>-9.6660980189456e-05</v>
+        <v>-9.2116469446624e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.00581</v>
+        <v>-0.00818</v>
       </c>
       <c r="M7" t="n">
-        <v>74438462885.66106</v>
+        <v>74232336773.57265</v>
       </c>
       <c r="N7" t="n">
-        <v>74446493791.62599</v>
+        <v>74268732987.49275</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-07T14:55:20.000Z</t>
+          <t>2026-09-08T13:25:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260907T145846Z-c22ca5</t>
+          <t>20260908T132838Z-1cee9e</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>104.63</v>
+        <v>102.81</v>
       </c>
       <c r="F8" t="n">
-        <v>61334747310</v>
+        <v>60283049312</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>3268333090</v>
+        <v>2909935160</v>
       </c>
       <c r="I8" t="n">
-        <v>106.96</v>
+        <v>105.15</v>
       </c>
       <c r="J8" t="n">
-        <v>103.95</v>
+        <v>102.49</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.190910922008328</v>
+        <v>-2.893527358991747</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.10505</v>
+        <v>-2.71972</v>
       </c>
       <c r="M8" t="n">
-        <v>586166024.1307415</v>
+        <v>586165228.9760597</v>
       </c>
       <c r="N8" t="n">
-        <v>633643310.3873425</v>
+        <v>633642512.3116686</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-07T14:55:20.000Z</t>
+          <t>2026-09-08T13:25:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260907T145846Z-c22ca5</t>
+          <t>20260908T132838Z-1cee9e</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.334807</v>
+        <v>0.338928</v>
       </c>
       <c r="F9" t="n">
-        <v>31789190703</v>
+        <v>32182217370</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>312110607</v>
+        <v>356631460</v>
       </c>
       <c r="I9" t="n">
-        <v>0.337279</v>
+        <v>0.338947</v>
       </c>
       <c r="J9" t="n">
-        <v>0.334766</v>
+        <v>0.333764</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.000286055151930975</v>
+        <v>0.00334657</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.07874</v>
+        <v>1.00395</v>
       </c>
       <c r="M9" t="n">
-        <v>94939385018.58868</v>
+        <v>94940751712.21188</v>
       </c>
       <c r="N9" t="n">
-        <v>94939383860.86168</v>
+        <v>94940753199.32329</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-07T14:55:20.000Z</t>
+          <t>2026-09-08T13:25:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260907T145846Z-c22ca5</t>
+          <t>20260908T132838Z-1cee9e</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1087,7 +1087,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260907T145846Z-c22ca5</t>
+          <t>20260908T132838Z-1cee9e</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1106,34 +1106,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1173.2</v>
+        <v>1157.43</v>
       </c>
       <c r="F11" t="n">
-        <v>19849025512</v>
+        <v>19588906582</v>
       </c>
       <c r="G11" t="n">
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>1283780184</v>
+        <v>913864528</v>
       </c>
       <c r="I11" t="n">
-        <v>1249.28</v>
+        <v>1184.29</v>
       </c>
       <c r="J11" t="n">
-        <v>1153.85</v>
+        <v>1115.46</v>
       </c>
       <c r="K11" t="n">
-        <v>11.19</v>
+        <v>-29.82380545707224</v>
       </c>
       <c r="L11" t="n">
-        <v>0.79725</v>
+        <v>-2.4627</v>
       </c>
       <c r="M11" t="n">
-        <v>16919136.1030448</v>
+        <v>16919759.5405448</v>
       </c>
       <c r="N11" t="n">
-        <v>16919603.2905448</v>
+        <v>16921262.6655448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1145,14 +1145,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-07T14:55:20.000Z</t>
+          <t>2026-09-08T13:25:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260907T145846Z-c22ca5</t>
+          <t>20260908T132838Z-1cee9e</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1171,28 +1171,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>86.79000000000001</v>
+        <v>82.78</v>
       </c>
       <c r="F12" t="n">
-        <v>19312568388</v>
+        <v>18418083322</v>
       </c>
       <c r="G12" t="n">
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>1293943906</v>
+        <v>1065432359</v>
       </c>
       <c r="I12" t="n">
-        <v>89.47</v>
+        <v>87.66</v>
       </c>
       <c r="J12" t="n">
-        <v>86.09</v>
+        <v>82.7</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.307690637938222</v>
+        <v>-5.199443310753225</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.57363</v>
+        <v>-5.92416</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1210,14 +1210,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-07T14:55:20.000Z</t>
+          <t>2026-09-08T13:25:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260907T145846Z-c22ca5</t>
+          <t>20260908T132838Z-1cee9e</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1236,34 +1236,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.09057800000000001</v>
+        <v>0.089368</v>
       </c>
       <c r="F13" t="n">
-        <v>14110684519</v>
+        <v>13926785926</v>
       </c>
       <c r="G13" t="n">
         <v>11</v>
       </c>
       <c r="H13" t="n">
-        <v>783869671</v>
+        <v>838176065</v>
       </c>
       <c r="I13" t="n">
-        <v>0.091742</v>
+        <v>0.091586</v>
       </c>
       <c r="J13" t="n">
-        <v>0.08817899999999999</v>
+        <v>0.088742</v>
       </c>
       <c r="K13" t="n">
-        <v>0.00192907</v>
+        <v>-0.002357967116344742</v>
       </c>
       <c r="L13" t="n">
-        <v>2.23945</v>
+        <v>-2.48255</v>
       </c>
       <c r="M13" t="n">
-        <v>155817046383.7052</v>
+        <v>155830216383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>171530173126.579</v>
+        <v>171542663126.579</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1275,14 +1275,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-07T14:55:20.000Z</t>
+          <t>2026-09-08T13:25:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260907T145846Z-c22ca5</t>
+          <t>20260908T132838Z-1cee9e</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1301,34 +1301,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.01642947</v>
+        <v>0.01673579</v>
       </c>
       <c r="F14" t="n">
-        <v>11652058418</v>
+        <v>11861320246</v>
       </c>
       <c r="G14" t="n">
         <v>12</v>
       </c>
       <c r="H14" t="n">
-        <v>28003652</v>
+        <v>18206033</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0168531</v>
+        <v>0.01702228</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01644404</v>
+        <v>0.01622091</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.000401803670891002</v>
+        <v>0.00021198</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.41006</v>
+        <v>1.29186</v>
       </c>
       <c r="M14" t="n">
-        <v>709208086630.5371</v>
+        <v>709209449466.9087</v>
       </c>
       <c r="N14" t="n">
-        <v>1142408537396.226</v>
+        <v>1142408531162.713</v>
       </c>
       <c r="O14" t="n">
         <v>0.01946402</v>
@@ -1340,274 +1340,274 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-09-07T14:55:20.000Z</t>
+          <t>2026-09-08T13:25:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260907T145846Z-c22ca5</t>
+          <t>20260908T132838Z-1cee9e</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>monero</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>xmr</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Monero</t>
+          <t>USDS</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>536.79</v>
+        <v>0.999646</v>
       </c>
       <c r="F15" t="n">
-        <v>10090294482</v>
+        <v>9842989591</v>
       </c>
       <c r="G15" t="n">
         <v>13</v>
       </c>
       <c r="H15" t="n">
-        <v>128059809</v>
+        <v>136893786</v>
       </c>
       <c r="I15" t="n">
-        <v>546.23</v>
+        <v>0.999985</v>
       </c>
       <c r="J15" t="n">
-        <v>522.6900000000001</v>
+        <v>0.999621</v>
       </c>
       <c r="K15" t="n">
-        <v>7.5</v>
+        <v>-0.000218243070376878</v>
       </c>
       <c r="L15" t="n">
-        <v>1.38272</v>
+        <v>-0.01687</v>
       </c>
       <c r="M15" t="n">
-        <v>18801531.99160966</v>
+        <v>9846522859.866425</v>
       </c>
       <c r="N15" t="n">
-        <v>18801559.59019433</v>
+        <v>9843382303.043961</v>
       </c>
       <c r="O15" t="n">
-        <v>797.73</v>
+        <v>1.057</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-01-14T11:34:07.000Z</t>
+          <t>2024-10-28T21:40:51.000Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-09-07T14:55:20.000Z</t>
+          <t>2026-09-08T13:25:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260907T145846Z-c22ca5</t>
+          <t>20260908T132838Z-1cee9e</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>monero</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>xmr</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>USDS</t>
+          <t>Monero</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.999797</v>
+        <v>500.87</v>
       </c>
       <c r="F16" t="n">
-        <v>9848004350</v>
+        <v>9417627268</v>
       </c>
       <c r="G16" t="n">
         <v>14</v>
       </c>
       <c r="H16" t="n">
-        <v>101081919</v>
+        <v>118275082</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>537.03</v>
       </c>
       <c r="J16" t="n">
-        <v>0.999631</v>
+        <v>502.78</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.000124456003702367</v>
+        <v>-35.94699426738242</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.009379999999999999</v>
+        <v>-6.71591</v>
       </c>
       <c r="M16" t="n">
-        <v>9849826110.139755</v>
+        <v>18801924.9784335</v>
       </c>
       <c r="N16" t="n">
-        <v>9846533593.644836</v>
+        <v>18801950.77826646</v>
       </c>
       <c r="O16" t="n">
-        <v>1.057</v>
+        <v>797.73</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2024-10-28T21:40:51.000Z</t>
+          <t>2026-01-14T11:34:07.000Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-09-07T14:55:20.000Z</t>
+          <t>2026-09-08T13:25:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260907T145846Z-c22ca5</t>
+          <t>20260908T132838Z-1cee9e</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>whitebit</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>wbt</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>WhiteBIT Coin</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>13.04</v>
+        <v>79.63</v>
       </c>
       <c r="F17" t="n">
-        <v>9760443017</v>
+        <v>9397094183</v>
       </c>
       <c r="G17" t="n">
         <v>15</v>
       </c>
       <c r="H17" t="n">
-        <v>881960287</v>
+        <v>107408999</v>
       </c>
       <c r="I17" t="n">
-        <v>13.67</v>
+        <v>80.02</v>
       </c>
       <c r="J17" t="n">
-        <v>12.12</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.863357</v>
+        <v>6.17</v>
       </c>
       <c r="L17" t="n">
-        <v>7.13279</v>
+        <v>8.505520000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>748099970.424884</v>
+        <v>117956019</v>
       </c>
       <c r="N17" t="n">
-        <v>1000000000</v>
+        <v>293606018</v>
       </c>
       <c r="O17" t="n">
-        <v>52.7</v>
+        <v>80.02</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2021-05-09T16:13:57.000Z</t>
+          <t>2026-09-08T12:55:30.000Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-09-07T14:55:20.000Z</t>
+          <t>2026-09-08T13:25:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260907T145846Z-c22ca5</t>
+          <t>20260908T132838Z-1cee9e</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>whitebit</t>
+          <t>chainlink</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>wbt</t>
+          <t>link</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>WhiteBIT Coin</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>73.01000000000001</v>
+        <v>12.47</v>
       </c>
       <c r="F18" t="n">
-        <v>8613578245</v>
+        <v>9337879909</v>
       </c>
       <c r="G18" t="n">
         <v>16</v>
       </c>
       <c r="H18" t="n">
-        <v>68514591</v>
+        <v>942480076</v>
       </c>
       <c r="I18" t="n">
-        <v>74.25</v>
+        <v>13.16</v>
       </c>
       <c r="J18" t="n">
-        <v>72.98999999999999</v>
+        <v>12.44</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3217745450649119</v>
+        <v>-0.7995158349880072</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.40532</v>
+        <v>-5.98914</v>
       </c>
       <c r="M18" t="n">
-        <v>117956019</v>
+        <v>748099970.424884</v>
       </c>
       <c r="N18" t="n">
-        <v>293606018</v>
+        <v>1000000000</v>
       </c>
       <c r="O18" t="n">
-        <v>74.97</v>
+        <v>52.7</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-08-25T02:42:30.000Z</t>
+          <t>2021-05-09T16:13:57.000Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-09-07T14:55:20.000Z</t>
+          <t>2026-09-08T13:25:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260907T145846Z-c22ca5</t>
+          <t>20260908T132838Z-1cee9e</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1626,28 +1626,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>9.15</v>
+        <v>9.18</v>
       </c>
       <c r="F19" t="n">
-        <v>8418541168</v>
+        <v>8446194637</v>
       </c>
       <c r="G19" t="n">
         <v>17</v>
       </c>
       <c r="H19" t="n">
-        <v>601096</v>
+        <v>221727</v>
       </c>
       <c r="I19" t="n">
-        <v>9.41</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>8.81</v>
+        <v>9.15</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.1772484978069055</v>
+        <v>0.00137277</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.9007</v>
+        <v>0.01404</v>
       </c>
       <c r="M19" t="n">
         <v>919857851.9</v>
@@ -1665,14 +1665,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-09-07T14:55:20.000Z</t>
+          <t>2026-09-08T13:25:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260907T145846Z-c22ca5</t>
+          <t>20260908T132838Z-1cee9e</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1691,28 +1691,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.221773</v>
+        <v>0.219022</v>
       </c>
       <c r="F20" t="n">
-        <v>8319640276</v>
+        <v>8217113911</v>
       </c>
       <c r="G20" t="n">
         <v>18</v>
       </c>
       <c r="H20" t="n">
-        <v>440209788</v>
+        <v>424297258</v>
       </c>
       <c r="I20" t="n">
-        <v>0.226224</v>
+        <v>0.222822</v>
       </c>
       <c r="J20" t="n">
-        <v>0.215287</v>
+        <v>0.21582</v>
       </c>
       <c r="K20" t="n">
-        <v>0.00410905</v>
+        <v>-0.005593066406881175</v>
       </c>
       <c r="L20" t="n">
-        <v>1.89788</v>
+        <v>-2.43569</v>
       </c>
       <c r="M20" t="n">
         <v>37510482444.2993</v>
@@ -1730,14 +1730,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-09-07T14:55:20.000Z</t>
+          <t>2026-09-08T13:25:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260907T145846Z-c22ca5</t>
+          <t>20260908T132838Z-1cee9e</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1756,31 +1756,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.192242</v>
+        <v>0.188401</v>
       </c>
       <c r="F21" t="n">
-        <v>6695445369</v>
+        <v>6557712622</v>
       </c>
       <c r="G21" t="n">
         <v>19</v>
       </c>
       <c r="H21" t="n">
-        <v>227800014</v>
+        <v>201625921</v>
       </c>
       <c r="I21" t="n">
-        <v>0.196218</v>
+        <v>0.194447</v>
       </c>
       <c r="J21" t="n">
-        <v>0.182861</v>
+        <v>0.187011</v>
       </c>
       <c r="K21" t="n">
-        <v>0.008405579999999999</v>
+        <v>-0.005815638001746781</v>
       </c>
       <c r="L21" t="n">
-        <v>4.52481</v>
+        <v>-2.98612</v>
       </c>
       <c r="M21" t="n">
-        <v>34802050139.15266</v>
+        <v>34802042501.18998</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.70248</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-09-07T14:55:20.000Z</t>
+          <t>2026-09-08T13:25:30.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260908T132838Z-1cee9e</t>
+          <t>20260909T013012Z-1a3f96</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>78348</v>
+        <v>78728</v>
       </c>
       <c r="F2" t="n">
-        <v>1573587576688</v>
+        <v>1580114526097</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>30082292059</v>
+        <v>37255171517</v>
       </c>
       <c r="I2" t="n">
         <v>79432</v>
       </c>
       <c r="J2" t="n">
-        <v>78193</v>
+        <v>77666</v>
       </c>
       <c r="K2" t="n">
-        <v>-1271.482630612853</v>
+        <v>-653.9158031940315</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.59094</v>
+        <v>-0.8226599999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>20081356</v>
+        <v>20081584</v>
       </c>
       <c r="N2" t="n">
-        <v>20081431</v>
+        <v>20081628</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-08T13:25:30.000Z</t>
+          <t>2026-09-09T01:27:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260908T132838Z-1cee9e</t>
+          <t>20260909T013012Z-1a3f96</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,28 +590,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2470.09</v>
+        <v>2492.64</v>
       </c>
       <c r="F3" t="n">
-        <v>301482428305</v>
+        <v>304020077819</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>10738190789</v>
+        <v>11910258184</v>
       </c>
       <c r="I3" t="n">
         <v>2505.13</v>
       </c>
       <c r="J3" t="n">
-        <v>2463.89</v>
+        <v>2442.98</v>
       </c>
       <c r="K3" t="n">
-        <v>-38.36756983722034</v>
+        <v>-9.542264194355084</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.49884</v>
+        <v>-0.3947</v>
       </c>
       <c r="M3" t="n">
         <v>122029704.5242925</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-08T13:25:30.000Z</t>
+          <t>2026-09-09T01:27:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260908T132838Z-1cee9e</t>
+          <t>20260909T013012Z-1a3f96</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,34 +655,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999564</v>
+        <v>0.999915</v>
       </c>
       <c r="F4" t="n">
-        <v>183357643237</v>
+        <v>183444550357</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>53434039190</v>
+        <v>58169765758</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999943</v>
+        <v>0.9998860000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999545</v>
+        <v>0.99953</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.000342179458228675</v>
+        <v>7.423999999999999e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.034</v>
+        <v>0.00878</v>
       </c>
       <c r="M4" t="n">
-        <v>183438580383.2119</v>
+        <v>183460193480.142</v>
       </c>
       <c r="N4" t="n">
-        <v>188905526211.2662</v>
+        <v>188927139311.3062</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-08T13:25:30.000Z</t>
+          <t>2026-09-09T01:27:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260908T132838Z-1cee9e</t>
+          <t>20260909T013012Z-1a3f96</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>750.66</v>
+        <v>750.9400000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>99976744355</v>
+        <v>99978566028</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1150532846</v>
+        <v>1257917913</v>
       </c>
       <c r="I5" t="n">
         <v>760.33</v>
       </c>
       <c r="J5" t="n">
-        <v>734.6799999999999</v>
+        <v>737.14</v>
       </c>
       <c r="K5" t="n">
-        <v>3.48</v>
+        <v>8.81</v>
       </c>
       <c r="L5" t="n">
-        <v>0.45732</v>
+        <v>1.19041</v>
       </c>
       <c r="M5" t="n">
-        <v>133161510.7</v>
+        <v>133161436.94</v>
       </c>
       <c r="N5" t="n">
-        <v>133161494.2</v>
+        <v>133161433.13</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-08T13:25:30.000Z</t>
+          <t>2026-09-09T01:27:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260908T132838Z-1cee9e</t>
+          <t>20260909T013012Z-1a3f96</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="F6" t="n">
-        <v>87873524544</v>
+        <v>88631923759</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>1856362704</v>
+        <v>2420690203</v>
       </c>
       <c r="I6" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="J6" t="n">
         <v>1.38</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.01193590122546562</v>
+        <v>0.008915569999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.80897</v>
+        <v>0.61812</v>
       </c>
       <c r="M6" t="n">
         <v>62744504852</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-08T13:25:30.000Z</t>
+          <t>2026-09-09T01:27:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260908T132838Z-1cee9e</t>
+          <t>20260909T013012Z-1a3f96</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999827</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>74219309720</v>
+        <v>74510066780</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>13276104278</v>
+        <v>15182410888</v>
       </c>
       <c r="I7" t="n">
-        <v>0.999974</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0.999715</v>
       </c>
       <c r="K7" t="n">
-        <v>-9.2116469446624e-05</v>
+        <v>9.574e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.00818</v>
+        <v>0.01075</v>
       </c>
       <c r="M7" t="n">
-        <v>74232336773.57265</v>
+        <v>74510139001.71434</v>
       </c>
       <c r="N7" t="n">
-        <v>74268732987.49275</v>
+        <v>74506121772.26845</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-08T13:25:30.000Z</t>
+          <t>2026-09-09T01:27:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260908T132838Z-1cee9e</t>
+          <t>20260909T013012Z-1a3f96</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102.81</v>
+        <v>103.55</v>
       </c>
       <c r="F8" t="n">
-        <v>60283049312</v>
+        <v>60664095976</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>2909935160</v>
+        <v>2996420083</v>
       </c>
       <c r="I8" t="n">
-        <v>105.15</v>
+        <v>104.71</v>
       </c>
       <c r="J8" t="n">
-        <v>102.49</v>
+        <v>101.79</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.893527358991747</v>
+        <v>-0.716759083677232</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.71972</v>
+        <v>-0.69877</v>
       </c>
       <c r="M8" t="n">
-        <v>586165228.9760597</v>
+        <v>586250953.6924145</v>
       </c>
       <c r="N8" t="n">
-        <v>633642512.3116686</v>
+        <v>633737181.8916483</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-08T13:25:30.000Z</t>
+          <t>2026-09-09T01:27:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260908T132838Z-1cee9e</t>
+          <t>20260909T013012Z-1a3f96</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.338928</v>
+        <v>0.338909</v>
       </c>
       <c r="F9" t="n">
-        <v>32182217370</v>
+        <v>32171779577</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>356631460</v>
+        <v>389915756</v>
       </c>
       <c r="I9" t="n">
-        <v>0.338947</v>
+        <v>0.339911</v>
       </c>
       <c r="J9" t="n">
-        <v>0.333764</v>
+        <v>0.334612</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00334657</v>
+        <v>0.00435562</v>
       </c>
       <c r="L9" t="n">
-        <v>1.00395</v>
+        <v>1.28692</v>
       </c>
       <c r="M9" t="n">
-        <v>94940751712.21188</v>
+        <v>94940716339.51509</v>
       </c>
       <c r="N9" t="n">
-        <v>94940753199.32329</v>
+        <v>94941426383.73468</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-08T13:25:30.000Z</t>
+          <t>2026-09-09T01:27:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260908T132838Z-1cee9e</t>
+          <t>20260909T013012Z-1a3f96</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,30 +1045,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.055</v>
+        <v>1.035</v>
       </c>
       <c r="F10" t="n">
-        <v>23516084575</v>
+        <v>23072109188</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>343538</v>
+        <v>34091424</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1.051</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>22290650137.398</v>
+        <v>22290610113.348</v>
       </c>
       <c r="N10" t="n">
-        <v>22292012681.268</v>
+        <v>22290610113.348</v>
       </c>
       <c r="O10" t="n">
         <v>1.061</v>
@@ -1080,14 +1080,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-09-05T22:40:20.000Z</t>
+          <t>2026-09-09T01:27:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260908T132838Z-1cee9e</t>
+          <t>20260909T013012Z-1a3f96</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1106,34 +1106,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1157.43</v>
+        <v>1180.3</v>
       </c>
       <c r="F11" t="n">
-        <v>19588906582</v>
+        <v>19967222607</v>
       </c>
       <c r="G11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>913864528</v>
+        <v>987804462</v>
       </c>
       <c r="I11" t="n">
-        <v>1184.29</v>
+        <v>1210.35</v>
       </c>
       <c r="J11" t="n">
-        <v>1115.46</v>
+        <v>1117.97</v>
       </c>
       <c r="K11" t="n">
-        <v>-29.82380545707224</v>
+        <v>34.76</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.4627</v>
+        <v>2.96045</v>
       </c>
       <c r="M11" t="n">
-        <v>16919759.5405448</v>
+        <v>16921867.3530448</v>
       </c>
       <c r="N11" t="n">
-        <v>16921262.6655448</v>
+        <v>16922134.5405448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1145,14 +1145,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-08T13:25:30.000Z</t>
+          <t>2026-09-09T01:27:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260908T132838Z-1cee9e</t>
+          <t>20260909T013012Z-1a3f96</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1171,28 +1171,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>82.78</v>
+        <v>85.58</v>
       </c>
       <c r="F12" t="n">
-        <v>18418083322</v>
+        <v>19030923082</v>
       </c>
       <c r="G12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>1065432359</v>
+        <v>1050051372</v>
       </c>
       <c r="I12" t="n">
-        <v>87.66</v>
+        <v>85.8</v>
       </c>
       <c r="J12" t="n">
-        <v>82.7</v>
+        <v>81.66</v>
       </c>
       <c r="K12" t="n">
-        <v>-5.199443310753225</v>
+        <v>0.321021</v>
       </c>
       <c r="L12" t="n">
-        <v>-5.92416</v>
+        <v>0.33886</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1210,14 +1210,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-08T13:25:30.000Z</t>
+          <t>2026-09-09T01:27:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260908T132838Z-1cee9e</t>
+          <t>20260909T013012Z-1a3f96</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1236,34 +1236,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.089368</v>
+        <v>0.09009399999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>13926785926</v>
+        <v>14017221157</v>
       </c>
       <c r="G13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>838176065</v>
+        <v>872758169</v>
       </c>
       <c r="I13" t="n">
-        <v>0.091586</v>
+        <v>0.091417</v>
       </c>
       <c r="J13" t="n">
-        <v>0.088742</v>
+        <v>0.088076</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.002357967116344742</v>
+        <v>-0.001347749905187684</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.48255</v>
+        <v>-1.46593</v>
       </c>
       <c r="M13" t="n">
-        <v>155830216383.7052</v>
+        <v>155835036383.7053</v>
       </c>
       <c r="N13" t="n">
-        <v>171542663126.579</v>
+        <v>171549433126.579</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1275,14 +1275,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-08T13:25:30.000Z</t>
+          <t>2026-09-09T01:27:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260908T132838Z-1cee9e</t>
+          <t>20260909T013012Z-1a3f96</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1301,34 +1301,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.01673579</v>
+        <v>0.01614377</v>
       </c>
       <c r="F14" t="n">
-        <v>11861320246</v>
+        <v>11443659114</v>
       </c>
       <c r="G14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>18206033</v>
+        <v>21214532</v>
       </c>
       <c r="I14" t="n">
         <v>0.01702228</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01622091</v>
+        <v>0.01614836</v>
       </c>
       <c r="K14" t="n">
-        <v>0.00021198</v>
+        <v>-0.000189746977732479</v>
       </c>
       <c r="L14" t="n">
-        <v>1.29186</v>
+        <v>-1.17884</v>
       </c>
       <c r="M14" t="n">
-        <v>709209449466.9087</v>
+        <v>709209721455.2999</v>
       </c>
       <c r="N14" t="n">
-        <v>1142408531162.713</v>
+        <v>1142408530745.808</v>
       </c>
       <c r="O14" t="n">
         <v>0.01946402</v>
@@ -1340,14 +1340,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-09-08T13:25:30.000Z</t>
+          <t>2026-09-09T01:27:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260908T132838Z-1cee9e</t>
+          <t>20260909T013012Z-1a3f96</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1366,34 +1366,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.999646</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>9842989591</v>
+        <v>9843016686</v>
       </c>
       <c r="G15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>136893786</v>
+        <v>207540681</v>
       </c>
       <c r="I15" t="n">
-        <v>0.999985</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.999621</v>
+        <v>0.999617</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.000218243070376878</v>
+        <v>0.00027099</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.01687</v>
+        <v>0.01853</v>
       </c>
       <c r="M15" t="n">
-        <v>9846522859.866425</v>
+        <v>9842539599.706585</v>
       </c>
       <c r="N15" t="n">
-        <v>9843382303.043961</v>
+        <v>9840532124.231136</v>
       </c>
       <c r="O15" t="n">
         <v>1.057</v>
@@ -1405,209 +1405,209 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-09-08T13:25:30.000Z</t>
+          <t>2026-09-09T01:27:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260908T132838Z-1cee9e</t>
+          <t>20260909T013012Z-1a3f96</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>monero</t>
+          <t>whitebit</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>xmr</t>
+          <t>wbt</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Monero</t>
+          <t>WhiteBIT Coin</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>500.87</v>
+        <v>81.55</v>
       </c>
       <c r="F16" t="n">
-        <v>9417627268</v>
+        <v>9609492977</v>
       </c>
       <c r="G16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>118275082</v>
+        <v>117604843</v>
       </c>
       <c r="I16" t="n">
-        <v>537.03</v>
+        <v>82.52</v>
       </c>
       <c r="J16" t="n">
-        <v>502.78</v>
+        <v>75.77</v>
       </c>
       <c r="K16" t="n">
-        <v>-35.94699426738242</v>
+        <v>4.69</v>
       </c>
       <c r="L16" t="n">
-        <v>-6.71591</v>
+        <v>6.09555</v>
       </c>
       <c r="M16" t="n">
-        <v>18801924.9784335</v>
+        <v>117919967</v>
       </c>
       <c r="N16" t="n">
-        <v>18801950.77826646</v>
+        <v>293569966</v>
       </c>
       <c r="O16" t="n">
-        <v>797.73</v>
+        <v>82.52</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-01-14T11:34:07.000Z</t>
+          <t>2026-09-09T00:48:20.000Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-09-08T13:25:30.000Z</t>
+          <t>2026-09-09T01:27:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260908T132838Z-1cee9e</t>
+          <t>20260909T013012Z-1a3f96</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>whitebit</t>
+          <t>chainlink</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>wbt</t>
+          <t>link</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>WhiteBIT Coin</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>79.63</v>
+        <v>12.47</v>
       </c>
       <c r="F17" t="n">
-        <v>9397094183</v>
+        <v>9328126456</v>
       </c>
       <c r="G17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>107408999</v>
+        <v>4292075727</v>
       </c>
       <c r="I17" t="n">
-        <v>80.02</v>
+        <v>12.8</v>
       </c>
       <c r="J17" t="n">
-        <v>72.56999999999999</v>
+        <v>12.35</v>
       </c>
       <c r="K17" t="n">
-        <v>6.17</v>
+        <v>-0.330752862079791</v>
       </c>
       <c r="L17" t="n">
-        <v>8.505520000000001</v>
+        <v>-2.57113</v>
       </c>
       <c r="M17" t="n">
-        <v>117956019</v>
+        <v>748099970.424884</v>
       </c>
       <c r="N17" t="n">
-        <v>293606018</v>
+        <v>1000000000</v>
       </c>
       <c r="O17" t="n">
-        <v>80.02</v>
+        <v>52.7</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-09-08T12:55:30.000Z</t>
+          <t>2021-05-09T16:13:57.000Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-09-08T13:25:30.000Z</t>
+          <t>2026-09-09T01:27:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260908T132838Z-1cee9e</t>
+          <t>20260909T013012Z-1a3f96</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>monero</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>xmr</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>Monero</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>12.47</v>
+        <v>496.04</v>
       </c>
       <c r="F18" t="n">
-        <v>9337879909</v>
+        <v>9314681900</v>
       </c>
       <c r="G18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>942480076</v>
+        <v>128601904</v>
       </c>
       <c r="I18" t="n">
-        <v>13.16</v>
+        <v>525.33</v>
       </c>
       <c r="J18" t="n">
-        <v>12.44</v>
+        <v>493.99</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.7995158349880072</v>
+        <v>-24.21691491878403</v>
       </c>
       <c r="L18" t="n">
-        <v>-5.98914</v>
+        <v>-4.65139</v>
       </c>
       <c r="M18" t="n">
-        <v>748099970.424884</v>
+        <v>18802139.13640226</v>
       </c>
       <c r="N18" t="n">
-        <v>1000000000</v>
+        <v>18802170.33633693</v>
       </c>
       <c r="O18" t="n">
-        <v>52.7</v>
+        <v>797.73</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2021-05-09T16:13:57.000Z</t>
+          <t>2026-01-14T11:34:07.000Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-09-08T13:25:30.000Z</t>
+          <t>2026-09-09T01:27:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260908T132838Z-1cee9e</t>
+          <t>20260909T013012Z-1a3f96</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1626,28 +1626,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>9.18</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>8446194637</v>
+        <v>8474228006</v>
       </c>
       <c r="G19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>221727</v>
+        <v>136526</v>
       </c>
       <c r="I19" t="n">
-        <v>9.279999999999999</v>
+        <v>9.27</v>
       </c>
       <c r="J19" t="n">
-        <v>9.15</v>
+        <v>9.16</v>
       </c>
       <c r="K19" t="n">
-        <v>0.00137277</v>
+        <v>0.01405112</v>
       </c>
       <c r="L19" t="n">
-        <v>0.01404</v>
+        <v>0.18388</v>
       </c>
       <c r="M19" t="n">
         <v>919857851.9</v>
@@ -1665,14 +1665,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-09-08T13:25:30.000Z</t>
+          <t>2026-09-09T01:27:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260908T132838Z-1cee9e</t>
+          <t>20260909T013012Z-1a3f96</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1691,28 +1691,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.219022</v>
+        <v>0.218716</v>
       </c>
       <c r="F20" t="n">
-        <v>8217113911</v>
+        <v>8194134616</v>
       </c>
       <c r="G20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>424297258</v>
+        <v>565945088</v>
       </c>
       <c r="I20" t="n">
-        <v>0.222822</v>
+        <v>0.231823</v>
       </c>
       <c r="J20" t="n">
-        <v>0.21582</v>
+        <v>0.215202</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.005593066406881175</v>
+        <v>-0.003596835227794026</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.43569</v>
+        <v>-1.64603</v>
       </c>
       <c r="M20" t="n">
         <v>37510482444.2993</v>
@@ -1730,14 +1730,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-09-08T13:25:30.000Z</t>
+          <t>2026-09-09T01:27:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260908T132838Z-1cee9e</t>
+          <t>20260909T013012Z-1a3f96</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1756,31 +1756,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.188401</v>
+        <v>0.18795</v>
       </c>
       <c r="F21" t="n">
-        <v>6557712622</v>
+        <v>6533504983</v>
       </c>
       <c r="G21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>201625921</v>
+        <v>185787384</v>
       </c>
       <c r="I21" t="n">
-        <v>0.194447</v>
+        <v>0.19354</v>
       </c>
       <c r="J21" t="n">
-        <v>0.187011</v>
+        <v>0.186398</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.005815638001746781</v>
+        <v>-0.006222802604615635</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.98612</v>
+        <v>-3.32049</v>
       </c>
       <c r="M21" t="n">
-        <v>34802042501.18998</v>
+        <v>34803517247.06119</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.70248</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-09-08T13:25:30.000Z</t>
+          <t>2026-09-09T01:27:20.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>78728</v>
+        <v>79593</v>
       </c>
       <c r="F2" t="n">
-        <v>1580114526097</v>
+        <v>1598364983123</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>37255171517</v>
+        <v>34113961073</v>
       </c>
       <c r="I2" t="n">
-        <v>79432</v>
+        <v>79701</v>
       </c>
       <c r="J2" t="n">
-        <v>77666</v>
+        <v>77888</v>
       </c>
       <c r="K2" t="n">
-        <v>-653.9158031940315</v>
+        <v>1519.73</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.8226599999999999</v>
+        <v>1.94656</v>
       </c>
       <c r="M2" t="n">
-        <v>20081584</v>
+        <v>20081850</v>
       </c>
       <c r="N2" t="n">
-        <v>20081628</v>
+        <v>20081881</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-09T01:27:20.000Z</t>
+          <t>2026-09-09T13:35:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2492.64</v>
+        <v>2515.98</v>
       </c>
       <c r="F3" t="n">
-        <v>304020077819</v>
+        <v>307031455725</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>11910258184</v>
+        <v>12320334940</v>
       </c>
       <c r="I3" t="n">
-        <v>2505.13</v>
+        <v>2521.51</v>
       </c>
       <c r="J3" t="n">
-        <v>2442.98</v>
+        <v>2457.39</v>
       </c>
       <c r="K3" t="n">
-        <v>-9.542264194355084</v>
+        <v>61.6</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.3947</v>
+        <v>2.50979</v>
       </c>
       <c r="M3" t="n">
-        <v>122029704.5242925</v>
+        <v>122032627.1379582</v>
       </c>
       <c r="N3" t="n">
-        <v>122029704.5242924</v>
+        <v>122032627.1379582</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-09T01:27:20.000Z</t>
+          <t>2026-09-09T13:35:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,28 +655,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999915</v>
+        <v>0.999827</v>
       </c>
       <c r="F4" t="n">
-        <v>183444550357</v>
+        <v>183428486563</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>58169765758</v>
+        <v>52915294657</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9998860000000001</v>
+        <v>0.999995</v>
       </c>
       <c r="J4" t="n">
-        <v>0.99953</v>
+        <v>0.99956</v>
       </c>
       <c r="K4" t="n">
-        <v>7.423999999999999e-05</v>
+        <v>0.0002526</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00878</v>
+        <v>0.02527</v>
       </c>
       <c r="M4" t="n">
         <v>183460193480.142</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-09T01:27:20.000Z</t>
+          <t>2026-09-09T13:35:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>750.9400000000001</v>
+        <v>750.04</v>
       </c>
       <c r="F5" t="n">
-        <v>99978566028</v>
+        <v>99876830887</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1257917913</v>
+        <v>923039010</v>
       </c>
       <c r="I5" t="n">
-        <v>760.33</v>
+        <v>757.36</v>
       </c>
       <c r="J5" t="n">
-        <v>737.14</v>
+        <v>746.05</v>
       </c>
       <c r="K5" t="n">
-        <v>8.81</v>
+        <v>2.88</v>
       </c>
       <c r="L5" t="n">
-        <v>1.19041</v>
+        <v>0.38481</v>
       </c>
       <c r="M5" t="n">
-        <v>133161436.94</v>
+        <v>133161358.02</v>
       </c>
       <c r="N5" t="n">
-        <v>133161433.13</v>
+        <v>133161354.33</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-09T01:27:20.000Z</t>
+          <t>2026-09-09T13:35:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="F6" t="n">
-        <v>88631923759</v>
+        <v>90039637527</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>2420690203</v>
+        <v>2699115770</v>
       </c>
       <c r="I6" t="n">
         <v>1.45</v>
       </c>
       <c r="J6" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="K6" t="n">
-        <v>0.008915569999999999</v>
+        <v>0.04390142</v>
       </c>
       <c r="L6" t="n">
-        <v>0.61812</v>
+        <v>3.15584</v>
       </c>
       <c r="M6" t="n">
         <v>62744504852</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-09T01:27:20.000Z</t>
+          <t>2026-09-09T13:35:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0.999918</v>
       </c>
       <c r="F7" t="n">
-        <v>74510066780</v>
+        <v>74323444836</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>15182410888</v>
+        <v>14970939745</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999715</v>
+        <v>0.99979</v>
       </c>
       <c r="K7" t="n">
-        <v>9.574e-05</v>
+        <v>0.00010693</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01075</v>
+        <v>0.0107</v>
       </c>
       <c r="M7" t="n">
-        <v>74510139001.71434</v>
+        <v>74329561446.62111</v>
       </c>
       <c r="N7" t="n">
-        <v>74506121772.26845</v>
+        <v>74328339343.75978</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-09T01:27:20.000Z</t>
+          <t>2026-09-09T13:35:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103.55</v>
+        <v>104.41</v>
       </c>
       <c r="F8" t="n">
-        <v>60664095976</v>
+        <v>61211194221</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>2996420083</v>
+        <v>2888831094</v>
       </c>
       <c r="I8" t="n">
-        <v>104.71</v>
+        <v>105.02</v>
       </c>
       <c r="J8" t="n">
-        <v>101.79</v>
+        <v>102.47</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.716759083677232</v>
+        <v>2.02</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.69877</v>
+        <v>1.97109</v>
       </c>
       <c r="M8" t="n">
-        <v>586250953.6924145</v>
+        <v>586250495.4491609</v>
       </c>
       <c r="N8" t="n">
-        <v>633737181.8916483</v>
+        <v>633736725.8982507</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-09T01:27:20.000Z</t>
+          <t>2026-09-09T13:35:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.338909</v>
+        <v>0.338701</v>
       </c>
       <c r="F9" t="n">
-        <v>32171779577</v>
+        <v>32156956766</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>389915756</v>
+        <v>332831706</v>
       </c>
       <c r="I9" t="n">
         <v>0.339911</v>
       </c>
       <c r="J9" t="n">
-        <v>0.334612</v>
+        <v>0.337749</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00435562</v>
+        <v>-7.553672881799301e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>1.28692</v>
+        <v>-0.0223</v>
       </c>
       <c r="M9" t="n">
-        <v>94940716339.51509</v>
+        <v>94942033418.39418</v>
       </c>
       <c r="N9" t="n">
-        <v>94941426383.73468</v>
+        <v>94942027879.98538</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-09T01:27:20.000Z</t>
+          <t>2026-09-09T13:35:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1048,13 +1048,13 @@
         <v>1.035</v>
       </c>
       <c r="F10" t="n">
-        <v>23072109188</v>
+        <v>23070630036</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>34091424</v>
+        <v>34613377</v>
       </c>
       <c r="I10" t="n">
         <v>1.051</v>
@@ -1080,14 +1080,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-09-09T01:27:20.000Z</t>
+          <t>2026-09-09T13:35:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1106,34 +1106,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1180.3</v>
+        <v>1280.44</v>
       </c>
       <c r="F11" t="n">
-        <v>19967222607</v>
+        <v>21667506605</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>987804462</v>
+        <v>1394137200</v>
       </c>
       <c r="I11" t="n">
-        <v>1210.35</v>
+        <v>1275.68</v>
       </c>
       <c r="J11" t="n">
-        <v>1117.97</v>
+        <v>1144.42</v>
       </c>
       <c r="K11" t="n">
-        <v>34.76</v>
+        <v>132.62</v>
       </c>
       <c r="L11" t="n">
-        <v>2.96045</v>
+        <v>11.55438</v>
       </c>
       <c r="M11" t="n">
         <v>16921867.3530448</v>
       </c>
       <c r="N11" t="n">
-        <v>16922134.5405448</v>
+        <v>16923028.2905448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1145,14 +1145,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-09T01:27:20.000Z</t>
+          <t>2026-09-09T13:35:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1171,28 +1171,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>85.58</v>
+        <v>86.54000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>19030923082</v>
+        <v>19250478039</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>1050051372</v>
+        <v>1058509523</v>
       </c>
       <c r="I12" t="n">
-        <v>85.8</v>
+        <v>86.98</v>
       </c>
       <c r="J12" t="n">
-        <v>81.66</v>
+        <v>82.44</v>
       </c>
       <c r="K12" t="n">
-        <v>0.321021</v>
+        <v>4.04</v>
       </c>
       <c r="L12" t="n">
-        <v>0.33886</v>
+        <v>4.89902</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1210,14 +1210,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-09T01:27:20.000Z</t>
+          <t>2026-09-09T13:35:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1236,34 +1236,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.09009399999999999</v>
+        <v>0.091074</v>
       </c>
       <c r="F13" t="n">
-        <v>14017221157</v>
+        <v>14193446782</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>872758169</v>
+        <v>811744469</v>
       </c>
       <c r="I13" t="n">
-        <v>0.091417</v>
+        <v>0.091515</v>
       </c>
       <c r="J13" t="n">
-        <v>0.088076</v>
+        <v>0.089</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.001347749905187684</v>
+        <v>0.00247604</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.46593</v>
+        <v>2.79468</v>
       </c>
       <c r="M13" t="n">
-        <v>155835036383.7053</v>
+        <v>155844386383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>171549433126.579</v>
+        <v>155844716383.7052</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1275,14 +1275,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-09T01:27:20.000Z</t>
+          <t>2026-09-09T13:35:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1301,34 +1301,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.01614377</v>
+        <v>0.01638259</v>
       </c>
       <c r="F14" t="n">
-        <v>11443659114</v>
+        <v>11618735510</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>21214532</v>
+        <v>39125793</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01702228</v>
+        <v>0.01675249</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01614836</v>
+        <v>0.01591912</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.000189746977732479</v>
+        <v>-0.000182873056705439</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.17884</v>
+        <v>-1.10394</v>
       </c>
       <c r="M14" t="n">
-        <v>709209721455.2999</v>
+        <v>709212380117.7289</v>
       </c>
       <c r="N14" t="n">
-        <v>1142408530745.808</v>
+        <v>1142408526965.963</v>
       </c>
       <c r="O14" t="n">
         <v>0.01946402</v>
@@ -1340,14 +1340,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-09-09T01:27:20.000Z</t>
+          <t>2026-09-09T13:35:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1366,34 +1366,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0.999939</v>
       </c>
       <c r="F15" t="n">
-        <v>9843016686</v>
+        <v>9847281876</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>207540681</v>
+        <v>226871382</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.999617</v>
+        <v>0.999628</v>
       </c>
       <c r="K15" t="n">
-        <v>0.00027099</v>
+        <v>0.00022649</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01853</v>
+        <v>0.02266</v>
       </c>
       <c r="M15" t="n">
-        <v>9842539599.706585</v>
+        <v>9847882071.139385</v>
       </c>
       <c r="N15" t="n">
-        <v>9840532124.231136</v>
+        <v>9851780066.236448</v>
       </c>
       <c r="O15" t="n">
         <v>1.057</v>
@@ -1405,14 +1405,14 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-09-09T01:27:20.000Z</t>
+          <t>2026-09-09T13:35:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1431,28 +1431,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>81.55</v>
+        <v>82.25</v>
       </c>
       <c r="F16" t="n">
-        <v>9609492977</v>
+        <v>9699044618</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>117604843</v>
+        <v>99572519</v>
       </c>
       <c r="I16" t="n">
         <v>82.52</v>
       </c>
       <c r="J16" t="n">
-        <v>75.77</v>
+        <v>79.16</v>
       </c>
       <c r="K16" t="n">
-        <v>4.69</v>
+        <v>2.97</v>
       </c>
       <c r="L16" t="n">
-        <v>6.09555</v>
+        <v>3.74938</v>
       </c>
       <c r="M16" t="n">
         <v>117919967</v>
@@ -1470,144 +1470,144 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-09-09T01:27:20.000Z</t>
+          <t>2026-09-09T13:35:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>monero</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>xmr</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>Monero</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>12.47</v>
+        <v>498.98</v>
       </c>
       <c r="F17" t="n">
-        <v>9328126456</v>
+        <v>9382098083</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>4292075727</v>
+        <v>115458264</v>
       </c>
       <c r="I17" t="n">
-        <v>12.8</v>
+        <v>507.62</v>
       </c>
       <c r="J17" t="n">
-        <v>12.35</v>
+        <v>491.57</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.330752862079791</v>
+        <v>1.62</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.57113</v>
+        <v>0.32548</v>
       </c>
       <c r="M17" t="n">
-        <v>748099970.424884</v>
+        <v>18802391.73259455</v>
       </c>
       <c r="N17" t="n">
-        <v>1000000000</v>
+        <v>18802409.73255417</v>
       </c>
       <c r="O17" t="n">
-        <v>52.7</v>
+        <v>797.73</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2021-05-09T16:13:57.000Z</t>
+          <t>2026-01-14T11:34:07.000Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-09-09T01:27:20.000Z</t>
+          <t>2026-09-09T13:35:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>monero</t>
+          <t>chainlink</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>xmr</t>
+          <t>link</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Monero</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>496.04</v>
+        <v>12.19</v>
       </c>
       <c r="F18" t="n">
-        <v>9314681900</v>
+        <v>9120564871</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>128601904</v>
+        <v>7088637519</v>
       </c>
       <c r="I18" t="n">
-        <v>525.33</v>
+        <v>12.77</v>
       </c>
       <c r="J18" t="n">
-        <v>493.99</v>
+        <v>11.98</v>
       </c>
       <c r="K18" t="n">
-        <v>-24.21691491878403</v>
+        <v>-0.2184760733722584</v>
       </c>
       <c r="L18" t="n">
-        <v>-4.65139</v>
+        <v>-1.76047</v>
       </c>
       <c r="M18" t="n">
-        <v>18802139.13640226</v>
+        <v>748099970.424884</v>
       </c>
       <c r="N18" t="n">
-        <v>18802170.33633693</v>
+        <v>1000000000</v>
       </c>
       <c r="O18" t="n">
-        <v>797.73</v>
+        <v>52.7</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-01-14T11:34:07.000Z</t>
+          <t>2021-05-09T16:13:57.000Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-09-09T01:27:20.000Z</t>
+          <t>2026-09-09T13:35:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1626,28 +1626,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>9.210000000000001</v>
+        <v>9.19</v>
       </c>
       <c r="F19" t="n">
-        <v>8474228006</v>
+        <v>8456838824</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>136526</v>
+        <v>163052</v>
       </c>
       <c r="I19" t="n">
-        <v>9.27</v>
+        <v>9.26</v>
       </c>
       <c r="J19" t="n">
-        <v>9.16</v>
+        <v>9.17</v>
       </c>
       <c r="K19" t="n">
-        <v>0.01405112</v>
+        <v>0.01153524</v>
       </c>
       <c r="L19" t="n">
-        <v>0.18388</v>
+        <v>0.12563</v>
       </c>
       <c r="M19" t="n">
         <v>919857851.9</v>
@@ -1665,14 +1665,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-09-09T01:27:20.000Z</t>
+          <t>2026-09-09T13:35:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1691,28 +1691,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.218716</v>
+        <v>0.220656</v>
       </c>
       <c r="F20" t="n">
-        <v>8194134616</v>
+        <v>8276912044</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>565945088</v>
+        <v>578223441</v>
       </c>
       <c r="I20" t="n">
         <v>0.231823</v>
       </c>
       <c r="J20" t="n">
-        <v>0.215202</v>
+        <v>0.216151</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.003596835227794026</v>
+        <v>0.00384314</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.64603</v>
+        <v>1.77256</v>
       </c>
       <c r="M20" t="n">
         <v>37510482444.2993</v>
@@ -1730,14 +1730,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-09-09T01:27:20.000Z</t>
+          <t>2026-09-09T13:35:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1756,31 +1756,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.18795</v>
+        <v>0.189212</v>
       </c>
       <c r="F21" t="n">
-        <v>6533504983</v>
+        <v>6585243621</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>185787384</v>
+        <v>168338211</v>
       </c>
       <c r="I21" t="n">
         <v>0.19354</v>
       </c>
       <c r="J21" t="n">
-        <v>0.186398</v>
+        <v>0.186697</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.006222802604615635</v>
+        <v>0.00201514</v>
       </c>
       <c r="L21" t="n">
-        <v>-3.32049</v>
+        <v>1.07648</v>
       </c>
       <c r="M21" t="n">
-        <v>34803517247.06119</v>
+        <v>34803513020.29381</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.70248</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-09-09T01:27:20.000Z</t>
+          <t>2026-09-09T13:35:30.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>79593</v>
+        <v>76869</v>
       </c>
       <c r="F2" t="n">
-        <v>1598364983123</v>
+        <v>1543780270779</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>34113961073</v>
+        <v>34152452226</v>
       </c>
       <c r="I2" t="n">
-        <v>79701</v>
+        <v>79351</v>
       </c>
       <c r="J2" t="n">
-        <v>77888</v>
+        <v>76748</v>
       </c>
       <c r="K2" t="n">
-        <v>1519.73</v>
+        <v>-2710.455693790631</v>
       </c>
       <c r="L2" t="n">
-        <v>1.94656</v>
+        <v>-3.40595</v>
       </c>
       <c r="M2" t="n">
-        <v>20081850</v>
+        <v>20082225</v>
       </c>
       <c r="N2" t="n">
-        <v>20081881</v>
+        <v>20082365</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-09T13:35:30.000Z</t>
+          <t>2026-09-10T13:27:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2515.98</v>
+        <v>2417.76</v>
       </c>
       <c r="F3" t="n">
-        <v>307031455725</v>
+        <v>295019194043</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>12320334940</v>
+        <v>13585995467</v>
       </c>
       <c r="I3" t="n">
-        <v>2521.51</v>
+        <v>2513.05</v>
       </c>
       <c r="J3" t="n">
-        <v>2457.39</v>
+        <v>2413.62</v>
       </c>
       <c r="K3" t="n">
-        <v>61.6</v>
+        <v>-96.6624874395302</v>
       </c>
       <c r="L3" t="n">
-        <v>2.50979</v>
+        <v>-3.84432</v>
       </c>
       <c r="M3" t="n">
-        <v>122032627.1379582</v>
+        <v>122035556.7865035</v>
       </c>
       <c r="N3" t="n">
-        <v>122032627.1379582</v>
+        <v>122035556.7865035</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-09T13:35:30.000Z</t>
+          <t>2026-09-10T13:27:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,34 +655,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999827</v>
+        <v>0.999689</v>
       </c>
       <c r="F4" t="n">
-        <v>183428486563</v>
+        <v>183399747382</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>52915294657</v>
+        <v>57650362193</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999995</v>
+        <v>0.999919</v>
       </c>
       <c r="J4" t="n">
-        <v>0.99956</v>
+        <v>0.9995579999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0002526</v>
+        <v>-0.000115082843732628</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02527</v>
+        <v>-0.01151</v>
       </c>
       <c r="M4" t="n">
-        <v>183460193480.142</v>
+        <v>183460843383.6048</v>
       </c>
       <c r="N4" t="n">
-        <v>188927139311.3062</v>
+        <v>188927789268.3162</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-09T13:35:30.000Z</t>
+          <t>2026-09-10T13:27:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>750.04</v>
+        <v>706.52</v>
       </c>
       <c r="F5" t="n">
-        <v>99876830887</v>
+        <v>94081938222</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>923039010</v>
+        <v>1262140120</v>
       </c>
       <c r="I5" t="n">
-        <v>757.36</v>
+        <v>746.28</v>
       </c>
       <c r="J5" t="n">
-        <v>746.05</v>
+        <v>704.86</v>
       </c>
       <c r="K5" t="n">
-        <v>2.88</v>
+        <v>-43.96882713677849</v>
       </c>
       <c r="L5" t="n">
-        <v>0.38481</v>
+        <v>-5.85871</v>
       </c>
       <c r="M5" t="n">
-        <v>133161358.02</v>
+        <v>133161225.51</v>
       </c>
       <c r="N5" t="n">
-        <v>133161354.33</v>
+        <v>133161220.23</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-09T13:35:30.000Z</t>
+          <t>2026-09-10T13:27:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="F6" t="n">
-        <v>90039637527</v>
+        <v>85090865143</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>2699115770</v>
+        <v>2406497456</v>
       </c>
       <c r="I6" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="J6" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="K6" t="n">
-        <v>0.04390142</v>
+        <v>-0.07915296347920031</v>
       </c>
       <c r="L6" t="n">
-        <v>3.15584</v>
+        <v>-5.51462</v>
       </c>
       <c r="M6" t="n">
         <v>62744504852</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-09T13:35:30.000Z</t>
+          <t>2026-09-10T13:27:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999918</v>
+        <v>0.999729</v>
       </c>
       <c r="F7" t="n">
-        <v>74323444836</v>
+        <v>74294024258</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>14970939745</v>
+        <v>16283054604</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.99979</v>
+        <v>0.999698</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00010693</v>
+        <v>-0.000171072760730695</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0107</v>
+        <v>-0.01711</v>
       </c>
       <c r="M7" t="n">
-        <v>74329561446.62111</v>
+        <v>74315470373.78728</v>
       </c>
       <c r="N7" t="n">
-        <v>74328339343.75978</v>
+        <v>74331256693.94714</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-09T13:35:30.000Z</t>
+          <t>2026-09-10T13:27:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>104.41</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>61211194221</v>
+        <v>58279078429</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>2888831094</v>
+        <v>3474521512</v>
       </c>
       <c r="I8" t="n">
-        <v>105.02</v>
+        <v>104.12</v>
       </c>
       <c r="J8" t="n">
-        <v>102.47</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>2.02</v>
+        <v>-5.139863338806535</v>
       </c>
       <c r="L8" t="n">
-        <v>1.97109</v>
+        <v>-4.91663</v>
       </c>
       <c r="M8" t="n">
-        <v>586250495.4491609</v>
+        <v>586335632.9426919</v>
       </c>
       <c r="N8" t="n">
-        <v>633736725.8982507</v>
+        <v>633830911.2985152</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-09T13:35:30.000Z</t>
+          <t>2026-09-10T13:27:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.338701</v>
+        <v>0.338163</v>
       </c>
       <c r="F9" t="n">
-        <v>32156956766</v>
+        <v>32108021382</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>332831706</v>
+        <v>386070975</v>
       </c>
       <c r="I9" t="n">
-        <v>0.339911</v>
+        <v>0.340659</v>
       </c>
       <c r="J9" t="n">
-        <v>0.337749</v>
+        <v>0.338005</v>
       </c>
       <c r="K9" t="n">
-        <v>-7.553672881799301e-05</v>
+        <v>-0.00057910542445333</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0223</v>
+        <v>-0.17096</v>
       </c>
       <c r="M9" t="n">
-        <v>94942033418.39418</v>
+        <v>94943377255.82779</v>
       </c>
       <c r="N9" t="n">
-        <v>94942027879.98538</v>
+        <v>94943389284.71849</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-09T13:35:30.000Z</t>
+          <t>2026-09-10T13:27:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,30 +1045,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.035</v>
+        <v>1.027</v>
       </c>
       <c r="F10" t="n">
-        <v>23070630036</v>
+        <v>22977477871</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>34613377</v>
+        <v>115171089</v>
       </c>
       <c r="I10" t="n">
-        <v>1.051</v>
+        <v>1.042</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+        <v>1.019</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0.008331250492084719</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.80491</v>
+      </c>
       <c r="M10" t="n">
-        <v>22290610113.348</v>
+        <v>22379027660.478</v>
       </c>
       <c r="N10" t="n">
-        <v>22290610113.348</v>
+        <v>22379027660.478</v>
       </c>
       <c r="O10" t="n">
         <v>1.061</v>
@@ -1080,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-09-09T13:35:30.000Z</t>
+          <t>2026-09-10T13:27:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1106,34 +1110,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1280.44</v>
+        <v>1174.12</v>
       </c>
       <c r="F11" t="n">
-        <v>21667506605</v>
+        <v>19885889479</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>1394137200</v>
+        <v>1377712454</v>
       </c>
       <c r="I11" t="n">
-        <v>1275.68</v>
+        <v>1293.92</v>
       </c>
       <c r="J11" t="n">
-        <v>1144.42</v>
+        <v>1188.47</v>
       </c>
       <c r="K11" t="n">
-        <v>132.62</v>
+        <v>-90.49896540877694</v>
       </c>
       <c r="L11" t="n">
-        <v>11.55438</v>
+        <v>-7.15622</v>
       </c>
       <c r="M11" t="n">
         <v>16921867.3530448</v>
       </c>
       <c r="N11" t="n">
-        <v>16923028.2905448</v>
+        <v>16924839.2280448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1145,14 +1149,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-09T13:35:30.000Z</t>
+          <t>2026-09-10T13:27:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1171,28 +1175,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>86.54000000000001</v>
+        <v>81.09</v>
       </c>
       <c r="F12" t="n">
-        <v>19250478039</v>
+        <v>18036831345</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>1058509523</v>
+        <v>1321535350</v>
       </c>
       <c r="I12" t="n">
-        <v>86.98</v>
+        <v>86.98999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>82.44</v>
+        <v>80.34</v>
       </c>
       <c r="K12" t="n">
-        <v>4.04</v>
+        <v>-5.605079227248268</v>
       </c>
       <c r="L12" t="n">
-        <v>4.89902</v>
+        <v>-6.46526</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1210,14 +1214,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-09T13:35:30.000Z</t>
+          <t>2026-09-10T13:27:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1236,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.091074</v>
+        <v>0.083634</v>
       </c>
       <c r="F13" t="n">
-        <v>14193446782</v>
+        <v>13029160774</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>811744469</v>
+        <v>945647801</v>
       </c>
       <c r="I13" t="n">
-        <v>0.091515</v>
+        <v>0.09052300000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>0.089</v>
+        <v>0.083463</v>
       </c>
       <c r="K13" t="n">
-        <v>0.00247604</v>
+        <v>-0.007554012353101672</v>
       </c>
       <c r="L13" t="n">
-        <v>2.79468</v>
+        <v>-8.284000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>155844386383.7052</v>
+        <v>155856586383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>155844716383.7052</v>
+        <v>171569863126.5791</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1275,14 +1279,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-09T13:35:30.000Z</t>
+          <t>2026-09-10T13:27:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1301,31 +1305,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.01638259</v>
+        <v>0.0158577</v>
       </c>
       <c r="F14" t="n">
-        <v>11618735510</v>
+        <v>11244080062</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>39125793</v>
+        <v>30442537</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01675249</v>
+        <v>0.01646211</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01591912</v>
+        <v>0.01579631</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.000182873056705439</v>
+        <v>-0.000524735521837818</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.10394</v>
+        <v>-3.20304</v>
       </c>
       <c r="M14" t="n">
-        <v>709212380117.7289</v>
+        <v>709212596238.4149</v>
       </c>
       <c r="N14" t="n">
         <v>1142408526965.963</v>
@@ -1340,14 +1344,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-09-09T13:35:30.000Z</t>
+          <t>2026-09-10T13:27:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1366,34 +1370,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.999939</v>
+        <v>0.99982</v>
       </c>
       <c r="F15" t="n">
-        <v>9847281876</v>
+        <v>9855532483</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>226871382</v>
+        <v>152958451</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.999628</v>
+        <v>0.999687</v>
       </c>
       <c r="K15" t="n">
-        <v>0.00022649</v>
+        <v>-0.000130622034676287</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02266</v>
+        <v>-0.01306</v>
       </c>
       <c r="M15" t="n">
-        <v>9847882071.139385</v>
+        <v>9857520169.204882</v>
       </c>
       <c r="N15" t="n">
-        <v>9851780066.236448</v>
+        <v>9838691287.558218</v>
       </c>
       <c r="O15" t="n">
         <v>1.057</v>
@@ -1405,144 +1409,144 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-09-09T13:35:30.000Z</t>
+          <t>2026-09-10T13:27:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>whitebit</t>
+          <t>monero</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>wbt</t>
+          <t>xmr</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>WhiteBIT Coin</t>
+          <t>Monero</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>82.25</v>
+        <v>502.71</v>
       </c>
       <c r="F16" t="n">
-        <v>9699044618</v>
+        <v>9437409909</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>99572519</v>
+        <v>142179940</v>
       </c>
       <c r="I16" t="n">
-        <v>82.52</v>
+        <v>518.34</v>
       </c>
       <c r="J16" t="n">
-        <v>79.16</v>
+        <v>498.54</v>
       </c>
       <c r="K16" t="n">
-        <v>2.97</v>
+        <v>3.76</v>
       </c>
       <c r="L16" t="n">
-        <v>3.74938</v>
+        <v>0.75295</v>
       </c>
       <c r="M16" t="n">
-        <v>117919967</v>
+        <v>18802821.25212499</v>
       </c>
       <c r="N16" t="n">
-        <v>293569966</v>
+        <v>18802833.85203534</v>
       </c>
       <c r="O16" t="n">
-        <v>82.52</v>
+        <v>797.73</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-09-09T00:48:20.000Z</t>
+          <t>2026-01-14T11:34:07.000Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-09-09T13:35:30.000Z</t>
+          <t>2026-09-10T13:27:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>monero</t>
+          <t>whitebit</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>xmr</t>
+          <t>wbt</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Monero</t>
+          <t>WhiteBIT Coin</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>498.98</v>
+        <v>79.34</v>
       </c>
       <c r="F17" t="n">
-        <v>9382098083</v>
+        <v>9350661300</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>115458264</v>
+        <v>108435650</v>
       </c>
       <c r="I17" t="n">
-        <v>507.62</v>
+        <v>81.98999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>491.57</v>
+        <v>79.22</v>
       </c>
       <c r="K17" t="n">
-        <v>1.62</v>
+        <v>-2.906928747854607</v>
       </c>
       <c r="L17" t="n">
-        <v>0.32548</v>
+        <v>-3.53455</v>
       </c>
       <c r="M17" t="n">
-        <v>18802391.73259455</v>
+        <v>117882016</v>
       </c>
       <c r="N17" t="n">
-        <v>18802409.73255417</v>
+        <v>293532015</v>
       </c>
       <c r="O17" t="n">
-        <v>797.73</v>
+        <v>82.52</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-01-14T11:34:07.000Z</t>
+          <t>2026-09-09T00:48:20.000Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-09-09T13:35:30.000Z</t>
+          <t>2026-09-10T13:27:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1561,28 +1565,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>12.19</v>
+        <v>11.67</v>
       </c>
       <c r="F18" t="n">
-        <v>9120564871</v>
+        <v>8732590784</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>7088637519</v>
+        <v>4027997415</v>
       </c>
       <c r="I18" t="n">
-        <v>12.77</v>
+        <v>12.15</v>
       </c>
       <c r="J18" t="n">
-        <v>11.98</v>
+        <v>11.6</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2184760733722584</v>
+        <v>-0.5381755019183387</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.76047</v>
+        <v>-4.40724</v>
       </c>
       <c r="M18" t="n">
         <v>748099970.424884</v>
@@ -1600,14 +1604,14 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-09-09T13:35:30.000Z</t>
+          <t>2026-09-10T13:27:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1626,28 +1630,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>9.19</v>
+        <v>9.18</v>
       </c>
       <c r="F19" t="n">
-        <v>8456838824</v>
+        <v>8447958234</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>163052</v>
+        <v>103636</v>
       </c>
       <c r="I19" t="n">
-        <v>9.26</v>
+        <v>9.23</v>
       </c>
       <c r="J19" t="n">
         <v>9.17</v>
       </c>
       <c r="K19" t="n">
-        <v>0.01153524</v>
+        <v>-0.009111009906101586</v>
       </c>
       <c r="L19" t="n">
-        <v>0.12563</v>
+        <v>-0.09911</v>
       </c>
       <c r="M19" t="n">
         <v>919857851.9</v>
@@ -1665,14 +1669,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-09-09T13:35:30.000Z</t>
+          <t>2026-09-10T13:27:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1691,28 +1695,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.220656</v>
+        <v>0.209835</v>
       </c>
       <c r="F20" t="n">
-        <v>8276912044</v>
+        <v>7871290286</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>578223441</v>
+        <v>462172278</v>
       </c>
       <c r="I20" t="n">
-        <v>0.231823</v>
+        <v>0.219716</v>
       </c>
       <c r="J20" t="n">
-        <v>0.216151</v>
+        <v>0.208156</v>
       </c>
       <c r="K20" t="n">
-        <v>0.00384314</v>
+        <v>-0.01121438589498572</v>
       </c>
       <c r="L20" t="n">
-        <v>1.77256</v>
+        <v>-5.07325</v>
       </c>
       <c r="M20" t="n">
         <v>37510482444.2993</v>
@@ -1730,14 +1734,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-09-09T13:35:30.000Z</t>
+          <t>2026-09-10T13:27:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1756,31 +1760,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.189212</v>
+        <v>0.177265</v>
       </c>
       <c r="F21" t="n">
-        <v>6585243621</v>
+        <v>6168073836</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>168338211</v>
+        <v>177475184</v>
       </c>
       <c r="I21" t="n">
-        <v>0.19354</v>
+        <v>0.188573</v>
       </c>
       <c r="J21" t="n">
-        <v>0.186697</v>
+        <v>0.176372</v>
       </c>
       <c r="K21" t="n">
-        <v>0.00201514</v>
+        <v>-0.01210439609112118</v>
       </c>
       <c r="L21" t="n">
-        <v>1.07648</v>
+        <v>-6.39196</v>
       </c>
       <c r="M21" t="n">
-        <v>34803513020.29381</v>
+        <v>34807089044.92414</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.70248</v>
@@ -1795,7 +1799,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-09-09T13:35:30.000Z</t>
+          <t>2026-09-10T13:27:20.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>76869</v>
+        <v>77677</v>
       </c>
       <c r="F2" t="n">
-        <v>1543780270779</v>
+        <v>1560125511429</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>34152452226</v>
+        <v>29594094775</v>
       </c>
       <c r="I2" t="n">
-        <v>79351</v>
+        <v>78035</v>
       </c>
       <c r="J2" t="n">
-        <v>76748</v>
+        <v>76393</v>
       </c>
       <c r="K2" t="n">
-        <v>-2710.455693790631</v>
+        <v>800.51</v>
       </c>
       <c r="L2" t="n">
-        <v>-3.40595</v>
+        <v>1.0413</v>
       </c>
       <c r="M2" t="n">
-        <v>20082225</v>
+        <v>20082787</v>
       </c>
       <c r="N2" t="n">
-        <v>20082365</v>
+        <v>20082809</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-10T13:27:20.000Z</t>
+          <t>2026-09-11T13:25:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2417.76</v>
+        <v>2506.31</v>
       </c>
       <c r="F3" t="n">
-        <v>295019194043</v>
+        <v>305935492370</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>13585995467</v>
+        <v>16878541137</v>
       </c>
       <c r="I3" t="n">
-        <v>2513.05</v>
+        <v>2512.29</v>
       </c>
       <c r="J3" t="n">
-        <v>2413.62</v>
+        <v>2428.8</v>
       </c>
       <c r="K3" t="n">
-        <v>-96.6624874395302</v>
+        <v>88.77</v>
       </c>
       <c r="L3" t="n">
-        <v>-3.84432</v>
+        <v>3.67177</v>
       </c>
       <c r="M3" t="n">
-        <v>122035556.7865035</v>
+        <v>122038476.3012703</v>
       </c>
       <c r="N3" t="n">
-        <v>122035556.7865035</v>
+        <v>122038476.3012702</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-10T13:27:20.000Z</t>
+          <t>2026-09-11T13:25:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,28 +655,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999689</v>
+        <v>0.99961</v>
       </c>
       <c r="F4" t="n">
-        <v>183399747382</v>
+        <v>183389557643</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>57650362193</v>
+        <v>58668007467</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999919</v>
+        <v>0.999861</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9995579999999999</v>
+        <v>0.999515</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.000115082843732628</v>
+        <v>-7.4913892993966e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.01151</v>
+        <v>-0.00749</v>
       </c>
       <c r="M4" t="n">
         <v>183460843383.6048</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-10T13:27:20.000Z</t>
+          <t>2026-09-11T13:25:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>706.52</v>
+        <v>720.65</v>
       </c>
       <c r="F5" t="n">
-        <v>94081938222</v>
+        <v>95991544747</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1262140120</v>
+        <v>886998934</v>
       </c>
       <c r="I5" t="n">
-        <v>746.28</v>
+        <v>723.4</v>
       </c>
       <c r="J5" t="n">
-        <v>704.86</v>
+        <v>704.72</v>
       </c>
       <c r="K5" t="n">
-        <v>-43.96882713677849</v>
+        <v>14.1</v>
       </c>
       <c r="L5" t="n">
-        <v>-5.85871</v>
+        <v>1.99581</v>
       </c>
       <c r="M5" t="n">
-        <v>133161225.51</v>
+        <v>133161118.37</v>
       </c>
       <c r="N5" t="n">
-        <v>133161220.23</v>
+        <v>133161113.02</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-10T13:27:20.000Z</t>
+          <t>2026-09-11T13:25:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -788,31 +788,31 @@
         <v>1.36</v>
       </c>
       <c r="F6" t="n">
-        <v>85090865143</v>
+        <v>85628071806</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>2406497456</v>
+        <v>2239415372</v>
       </c>
       <c r="I6" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="J6" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.07915296347920031</v>
+        <v>0.00524616</v>
       </c>
       <c r="L6" t="n">
-        <v>-5.51462</v>
+        <v>0.38688</v>
       </c>
       <c r="M6" t="n">
-        <v>62744504852</v>
+        <v>62879209849</v>
       </c>
       <c r="N6" t="n">
-        <v>99985627691</v>
+        <v>99985622230</v>
       </c>
       <c r="O6" t="n">
         <v>3.65</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-10T13:27:20.000Z</t>
+          <t>2026-09-11T13:25:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999729</v>
+        <v>0.999807</v>
       </c>
       <c r="F7" t="n">
-        <v>74294024258</v>
+        <v>74180090683</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>16283054604</v>
+        <v>16624710113</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999698</v>
+        <v>0.999741</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.000171072760730695</v>
+        <v>8.262000000000001e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.01711</v>
+        <v>0.00826</v>
       </c>
       <c r="M7" t="n">
-        <v>74315470373.78728</v>
+        <v>74193437886.21786</v>
       </c>
       <c r="N7" t="n">
-        <v>74331256693.94714</v>
+        <v>74212582140.11983</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-10T13:27:20.000Z</t>
+          <t>2026-09-11T13:25:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>99.40000000000001</v>
+        <v>101.29</v>
       </c>
       <c r="F8" t="n">
-        <v>58279078429</v>
+        <v>59439992570</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>3474521512</v>
+        <v>3174746581</v>
       </c>
       <c r="I8" t="n">
-        <v>104.12</v>
+        <v>101.74</v>
       </c>
       <c r="J8" t="n">
-        <v>98.90000000000001</v>
+        <v>98.56</v>
       </c>
       <c r="K8" t="n">
-        <v>-5.139863338806535</v>
+        <v>1.9</v>
       </c>
       <c r="L8" t="n">
-        <v>-4.91663</v>
+        <v>1.90687</v>
       </c>
       <c r="M8" t="n">
-        <v>586335632.9426919</v>
+        <v>586537449.1371635</v>
       </c>
       <c r="N8" t="n">
-        <v>633830911.2985152</v>
+        <v>633830009.5093167</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-10T13:27:20.000Z</t>
+          <t>2026-09-11T13:25:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.338163</v>
+        <v>0.336103</v>
       </c>
       <c r="F9" t="n">
-        <v>32108021382</v>
+        <v>31912142968</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>386070975</v>
+        <v>358032118</v>
       </c>
       <c r="I9" t="n">
-        <v>0.340659</v>
+        <v>0.340962</v>
       </c>
       <c r="J9" t="n">
-        <v>0.338005</v>
+        <v>0.335436</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.00057910542445333</v>
+        <v>-0.002159410412531093</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.17096</v>
+        <v>-0.6383799999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>94943377255.82779</v>
+        <v>94944701333.48628</v>
       </c>
       <c r="N9" t="n">
-        <v>94943389284.71849</v>
+        <v>94944700423.18279</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-10T13:27:20.000Z</t>
+          <t>2026-09-11T13:25:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,34 +1045,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.027</v>
+        <v>1.035</v>
       </c>
       <c r="F10" t="n">
-        <v>22977477871</v>
+        <v>23223868031</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>115171089</v>
+        <v>93264084</v>
       </c>
       <c r="I10" t="n">
-        <v>1.042</v>
+        <v>1.036</v>
       </c>
       <c r="J10" t="n">
-        <v>1.019</v>
+        <v>1.015</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.008331250492084719</v>
+        <v>0.007932140000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.80491</v>
+        <v>0.77257</v>
       </c>
       <c r="M10" t="n">
-        <v>22379027660.478</v>
+        <v>22446057111.938</v>
       </c>
       <c r="N10" t="n">
-        <v>22379027660.478</v>
+        <v>22446057111.938</v>
       </c>
       <c r="O10" t="n">
         <v>1.061</v>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-09-10T13:27:20.000Z</t>
+          <t>2026-09-11T13:25:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,34 +1110,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1174.12</v>
+        <v>1158.21</v>
       </c>
       <c r="F11" t="n">
-        <v>19885889479</v>
+        <v>19616404230</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>1377712454</v>
+        <v>1671260451</v>
       </c>
       <c r="I11" t="n">
-        <v>1293.92</v>
+        <v>1183.37</v>
       </c>
       <c r="J11" t="n">
-        <v>1188.47</v>
+        <v>1055.58</v>
       </c>
       <c r="K11" t="n">
-        <v>-90.49896540877694</v>
+        <v>-17.24410873122633</v>
       </c>
       <c r="L11" t="n">
-        <v>-7.15622</v>
+        <v>-1.46702</v>
       </c>
       <c r="M11" t="n">
-        <v>16921867.3530448</v>
+        <v>16925695.4780448</v>
       </c>
       <c r="N11" t="n">
-        <v>16924839.2280448</v>
+        <v>16926651.7280448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1149,14 +1149,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-10T13:27:20.000Z</t>
+          <t>2026-09-11T13:25:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,28 +1175,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>81.09</v>
+        <v>81.20999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>18036831345</v>
+        <v>18098825995</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>1321535350</v>
+        <v>1095111848</v>
       </c>
       <c r="I12" t="n">
-        <v>86.98999999999999</v>
+        <v>82.09</v>
       </c>
       <c r="J12" t="n">
-        <v>80.34</v>
+        <v>78.27</v>
       </c>
       <c r="K12" t="n">
-        <v>-5.605079227248268</v>
+        <v>0.123405</v>
       </c>
       <c r="L12" t="n">
-        <v>-6.46526</v>
+        <v>0.15219</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1214,14 +1214,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-10T13:27:20.000Z</t>
+          <t>2026-09-11T13:25:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.083634</v>
+        <v>0.0848</v>
       </c>
       <c r="F13" t="n">
-        <v>13029160774</v>
+        <v>13224091428</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>945647801</v>
+        <v>678267919</v>
       </c>
       <c r="I13" t="n">
-        <v>0.09052300000000001</v>
+        <v>0.085089</v>
       </c>
       <c r="J13" t="n">
-        <v>0.083463</v>
+        <v>0.082747</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.007554012353101672</v>
+        <v>0.00124017</v>
       </c>
       <c r="L13" t="n">
-        <v>-8.284000000000001</v>
+        <v>1.48417</v>
       </c>
       <c r="M13" t="n">
-        <v>155856586383.7052</v>
+        <v>155871456383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>171569863126.5791</v>
+        <v>155871546383.7052</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-10T13:27:20.000Z</t>
+          <t>2026-09-11T13:25:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,31 +1305,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.0158577</v>
+        <v>0.01582451</v>
       </c>
       <c r="F14" t="n">
-        <v>11244080062</v>
+        <v>11227376908</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>30442537</v>
+        <v>39502813</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01646211</v>
+        <v>0.0160076</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01579631</v>
+        <v>0.01551577</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.000524735521837818</v>
+        <v>-3.0215214789967e-05</v>
       </c>
       <c r="L14" t="n">
-        <v>-3.20304</v>
+        <v>-0.19058</v>
       </c>
       <c r="M14" t="n">
-        <v>709212596238.4149</v>
+        <v>709212992829.0042</v>
       </c>
       <c r="N14" t="n">
         <v>1142408526965.963</v>
@@ -1344,14 +1344,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-09-10T13:27:20.000Z</t>
+          <t>2026-09-11T13:25:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1370,34 +1370,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.99982</v>
+        <v>0.999744</v>
       </c>
       <c r="F15" t="n">
-        <v>9855532483</v>
+        <v>9744724175</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>152958451</v>
+        <v>197400586</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0.999936</v>
       </c>
       <c r="J15" t="n">
-        <v>0.999687</v>
+        <v>0.999592</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.000130622034676287</v>
+        <v>-7.2646757613426e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.01306</v>
+        <v>-0.00727</v>
       </c>
       <c r="M15" t="n">
-        <v>9857520169.204882</v>
+        <v>9747194186.835777</v>
       </c>
       <c r="N15" t="n">
-        <v>9838691287.558218</v>
+        <v>9748798031.413788</v>
       </c>
       <c r="O15" t="n">
         <v>1.057</v>
@@ -1409,14 +1409,14 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-09-10T13:27:20.000Z</t>
+          <t>2026-09-11T13:25:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1435,34 +1435,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>502.71</v>
+        <v>512.91</v>
       </c>
       <c r="F16" t="n">
-        <v>9437409909</v>
+        <v>9645572026</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>142179940</v>
+        <v>102137061</v>
       </c>
       <c r="I16" t="n">
-        <v>518.34</v>
+        <v>518.6799999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>498.54</v>
+        <v>500.26</v>
       </c>
       <c r="K16" t="n">
-        <v>3.76</v>
+        <v>11.01</v>
       </c>
       <c r="L16" t="n">
-        <v>0.75295</v>
+        <v>2.1934</v>
       </c>
       <c r="M16" t="n">
-        <v>18802821.25212499</v>
+        <v>18803154.24465362</v>
       </c>
       <c r="N16" t="n">
-        <v>18802833.85203534</v>
+        <v>18803235.84437571</v>
       </c>
       <c r="O16" t="n">
         <v>797.73</v>
@@ -1474,14 +1474,14 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-09-10T13:27:20.000Z</t>
+          <t>2026-09-11T13:25:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1500,28 +1500,28 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>79.34</v>
+        <v>80.55</v>
       </c>
       <c r="F17" t="n">
-        <v>9350661300</v>
+        <v>9497240871</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>108435650</v>
+        <v>101915128</v>
       </c>
       <c r="I17" t="n">
-        <v>81.98999999999999</v>
+        <v>80.97</v>
       </c>
       <c r="J17" t="n">
-        <v>79.22</v>
+        <v>79</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.906928747854607</v>
+        <v>1.23</v>
       </c>
       <c r="L17" t="n">
-        <v>-3.53455</v>
+        <v>1.54504</v>
       </c>
       <c r="M17" t="n">
         <v>117882016</v>
@@ -1539,14 +1539,14 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-09-10T13:27:20.000Z</t>
+          <t>2026-09-11T13:25:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1565,28 +1565,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>11.67</v>
+        <v>11.69</v>
       </c>
       <c r="F18" t="n">
-        <v>8732590784</v>
+        <v>8749576424</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>4027997415</v>
+        <v>371507695</v>
       </c>
       <c r="I18" t="n">
-        <v>12.15</v>
+        <v>11.72</v>
       </c>
       <c r="J18" t="n">
-        <v>11.6</v>
+        <v>11.31</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5381755019183387</v>
+        <v>0.02035372</v>
       </c>
       <c r="L18" t="n">
-        <v>-4.40724</v>
+        <v>0.17437</v>
       </c>
       <c r="M18" t="n">
         <v>748099970.424884</v>
@@ -1604,14 +1604,14 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-09-10T13:27:20.000Z</t>
+          <t>2026-09-11T13:25:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1630,28 +1630,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>9.18</v>
+        <v>9.15</v>
       </c>
       <c r="F19" t="n">
-        <v>8447958234</v>
+        <v>8418079995</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>103636</v>
+        <v>189958</v>
       </c>
       <c r="I19" t="n">
         <v>9.23</v>
       </c>
       <c r="J19" t="n">
-        <v>9.17</v>
+        <v>9.02</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.009111009906101586</v>
+        <v>-0.03241308782886954</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.09911</v>
+        <v>-0.35293</v>
       </c>
       <c r="M19" t="n">
         <v>919857851.9</v>
@@ -1669,14 +1669,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-09-10T13:27:20.000Z</t>
+          <t>2026-09-11T13:25:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1695,28 +1695,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.209835</v>
+        <v>0.207783</v>
       </c>
       <c r="F20" t="n">
-        <v>7871290286</v>
+        <v>7799990505</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>462172278</v>
+        <v>475922020</v>
       </c>
       <c r="I20" t="n">
-        <v>0.219716</v>
+        <v>0.211947</v>
       </c>
       <c r="J20" t="n">
-        <v>0.208156</v>
+        <v>0.200878</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.01121438589498572</v>
+        <v>-0.002025983797910053</v>
       </c>
       <c r="L20" t="n">
-        <v>-5.07325</v>
+        <v>-0.96563</v>
       </c>
       <c r="M20" t="n">
         <v>37510482444.2993</v>
@@ -1734,14 +1734,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-09-10T13:27:20.000Z</t>
+          <t>2026-09-11T13:25:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1760,31 +1760,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.177265</v>
+        <v>0.1788</v>
       </c>
       <c r="F21" t="n">
-        <v>6168073836</v>
+        <v>6226118444</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>177475184</v>
+        <v>144935960</v>
       </c>
       <c r="I21" t="n">
-        <v>0.188573</v>
+        <v>0.179365</v>
       </c>
       <c r="J21" t="n">
-        <v>0.176372</v>
+        <v>0.173418</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.01210439609112118</v>
+        <v>0.00162509</v>
       </c>
       <c r="L21" t="n">
-        <v>-6.39196</v>
+        <v>0.91722</v>
       </c>
       <c r="M21" t="n">
-        <v>34807089044.92414</v>
+        <v>34811503371.5922</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.70248</v>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-09-10T13:27:20.000Z</t>
+          <t>2026-09-11T13:25:10.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>77677</v>
+        <v>77314</v>
       </c>
       <c r="F2" t="n">
-        <v>1560125511429</v>
+        <v>1552722866590</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>29594094775</v>
+        <v>28639817629</v>
       </c>
       <c r="I2" t="n">
-        <v>78035</v>
+        <v>79607</v>
       </c>
       <c r="J2" t="n">
-        <v>76393</v>
+        <v>76952</v>
       </c>
       <c r="K2" t="n">
-        <v>800.51</v>
+        <v>-262.4575759976724</v>
       </c>
       <c r="L2" t="n">
-        <v>1.0413</v>
+        <v>-0.40435</v>
       </c>
       <c r="M2" t="n">
-        <v>20082787</v>
+        <v>20083262</v>
       </c>
       <c r="N2" t="n">
-        <v>20082809</v>
+        <v>20083312</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-11T13:25:10.000Z</t>
+          <t>2026-09-12T12:44:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2506.31</v>
+        <v>2534.68</v>
       </c>
       <c r="F3" t="n">
-        <v>305935492370</v>
+        <v>309335837072</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>16878541137</v>
+        <v>21125178458</v>
       </c>
       <c r="I3" t="n">
-        <v>2512.29</v>
+        <v>2647.68</v>
       </c>
       <c r="J3" t="n">
-        <v>2428.8</v>
+        <v>2492.31</v>
       </c>
       <c r="K3" t="n">
-        <v>88.77</v>
+        <v>40.13</v>
       </c>
       <c r="L3" t="n">
-        <v>3.67177</v>
+        <v>1.54763</v>
       </c>
       <c r="M3" t="n">
-        <v>122038476.3012703</v>
+        <v>122041373.1030534</v>
       </c>
       <c r="N3" t="n">
-        <v>122038476.3012702</v>
+        <v>122041373.1030533</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-11T13:25:10.000Z</t>
+          <t>2026-09-12T12:44:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,34 +655,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.99961</v>
+        <v>0.99981</v>
       </c>
       <c r="F4" t="n">
-        <v>183389557643</v>
+        <v>183482230974</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>58668007467</v>
+        <v>59719219122</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999861</v>
+        <v>0.99993</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999515</v>
+        <v>0.999562</v>
       </c>
       <c r="K4" t="n">
-        <v>-7.4913892993966e-05</v>
+        <v>0.00025862</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.00749</v>
+        <v>0.02306</v>
       </c>
       <c r="M4" t="n">
-        <v>183460843383.6048</v>
+        <v>183517171052.1943</v>
       </c>
       <c r="N4" t="n">
-        <v>188927789268.3162</v>
+        <v>188984116915.3062</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-11T13:25:10.000Z</t>
+          <t>2026-09-12T12:44:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>720.65</v>
+        <v>736.4299999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>95991544747</v>
+        <v>98062399038</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>886998934</v>
+        <v>1194854270</v>
       </c>
       <c r="I5" t="n">
-        <v>723.4</v>
+        <v>740.12</v>
       </c>
       <c r="J5" t="n">
-        <v>704.72</v>
+        <v>717.4400000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>14.1</v>
+        <v>14.67</v>
       </c>
       <c r="L5" t="n">
-        <v>1.99581</v>
+        <v>1.99022</v>
       </c>
       <c r="M5" t="n">
-        <v>133161118.37</v>
+        <v>133161036.91</v>
       </c>
       <c r="N5" t="n">
-        <v>133161113.02</v>
+        <v>133161033.96</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-11T13:25:10.000Z</t>
+          <t>2026-09-12T12:44:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="F6" t="n">
-        <v>85628071806</v>
+        <v>86186130739</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>2239415372</v>
+        <v>2258448691</v>
       </c>
       <c r="I6" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="J6" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00524616</v>
+        <v>0.0121198</v>
       </c>
       <c r="L6" t="n">
-        <v>0.38688</v>
+        <v>0.73402</v>
       </c>
       <c r="M6" t="n">
         <v>62879209849</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-11T13:25:10.000Z</t>
+          <t>2026-09-12T12:44:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999807</v>
+        <v>0.999865</v>
       </c>
       <c r="F7" t="n">
-        <v>74180090683</v>
+        <v>74337600627</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>16624710113</v>
+        <v>15757949678</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0.999952</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999741</v>
+        <v>0.999771</v>
       </c>
       <c r="K7" t="n">
-        <v>8.262000000000001e-05</v>
+        <v>7.379e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00826</v>
+        <v>0.00401</v>
       </c>
       <c r="M7" t="n">
-        <v>74193437886.21786</v>
+        <v>74347671861.2077</v>
       </c>
       <c r="N7" t="n">
-        <v>74212582140.11983</v>
+        <v>74349866797.12619</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-11T13:25:10.000Z</t>
+          <t>2026-09-12T12:44:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101.29</v>
+        <v>102.26</v>
       </c>
       <c r="F8" t="n">
-        <v>59439992570</v>
+        <v>59986196956</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>3174746581</v>
+        <v>4038038163</v>
       </c>
       <c r="I8" t="n">
-        <v>101.74</v>
+        <v>105.42</v>
       </c>
       <c r="J8" t="n">
-        <v>98.56</v>
+        <v>100.64</v>
       </c>
       <c r="K8" t="n">
-        <v>1.9</v>
+        <v>1.29</v>
       </c>
       <c r="L8" t="n">
-        <v>1.90687</v>
+        <v>1.16766</v>
       </c>
       <c r="M8" t="n">
-        <v>586537449.1371635</v>
+        <v>586632914.9787524</v>
       </c>
       <c r="N8" t="n">
-        <v>633830009.5093167</v>
+        <v>633924207.4848769</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-11T13:25:10.000Z</t>
+          <t>2026-09-12T12:44:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.336103</v>
+        <v>0.341025</v>
       </c>
       <c r="F9" t="n">
-        <v>31912142968</v>
+        <v>32378541531</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>358032118</v>
+        <v>521177154</v>
       </c>
       <c r="I9" t="n">
-        <v>0.340962</v>
+        <v>0.344079</v>
       </c>
       <c r="J9" t="n">
-        <v>0.335436</v>
+        <v>0.335532</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.002159410412531093</v>
+        <v>0.00460594</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6383799999999999</v>
+        <v>1.36849</v>
       </c>
       <c r="M9" t="n">
-        <v>94944701333.48628</v>
+        <v>94944652948.92628</v>
       </c>
       <c r="N9" t="n">
-        <v>94944700423.18279</v>
+        <v>94946361438.41998</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-11T13:25:10.000Z</t>
+          <t>2026-09-12T12:44:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,34 +1045,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.035</v>
+        <v>1.016</v>
       </c>
       <c r="F10" t="n">
-        <v>23223868031</v>
+        <v>22870501626</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>93264084</v>
+        <v>60215308</v>
       </c>
       <c r="I10" t="n">
         <v>1.036</v>
       </c>
       <c r="J10" t="n">
-        <v>1.015</v>
+        <v>1.016</v>
       </c>
       <c r="K10" t="n">
-        <v>0.007932140000000001</v>
+        <v>-0.0185665039219145</v>
       </c>
       <c r="L10" t="n">
-        <v>0.77257</v>
+        <v>-1.79099</v>
       </c>
       <c r="M10" t="n">
-        <v>22446057111.938</v>
+        <v>22502232981.668</v>
       </c>
       <c r="N10" t="n">
-        <v>22446057111.938</v>
+        <v>22502232981.668</v>
       </c>
       <c r="O10" t="n">
         <v>1.061</v>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-09-11T13:25:10.000Z</t>
+          <t>2026-09-12T12:44:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,34 +1110,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1158.21</v>
+        <v>1158.26</v>
       </c>
       <c r="F11" t="n">
-        <v>19616404230</v>
+        <v>19604336005</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>1671260451</v>
+        <v>1665786195</v>
       </c>
       <c r="I11" t="n">
-        <v>1183.37</v>
+        <v>1215.61</v>
       </c>
       <c r="J11" t="n">
-        <v>1055.58</v>
+        <v>1121.91</v>
       </c>
       <c r="K11" t="n">
-        <v>-17.24410873122633</v>
+        <v>-0.629609895717067</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.46702</v>
+        <v>0.1411</v>
       </c>
       <c r="M11" t="n">
         <v>16925695.4780448</v>
       </c>
       <c r="N11" t="n">
-        <v>16926651.7280448</v>
+        <v>16928367.3530448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1149,14 +1149,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-11T13:25:10.000Z</t>
+          <t>2026-09-12T12:44:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,28 +1175,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>81.20999999999999</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>18098825995</v>
+        <v>17867396242</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>1095111848</v>
+        <v>1071366521</v>
       </c>
       <c r="I12" t="n">
-        <v>82.09</v>
+        <v>83.63</v>
       </c>
       <c r="J12" t="n">
-        <v>78.27</v>
+        <v>78.41</v>
       </c>
       <c r="K12" t="n">
-        <v>0.123405</v>
+        <v>-1.044752684165488</v>
       </c>
       <c r="L12" t="n">
-        <v>0.15219</v>
+        <v>-1.36165</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1214,14 +1214,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-11T13:25:10.000Z</t>
+          <t>2026-09-12T12:44:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.0848</v>
+        <v>0.085033</v>
       </c>
       <c r="F13" t="n">
-        <v>13224091428</v>
+        <v>13255413715</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>678267919</v>
+        <v>651168802</v>
       </c>
       <c r="I13" t="n">
-        <v>0.085089</v>
+        <v>0.087898</v>
       </c>
       <c r="J13" t="n">
-        <v>0.082747</v>
+        <v>0.08368</v>
       </c>
       <c r="K13" t="n">
-        <v>0.00124017</v>
+        <v>0.00046809</v>
       </c>
       <c r="L13" t="n">
-        <v>1.48417</v>
+        <v>0.50806</v>
       </c>
       <c r="M13" t="n">
-        <v>155871456383.7052</v>
+        <v>155884756383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>155871546383.7052</v>
+        <v>155884476383.7052</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-11T13:25:10.000Z</t>
+          <t>2026-09-12T12:44:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,31 +1305,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.01582451</v>
+        <v>0.01512165</v>
       </c>
       <c r="F14" t="n">
-        <v>11227376908</v>
+        <v>10724534145</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>39502813</v>
+        <v>38289961</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0160076</v>
+        <v>0.01626765</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01551577</v>
+        <v>0.01509086</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.0215214789967e-05</v>
+        <v>-0.000651524093373202</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.19058</v>
+        <v>-4.09935</v>
       </c>
       <c r="M14" t="n">
-        <v>709212992829.0042</v>
+        <v>709217602168.6873</v>
       </c>
       <c r="N14" t="n">
         <v>1142408526965.963</v>
@@ -1344,144 +1344,144 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-09-11T13:25:10.000Z</t>
+          <t>2026-09-12T12:44:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>monero</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>xmr</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>USDS</t>
+          <t>Monero</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.999744</v>
+        <v>529.46</v>
       </c>
       <c r="F15" t="n">
-        <v>9744724175</v>
+        <v>9955702220</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>197400586</v>
+        <v>123793672</v>
       </c>
       <c r="I15" t="n">
-        <v>0.999936</v>
+        <v>546.62</v>
       </c>
       <c r="J15" t="n">
-        <v>0.999592</v>
+        <v>509.38</v>
       </c>
       <c r="K15" t="n">
-        <v>-7.2646757613426e-05</v>
+        <v>16.48</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.00727</v>
+        <v>3.27851</v>
       </c>
       <c r="M15" t="n">
-        <v>9747194186.835777</v>
+        <v>18803665.4396461</v>
       </c>
       <c r="N15" t="n">
-        <v>9748798031.413788</v>
+        <v>18803679.83773144</v>
       </c>
       <c r="O15" t="n">
-        <v>1.057</v>
+        <v>797.73</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2024-10-28T21:40:51.000Z</t>
+          <t>2026-01-14T11:34:07.000Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-09-11T13:25:10.000Z</t>
+          <t>2026-09-12T12:44:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>monero</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>xmr</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Monero</t>
+          <t>USDS</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>512.91</v>
+        <v>0.999871</v>
       </c>
       <c r="F16" t="n">
-        <v>9645572026</v>
+        <v>9804836648</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>102137061</v>
+        <v>169068394</v>
       </c>
       <c r="I16" t="n">
-        <v>518.6799999999999</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>500.26</v>
+        <v>0.999626</v>
       </c>
       <c r="K16" t="n">
-        <v>11.01</v>
+        <v>0.00020096</v>
       </c>
       <c r="L16" t="n">
-        <v>2.1934</v>
+        <v>0.00217</v>
       </c>
       <c r="M16" t="n">
-        <v>18803154.24465362</v>
+        <v>9806099950.497782</v>
       </c>
       <c r="N16" t="n">
-        <v>18803235.84437571</v>
+        <v>9806099950.497782</v>
       </c>
       <c r="O16" t="n">
-        <v>797.73</v>
+        <v>1.057</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-01-14T11:34:07.000Z</t>
+          <t>2024-10-28T21:40:51.000Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-09-11T13:25:10.000Z</t>
+          <t>2026-09-12T12:44:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1500,28 +1500,28 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>80.55</v>
+        <v>80.37</v>
       </c>
       <c r="F17" t="n">
-        <v>9497240871</v>
+        <v>9474296952</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>101915128</v>
+        <v>120604559</v>
       </c>
       <c r="I17" t="n">
-        <v>80.97</v>
+        <v>83.22</v>
       </c>
       <c r="J17" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K17" t="n">
-        <v>1.23</v>
+        <v>0.054638</v>
       </c>
       <c r="L17" t="n">
-        <v>1.54504</v>
+        <v>-0.18838</v>
       </c>
       <c r="M17" t="n">
         <v>117882016</v>
@@ -1530,23 +1530,23 @@
         <v>293532015</v>
       </c>
       <c r="O17" t="n">
-        <v>82.52</v>
+        <v>83.22</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-09-09T00:48:20.000Z</t>
+          <t>2026-09-11T14:03:10.000Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-09-11T13:25:10.000Z</t>
+          <t>2026-09-12T12:44:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1565,28 +1565,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>11.69</v>
+        <v>11.57</v>
       </c>
       <c r="F18" t="n">
-        <v>8749576424</v>
+        <v>8653159423</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>371507695</v>
+        <v>449714905</v>
       </c>
       <c r="I18" t="n">
-        <v>11.72</v>
+        <v>12.17</v>
       </c>
       <c r="J18" t="n">
-        <v>11.31</v>
+        <v>11.46</v>
       </c>
       <c r="K18" t="n">
-        <v>0.02035372</v>
+        <v>0.02458788</v>
       </c>
       <c r="L18" t="n">
-        <v>0.17437</v>
+        <v>0.05704</v>
       </c>
       <c r="M18" t="n">
         <v>748099970.424884</v>
@@ -1604,14 +1604,14 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-09-11T13:25:10.000Z</t>
+          <t>2026-09-12T12:44:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1630,28 +1630,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>9.15</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>8418079995</v>
+        <v>8383078709</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>189958</v>
+        <v>119813</v>
       </c>
       <c r="I19" t="n">
-        <v>9.23</v>
+        <v>9.16</v>
       </c>
       <c r="J19" t="n">
-        <v>9.02</v>
+        <v>9.1</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.03241308782886954</v>
+        <v>-0.03313417990051093</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.35293</v>
+        <v>-0.36101</v>
       </c>
       <c r="M19" t="n">
         <v>919857851.9</v>
@@ -1669,14 +1669,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-09-11T13:25:10.000Z</t>
+          <t>2026-09-12T12:44:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1695,31 +1695,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.207783</v>
+        <v>0.208994</v>
       </c>
       <c r="F20" t="n">
-        <v>7799990505</v>
+        <v>7840773190</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>475922020</v>
+        <v>484036030</v>
       </c>
       <c r="I20" t="n">
-        <v>0.211947</v>
+        <v>0.215743</v>
       </c>
       <c r="J20" t="n">
-        <v>0.200878</v>
+        <v>0.203215</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.002025983797910053</v>
+        <v>0.00173125</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.96563</v>
+        <v>0.54303</v>
       </c>
       <c r="M20" t="n">
-        <v>37510482444.2993</v>
+        <v>37516725700.17653</v>
       </c>
       <c r="N20" t="n">
         <v>45000000000</v>
@@ -1734,14 +1734,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-09-11T13:25:10.000Z</t>
+          <t>2026-09-12T12:44:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1760,31 +1760,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.1788</v>
+        <v>0.181899</v>
       </c>
       <c r="F21" t="n">
-        <v>6226118444</v>
+        <v>6336215728</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>144935960</v>
+        <v>152590419</v>
       </c>
       <c r="I21" t="n">
-        <v>0.179365</v>
+        <v>0.184869</v>
       </c>
       <c r="J21" t="n">
-        <v>0.173418</v>
+        <v>0.177114</v>
       </c>
       <c r="K21" t="n">
-        <v>0.00162509</v>
+        <v>0.00402238</v>
       </c>
       <c r="L21" t="n">
-        <v>0.91722</v>
+        <v>2.13215</v>
       </c>
       <c r="M21" t="n">
-        <v>34811503371.5922</v>
+        <v>34833772973.98598</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.70248</v>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-09-11T13:25:10.000Z</t>
+          <t>2026-09-12T12:44:20.000Z</t>
         </is>
       </c>
     </row>
